--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
   <si>
     <t>아이디</t>
   </si>
@@ -157,7 +157,7 @@
     <t>ExtraDamage</t>
   </si>
   <si>
-    <t>skill_scholar_basic_Fire</t>
+    <t>skill_scholar_basic_fire</t>
   </si>
   <si>
     <t>화염 화살</t>
@@ -175,7 +175,10 @@
     <t>Player/Projectile/Fire Arrow</t>
   </si>
   <si>
-    <t>skill_scholar_basic_Water</t>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_water</t>
   </si>
   <si>
     <t>냉기 화살</t>
@@ -187,7 +190,10 @@
     <t>Cold</t>
   </si>
   <si>
-    <t>skill_scholar_basic_Earth</t>
+    <t>Player/Projectile/Ice Arrow</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_earth</t>
   </si>
   <si>
     <t>암석 화살</t>
@@ -199,7 +205,10 @@
     <t>Physical</t>
   </si>
   <si>
-    <t>skill_scholar_basic_Air</t>
+    <t>Player/Projectile/Stone Arrow</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_air</t>
   </si>
   <si>
     <t>번개 화살</t>
@@ -211,7 +220,10 @@
     <t>Electric</t>
   </si>
   <si>
-    <t>skill_scholar_basic_Magic</t>
+    <t>Player/Projectile/Electric Arrow</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_magic</t>
   </si>
   <si>
     <t>마력 화살</t>
@@ -223,6 +235,9 @@
     <t>Magic</t>
   </si>
   <si>
+    <t>Player/Projectile/Magic Arrow</t>
+  </si>
+  <si>
     <t>skill_scholar_special_fire</t>
   </si>
   <si>
@@ -232,30 +247,48 @@
     <t>마우스 위치에 원소 폭발을 일으켜 몰려 있는 적을 정리합니다.</t>
   </si>
   <si>
+    <t>Player/Skill/Scholar_AOE/Fire Explosion</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
     <t>skill_scholar_special_water</t>
   </si>
   <si>
     <t>냉기 폭발</t>
   </si>
   <si>
+    <t>Player/Skill/Scholar_AOE/Ice Explosion</t>
+  </si>
+  <si>
     <t>skill_scholar_special_earth</t>
   </si>
   <si>
     <t>대지 폭발</t>
   </si>
   <si>
+    <t>Player/Skill/Scholar_AOE/Earth Explosion</t>
+  </si>
+  <si>
     <t>skill_scholar_special_air</t>
   </si>
   <si>
     <t>전기 폭발</t>
   </si>
   <si>
+    <t>Player/Skill/Scholar_AOE/Electric Explosion</t>
+  </si>
+  <si>
     <t>skill_scholar_special_magic</t>
   </si>
   <si>
     <t>마력 폭발</t>
   </si>
   <si>
+    <t>Player/Skill/Scholar_AOE/Magic Explosion</t>
+  </si>
+  <si>
     <t>skill_scholar_ult_summonbarrier</t>
   </si>
   <si>
@@ -316,9 +349,6 @@
     <t>ScholarBasic</t>
   </si>
   <si>
-    <t>Basic</t>
-  </si>
-  <si>
     <t>skill_scholar_special</t>
   </si>
   <si>
@@ -326,9 +356,6 @@
   </si>
   <si>
     <t>ScholarSpecial</t>
-  </si>
-  <si>
-    <t>Special</t>
   </si>
   <si>
     <t>skill_mercenary_passive</t>
@@ -503,6 +530,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -513,9 +543,6 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
@@ -1013,20 +1040,22 @@
       <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="12">
+      <c r="U4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="V4" s="13">
         <v>10.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D5" s="8">
         <v>15.0</v>
@@ -1058,25 +1087,29 @@
         <v>51</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5" s="8"/>
-      <c r="Q5" s="9"/>
+      <c r="Q5" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
       <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+      <c r="U5" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="V5" s="11"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D6" s="8">
         <v>28.0</v>
@@ -1108,25 +1141,29 @@
         <v>51</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P6" s="8"/>
-      <c r="Q6" s="9"/>
+      <c r="Q6" s="10" t="s">
+        <v>64</v>
+      </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
       <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+      <c r="U6" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="V6" s="11"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D7" s="8">
         <v>10.0</v>
@@ -1158,25 +1195,29 @@
         <v>51</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P7" s="8"/>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="10" t="s">
+        <v>69</v>
+      </c>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+      <c r="U7" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="V7" s="11"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8" s="8">
         <v>20.0</v>
@@ -1208,664 +1249,688 @@
         <v>51</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="9"/>
+        <v>73</v>
+      </c>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
       <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+      <c r="U8" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="V8" s="11"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="A9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="16">
         <v>45.0</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="16">
         <v>8.0</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="16">
         <v>30.0</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15">
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16">
         <v>4.0</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="16">
         <v>10.0</v>
       </c>
-      <c r="M9" s="15"/>
+      <c r="M9" s="16"/>
       <c r="N9" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
       <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="U9" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="V9" s="11"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="A10" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="16">
         <v>45.0</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="16">
         <v>8.0</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="16">
         <v>30.0</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15">
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16">
         <v>4.0</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="16">
         <v>10.0</v>
       </c>
-      <c r="M10" s="15"/>
+      <c r="M10" s="16"/>
       <c r="N10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
+        <v>58</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
       <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+      <c r="U10" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="V10" s="11"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="A11" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="16">
         <v>45.0</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="16">
         <v>8.0</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="16">
         <v>30.0</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15">
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16">
         <v>4.0</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="16">
         <v>10.0</v>
       </c>
-      <c r="M11" s="15"/>
+      <c r="M11" s="16"/>
       <c r="N11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
       <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="U11" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="V11" s="11"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="D12" s="16">
         <v>45.0</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="16">
         <v>8.0</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="16">
         <v>30.0</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15">
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16">
         <v>4.0</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="16">
         <v>10.0</v>
       </c>
-      <c r="M12" s="15"/>
+      <c r="M12" s="16"/>
       <c r="N12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
+        <v>68</v>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
       <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+      <c r="U12" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="V12" s="11"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="A13" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="16">
         <v>45.0</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="16">
         <v>8.0</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="16">
         <v>30.0</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15">
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16">
         <v>4.0</v>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="16">
         <v>10.0</v>
       </c>
-      <c r="M13" s="15"/>
+      <c r="M13" s="16"/>
       <c r="N13" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
+        <v>73</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
       <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="U13" s="12" t="s">
+        <v>79</v>
+      </c>
       <c r="V13" s="11"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15">
+      <c r="A14" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16">
         <v>45.0</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="16">
         <v>60.0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="15">
         <v>8.0</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15">
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16">
         <v>5.0</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="16">
         <v>8.0</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="16">
         <v>120.0</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="O14" s="9"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="U14" s="16" t="s">
-        <v>86</v>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="V14" s="11"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15">
+      <c r="A15" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16">
         <v>60.0</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="16">
         <v>50.0</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
       <c r="N15" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="U15" s="16" t="s">
-        <v>86</v>
+        <v>102</v>
+      </c>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="V15" s="11"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
+      <c r="A16" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
       <c r="N16" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="O16" s="9"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="A17" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="16">
         <v>20.0</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="16">
         <v>0.65</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="16">
         <v>0.0</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="16">
         <v>3.0</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="16">
         <v>15.0</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="16">
         <v>1.0</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="16">
         <v>1.0</v>
       </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16">
         <v>12.0</v>
       </c>
-      <c r="M17" s="15"/>
+      <c r="M17" s="16"/>
       <c r="N17" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="U17" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="V17" s="16"/>
+        <v>73</v>
+      </c>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="V17" s="12"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
+        <v>112</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
-      <c r="T18" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="U18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="V18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="U18" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="V18" s="12"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="15" t="s">
+      <c r="A19" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="9" t="s">
-        <v>96</v>
-      </c>
       <c r="O19" s="9"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
       <c r="T19" s="11"/>
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="A20" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="16">
         <v>18.0</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="16">
         <v>0.55</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="16">
         <v>0.0</v>
       </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15">
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16">
         <v>2.0</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="16">
         <v>2.5</v>
       </c>
-      <c r="M20" s="15"/>
+      <c r="M20" s="16"/>
       <c r="N20" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="P20" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
       <c r="T20" s="11"/>
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="A21" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="16">
         <v>32.0</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="16">
         <v>7.0</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="16">
         <v>25.0</v>
       </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15">
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16">
         <v>3.5</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="16">
         <v>4.5</v>
       </c>
-      <c r="M21" s="15"/>
+      <c r="M21" s="16"/>
       <c r="N21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="15"/>
-      <c r="R21" s="15"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="16"/>
+        <v>63</v>
+      </c>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="12"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="A22" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="16">
         <v>90.0</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="16">
         <v>45.0</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="16">
         <v>50.0</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="16">
         <v>2.0</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="16">
         <v>10.0</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="16">
         <v>0.0</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="16">
         <v>1.0</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="16">
         <v>3.0</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="16">
         <v>10.0</v>
       </c>
-      <c r="M22" s="15"/>
+      <c r="M22" s="16"/>
       <c r="N22" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="15"/>
-      <c r="R22" s="15"/>
-      <c r="S22" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="A23" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="16">
         <v>18.0</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="16">
         <v>60.0</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="16">
         <v>55.0</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="16">
         <v>5.0</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="16">
         <v>4.0</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15">
+      <c r="I23" s="16"/>
+      <c r="J23" s="16">
         <v>1.0</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="16">
         <v>5.0</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="16">
         <v>10.0</v>
       </c>
-      <c r="M23" s="15"/>
+      <c r="M23" s="16"/>
       <c r="N23" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
       <c r="T23" s="11"/>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>

--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태영\Desktop\WanderSoul\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12930" windowHeight="12135"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="145">
   <si>
     <t>아이디</t>
   </si>
@@ -404,60 +412,150 @@
   </si>
   <si>
     <t>직선 경로를 따라 이동하는 회오리를 만들어 경로 내 적에게 지속 피해를 줍니다. 끌어당김은 스킬 코드에서 처리합니다.</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_air</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_magic</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_fire</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_water</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_earth</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_air</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_magic</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_fire</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_water</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_earth</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special</t>
+  </si>
+  <si>
+    <r>
+      <t>Sprites/UI/Icon/skill_scholar_ult_summonbarrier_v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Carlito"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_ult_berserksoul_sample_B_charge</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="10">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -465,7 +563,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -475,7 +573,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -489,75 +593,80 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -565,7 +674,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -755,37 +864,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V1001"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.5"/>
-    <col customWidth="1" min="2" max="2" width="11.5"/>
-    <col customWidth="1" min="3" max="3" width="93.25"/>
-    <col customWidth="1" min="4" max="4" width="5.88"/>
-    <col customWidth="1" min="5" max="6" width="8.75"/>
-    <col customWidth="1" min="7" max="7" width="15.5"/>
-    <col customWidth="1" min="8" max="8" width="12.88"/>
-    <col customWidth="1" min="9" max="9" width="11.5"/>
-    <col customWidth="1" min="10" max="10" width="16.13"/>
-    <col customWidth="1" min="11" max="11" width="14.38"/>
-    <col customWidth="1" min="12" max="12" width="12.0"/>
-    <col customWidth="1" min="13" max="13" width="17.88"/>
-    <col customWidth="1" min="14" max="15" width="15.13"/>
-    <col customWidth="1" min="16" max="16" width="17.88"/>
-    <col customWidth="1" min="17" max="17" width="21.88"/>
-    <col customWidth="1" min="18" max="18" width="7.13"/>
-    <col customWidth="1" min="19" max="19" width="7.63"/>
-    <col customWidth="1" min="22" max="22" width="20.38"/>
+    <col min="1" max="1" width="25.5" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="93.25" customWidth="1"/>
+    <col min="4" max="4" width="5.875" customWidth="1"/>
+    <col min="5" max="6" width="8.75" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="14.375" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="17.875" customWidth="1"/>
+    <col min="14" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="17.875" customWidth="1"/>
+    <col min="17" max="17" width="21.875" customWidth="1"/>
+    <col min="18" max="18" width="7.125" customWidth="1"/>
+    <col min="19" max="19" width="55.75" customWidth="1"/>
+    <col min="22" max="22" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:22" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,7 +962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="24.0" customHeight="1">
+    <row r="2" spans="1:22" ht="24" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -921,7 +1030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="27.75" customHeight="1">
+    <row r="3" spans="1:22" ht="27.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -989,7 +1098,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:22" ht="13.5">
       <c r="A4" s="7" t="s">
         <v>48</v>
       </c>
@@ -1000,31 +1109,31 @@
         <v>50</v>
       </c>
       <c r="D4" s="7">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8">
         <v>0.6</v>
       </c>
       <c r="F4" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G4" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="9">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I4" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="9" t="s">
@@ -1038,16 +1147,18 @@
         <v>53</v>
       </c>
       <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
+      <c r="S4" s="9" t="s">
+        <v>138</v>
+      </c>
       <c r="T4" s="11"/>
       <c r="U4" s="12" t="s">
         <v>54</v>
       </c>
       <c r="V4" s="13">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="13.5">
       <c r="A5" s="7" t="s">
         <v>55</v>
       </c>
@@ -1058,29 +1169,29 @@
         <v>57</v>
       </c>
       <c r="D5" s="8">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E5" s="8">
         <v>0.7</v>
       </c>
       <c r="F5" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="9">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="I5" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9" t="s">
@@ -1094,14 +1205,16 @@
         <v>59</v>
       </c>
       <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
+      <c r="S5" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="T5" s="11"/>
       <c r="U5" s="12" t="s">
         <v>54</v>
       </c>
       <c r="V5" s="11"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:22" ht="13.5">
       <c r="A6" s="7" t="s">
         <v>60</v>
       </c>
@@ -1112,29 +1225,29 @@
         <v>62</v>
       </c>
       <c r="D6" s="8">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="E6" s="8">
         <v>0.95</v>
       </c>
       <c r="F6" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I6" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="9" t="s">
@@ -1148,14 +1261,16 @@
         <v>64</v>
       </c>
       <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
+      <c r="S6" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="T6" s="11"/>
       <c r="U6" s="12" t="s">
         <v>54</v>
       </c>
       <c r="V6" s="11"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:22" ht="13.5">
       <c r="A7" s="7" t="s">
         <v>65</v>
       </c>
@@ -1166,29 +1281,29 @@
         <v>67</v>
       </c>
       <c r="D7" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E7" s="8">
         <v>0.35</v>
       </c>
       <c r="F7" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G7" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H7" s="9">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="I7" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9" t="s">
@@ -1202,14 +1317,16 @@
         <v>69</v>
       </c>
       <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
+      <c r="S7" s="9" t="s">
+        <v>131</v>
+      </c>
       <c r="T7" s="11"/>
       <c r="U7" s="12" t="s">
         <v>54</v>
       </c>
       <c r="V7" s="11"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:22" ht="13.5">
       <c r="A8" s="7" t="s">
         <v>70</v>
       </c>
@@ -1220,29 +1337,29 @@
         <v>72</v>
       </c>
       <c r="D8" s="8">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E8" s="8">
         <v>0.65</v>
       </c>
       <c r="F8" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="9">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="I8" s="9">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="9" t="s">
@@ -1256,14 +1373,16 @@
         <v>74</v>
       </c>
       <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
+      <c r="S8" s="9" t="s">
+        <v>132</v>
+      </c>
       <c r="T8" s="11"/>
       <c r="U8" s="12" t="s">
         <v>54</v>
       </c>
       <c r="V8" s="11"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:22" ht="13.5">
       <c r="A9" s="15" t="s">
         <v>75</v>
       </c>
@@ -1274,23 +1393,23 @@
         <v>77</v>
       </c>
       <c r="D9" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E9" s="16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F9" s="16">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M9" s="16"/>
       <c r="N9" s="9" t="s">
@@ -1304,14 +1423,16 @@
         <v>78</v>
       </c>
       <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
+      <c r="S9" s="19" t="s">
+        <v>133</v>
+      </c>
       <c r="T9" s="11"/>
       <c r="U9" s="12" t="s">
         <v>79</v>
       </c>
       <c r="V9" s="11"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:22" ht="13.5">
       <c r="A10" s="16" t="s">
         <v>80</v>
       </c>
@@ -1322,23 +1443,23 @@
         <v>77</v>
       </c>
       <c r="D10" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E10" s="16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="16">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
       <c r="K10" s="16">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="9" t="s">
@@ -1352,14 +1473,16 @@
         <v>82</v>
       </c>
       <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="16" t="s">
+        <v>134</v>
+      </c>
       <c r="T10" s="11"/>
       <c r="U10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="V10" s="11"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:22" ht="13.5">
       <c r="A11" s="16" t="s">
         <v>83</v>
       </c>
@@ -1370,23 +1493,23 @@
         <v>77</v>
       </c>
       <c r="D11" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E11" s="16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F11" s="16">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
       <c r="K11" s="16">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="9" t="s">
@@ -1400,14 +1523,16 @@
         <v>85</v>
       </c>
       <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
+      <c r="S11" s="19" t="s">
+        <v>135</v>
+      </c>
       <c r="T11" s="11"/>
       <c r="U11" s="12" t="s">
         <v>79</v>
       </c>
       <c r="V11" s="11"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:22" ht="13.5">
       <c r="A12" s="16" t="s">
         <v>86</v>
       </c>
@@ -1418,23 +1543,23 @@
         <v>77</v>
       </c>
       <c r="D12" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E12" s="16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F12" s="16">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
       <c r="K12" s="16">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M12" s="16"/>
       <c r="N12" s="9" t="s">
@@ -1448,14 +1573,16 @@
         <v>88</v>
       </c>
       <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
+      <c r="S12" s="16" t="s">
+        <v>136</v>
+      </c>
       <c r="T12" s="11"/>
       <c r="U12" s="12" t="s">
         <v>79</v>
       </c>
       <c r="V12" s="11"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:22" ht="13.5">
       <c r="A13" s="16" t="s">
         <v>89</v>
       </c>
@@ -1466,23 +1593,23 @@
         <v>77</v>
       </c>
       <c r="D13" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E13" s="16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F13" s="16">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M13" s="16"/>
       <c r="N13" s="9" t="s">
@@ -1496,14 +1623,16 @@
         <v>91</v>
       </c>
       <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
+      <c r="S13" s="16" t="s">
+        <v>137</v>
+      </c>
       <c r="T13" s="11"/>
       <c r="U13" s="12" t="s">
         <v>79</v>
       </c>
       <c r="V13" s="11"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:22" ht="13.5">
       <c r="A14" s="16" t="s">
         <v>92</v>
       </c>
@@ -1515,25 +1644,25 @@
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="F14" s="16">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="G14" s="15">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L14" s="16">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="M14" s="16">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="N14" s="9" t="s">
         <v>95</v>
@@ -1542,7 +1671,9 @@
       <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
+      <c r="S14" s="19" t="s">
+        <v>142</v>
+      </c>
       <c r="T14" s="12" t="s">
         <v>96</v>
       </c>
@@ -1551,7 +1682,7 @@
       </c>
       <c r="V14" s="11"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:22" ht="81">
       <c r="A15" s="16" t="s">
         <v>98</v>
       </c>
@@ -1563,10 +1694,10 @@
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F15" s="16">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
@@ -1593,7 +1724,7 @@
       </c>
       <c r="V15" s="11"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:22" ht="13.5">
       <c r="A16" s="16" t="s">
         <v>104</v>
       </c>
@@ -1620,12 +1751,14 @@
       <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
+      <c r="S16" s="19" t="s">
+        <v>144</v>
+      </c>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:22" ht="13.5">
       <c r="A17" s="16" t="s">
         <v>108</v>
       </c>
@@ -1636,29 +1769,29 @@
         <v>110</v>
       </c>
       <c r="D17" s="16">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E17" s="16">
         <v>0.65</v>
       </c>
       <c r="F17" s="16">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G17" s="16">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="16">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="I17" s="16">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="16">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="16"/>
       <c r="L17" s="16">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M17" s="16"/>
       <c r="N17" s="9" t="s">
@@ -1670,7 +1803,9 @@
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
       <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
+      <c r="S17" s="19" t="s">
+        <v>143</v>
+      </c>
       <c r="T17" s="12" t="s">
         <v>111</v>
       </c>
@@ -1679,7 +1814,7 @@
       </c>
       <c r="V17" s="12"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:22" ht="13.5">
       <c r="A18" s="8" t="s">
         <v>112</v>
       </c>
@@ -1702,7 +1837,9 @@
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
+      <c r="S18" s="16" t="s">
+        <v>141</v>
+      </c>
       <c r="T18" s="12" t="s">
         <v>114</v>
       </c>
@@ -1711,7 +1848,7 @@
       </c>
       <c r="V18" s="12"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:22" ht="13.5">
       <c r="A19" s="16" t="s">
         <v>115</v>
       </c>
@@ -1743,7 +1880,7 @@
       <c r="U19" s="11"/>
       <c r="V19" s="11"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:22" ht="15.75" customHeight="1">
       <c r="A20" s="16" t="s">
         <v>118</v>
       </c>
@@ -1754,20 +1891,20 @@
         <v>120</v>
       </c>
       <c r="D20" s="16">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="E20" s="16">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F20" s="16">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
       <c r="J20" s="16"/>
       <c r="K20" s="16">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="16">
         <v>2.5</v>
@@ -1789,7 +1926,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:22" ht="15.75" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>122</v>
       </c>
@@ -1800,13 +1937,13 @@
         <v>124</v>
       </c>
       <c r="D21" s="16">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="E21" s="16">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="16">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
@@ -1833,7 +1970,7 @@
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:22" ht="15.75" customHeight="1">
       <c r="A22" s="16" t="s">
         <v>125</v>
       </c>
@@ -1844,31 +1981,31 @@
         <v>127</v>
       </c>
       <c r="D22" s="16">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="E22" s="16">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="F22" s="16">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="G22" s="16">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="I22" s="16">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J22" s="16">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="16">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="9" t="s">
@@ -1885,7 +2022,7 @@
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:22" ht="15.75" customHeight="1">
       <c r="A23" s="16" t="s">
         <v>128</v>
       </c>
@@ -1896,29 +2033,29 @@
         <v>130</v>
       </c>
       <c r="D23" s="16">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="E23" s="16">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F23" s="16">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="G23" s="16">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H23" s="16">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I23" s="16"/>
       <c r="J23" s="16">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="16">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L23" s="16">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M23" s="16"/>
       <c r="N23" s="9" t="s">
@@ -1935,7 +2072,7 @@
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:22" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
@@ -1959,7 +2096,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:22" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -1983,7 +2120,7 @@
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:22" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -2007,7 +2144,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:22" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -2031,7 +2168,7 @@
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:22" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -2055,7 +2192,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:22" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2079,7 +2216,7 @@
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:22" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -2103,7 +2240,7 @@
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:22" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -2127,7 +2264,7 @@
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:22" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -2151,7 +2288,7 @@
       <c r="U32" s="11"/>
       <c r="V32" s="11"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:22" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -2175,7 +2312,7 @@
       <c r="U33" s="11"/>
       <c r="V33" s="11"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:22" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -2199,7 +2336,7 @@
       <c r="U34" s="11"/>
       <c r="V34" s="11"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:22" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -2223,7 +2360,7 @@
       <c r="U35" s="11"/>
       <c r="V35" s="11"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:22" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2247,7 +2384,7 @@
       <c r="U36" s="11"/>
       <c r="V36" s="11"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:22" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -2271,7 +2408,7 @@
       <c r="U37" s="11"/>
       <c r="V37" s="11"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:22" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -2295,7 +2432,7 @@
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:22" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2319,7 +2456,7 @@
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:22" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -2343,7 +2480,7 @@
       <c r="U40" s="11"/>
       <c r="V40" s="11"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:22" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -2367,7 +2504,7 @@
       <c r="U41" s="11"/>
       <c r="V41" s="11"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:22" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2391,7 +2528,7 @@
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:22" ht="15.75" customHeight="1">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -2415,7 +2552,7 @@
       <c r="U43" s="11"/>
       <c r="V43" s="11"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:22" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -2439,7 +2576,7 @@
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:22" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -2463,7 +2600,7 @@
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:22" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -2487,7 +2624,7 @@
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:22" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -2511,7 +2648,7 @@
       <c r="U47" s="11"/>
       <c r="V47" s="11"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:22" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -2535,7 +2672,7 @@
       <c r="U48" s="11"/>
       <c r="V48" s="11"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:22" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -2559,7 +2696,7 @@
       <c r="U49" s="11"/>
       <c r="V49" s="11"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:22" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -2583,7 +2720,7 @@
       <c r="U50" s="11"/>
       <c r="V50" s="11"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:22" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -2607,7 +2744,7 @@
       <c r="U51" s="11"/>
       <c r="V51" s="11"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:22" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -2631,7 +2768,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:22" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -2655,7 +2792,7 @@
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:22" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -2679,7 +2816,7 @@
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:22" ht="15.75" customHeight="1">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -2703,7 +2840,7 @@
       <c r="U55" s="11"/>
       <c r="V55" s="11"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:22" ht="15.75" customHeight="1">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -2727,7 +2864,7 @@
       <c r="U56" s="11"/>
       <c r="V56" s="11"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:22" ht="15.75" customHeight="1">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -2751,7 +2888,7 @@
       <c r="U57" s="11"/>
       <c r="V57" s="11"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:22" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -2775,7 +2912,7 @@
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:22" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -2799,7 +2936,7 @@
       <c r="U59" s="11"/>
       <c r="V59" s="11"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:22" ht="15.75" customHeight="1">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -2823,7 +2960,7 @@
       <c r="U60" s="11"/>
       <c r="V60" s="11"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:22" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -2847,7 +2984,7 @@
       <c r="U61" s="11"/>
       <c r="V61" s="11"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:22" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -2871,7 +3008,7 @@
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:22" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -2895,7 +3032,7 @@
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:22" ht="15.75" customHeight="1">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -2919,7 +3056,7 @@
       <c r="U64" s="11"/>
       <c r="V64" s="11"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:22" ht="15.75" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -2943,7 +3080,7 @@
       <c r="U65" s="11"/>
       <c r="V65" s="11"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:22" ht="15.75" customHeight="1">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -2967,7 +3104,7 @@
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:22" ht="15.75" customHeight="1">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -2991,7 +3128,7 @@
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:22" ht="15.75" customHeight="1">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -3015,7 +3152,7 @@
       <c r="U68" s="11"/>
       <c r="V68" s="11"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:22" ht="15.75" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -3039,7 +3176,7 @@
       <c r="U69" s="11"/>
       <c r="V69" s="11"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:22" ht="15.75" customHeight="1">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -3063,7 +3200,7 @@
       <c r="U70" s="11"/>
       <c r="V70" s="11"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:22" ht="15.75" customHeight="1">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -3087,7 +3224,7 @@
       <c r="U71" s="11"/>
       <c r="V71" s="11"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:22" ht="15.75" customHeight="1">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -3111,7 +3248,7 @@
       <c r="U72" s="11"/>
       <c r="V72" s="11"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:22" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -3135,7 +3272,7 @@
       <c r="U73" s="11"/>
       <c r="V73" s="11"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:22" ht="15.75" customHeight="1">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -3159,7 +3296,7 @@
       <c r="U74" s="11"/>
       <c r="V74" s="11"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:22" ht="15.75" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -3183,7 +3320,7 @@
       <c r="U75" s="11"/>
       <c r="V75" s="11"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:22" ht="15.75" customHeight="1">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -3207,7 +3344,7 @@
       <c r="U76" s="11"/>
       <c r="V76" s="11"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:22" ht="15.75" customHeight="1">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -3231,7 +3368,7 @@
       <c r="U77" s="11"/>
       <c r="V77" s="11"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:22" ht="15.75" customHeight="1">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -3255,7 +3392,7 @@
       <c r="U78" s="11"/>
       <c r="V78" s="11"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:22" ht="15.75" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -3279,7 +3416,7 @@
       <c r="U79" s="11"/>
       <c r="V79" s="11"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:22" ht="15.75" customHeight="1">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -3303,7 +3440,7 @@
       <c r="U80" s="11"/>
       <c r="V80" s="11"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:22" ht="15.75" customHeight="1">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -3327,7 +3464,7 @@
       <c r="U81" s="11"/>
       <c r="V81" s="11"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:22" ht="15.75" customHeight="1">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -3351,7 +3488,7 @@
       <c r="U82" s="11"/>
       <c r="V82" s="11"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:22" ht="15.75" customHeight="1">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -3375,7 +3512,7 @@
       <c r="U83" s="11"/>
       <c r="V83" s="11"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:22" ht="15.75" customHeight="1">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -3399,7 +3536,7 @@
       <c r="U84" s="11"/>
       <c r="V84" s="11"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:22" ht="15.75" customHeight="1">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -3423,7 +3560,7 @@
       <c r="U85" s="11"/>
       <c r="V85" s="11"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:22" ht="15.75" customHeight="1">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -3447,7 +3584,7 @@
       <c r="U86" s="11"/>
       <c r="V86" s="11"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:22" ht="15.75" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -3471,7 +3608,7 @@
       <c r="U87" s="11"/>
       <c r="V87" s="11"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:22" ht="15.75" customHeight="1">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -3495,7 +3632,7 @@
       <c r="U88" s="11"/>
       <c r="V88" s="11"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:22" ht="15.75" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -3519,7 +3656,7 @@
       <c r="U89" s="11"/>
       <c r="V89" s="11"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:22" ht="15.75" customHeight="1">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -3543,7 +3680,7 @@
       <c r="U90" s="11"/>
       <c r="V90" s="11"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:22" ht="15.75" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -3567,7 +3704,7 @@
       <c r="U91" s="11"/>
       <c r="V91" s="11"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:22" ht="15.75" customHeight="1">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -3591,7 +3728,7 @@
       <c r="U92" s="11"/>
       <c r="V92" s="11"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:22" ht="15.75" customHeight="1">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -3615,7 +3752,7 @@
       <c r="U93" s="11"/>
       <c r="V93" s="11"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:22" ht="15.75" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -3639,7 +3776,7 @@
       <c r="U94" s="11"/>
       <c r="V94" s="11"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:22" ht="15.75" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -3663,7 +3800,7 @@
       <c r="U95" s="11"/>
       <c r="V95" s="11"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:22" ht="15.75" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -3687,7 +3824,7 @@
       <c r="U96" s="11"/>
       <c r="V96" s="11"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:22" ht="15.75" customHeight="1">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -3711,7 +3848,7 @@
       <c r="U97" s="11"/>
       <c r="V97" s="11"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:22" ht="15.75" customHeight="1">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -3735,7 +3872,7 @@
       <c r="U98" s="11"/>
       <c r="V98" s="11"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:22" ht="15.75" customHeight="1">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -3759,7 +3896,7 @@
       <c r="U99" s="11"/>
       <c r="V99" s="11"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:22" ht="15.75" customHeight="1">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -3783,7 +3920,7 @@
       <c r="U100" s="11"/>
       <c r="V100" s="11"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:22" ht="15.75" customHeight="1">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -3807,7 +3944,7 @@
       <c r="U101" s="11"/>
       <c r="V101" s="11"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:22" ht="15.75" customHeight="1">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -3831,7 +3968,7 @@
       <c r="U102" s="11"/>
       <c r="V102" s="11"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:22" ht="15.75" customHeight="1">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -3855,7 +3992,7 @@
       <c r="U103" s="11"/>
       <c r="V103" s="11"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:22" ht="15.75" customHeight="1">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -3879,7 +4016,7 @@
       <c r="U104" s="11"/>
       <c r="V104" s="11"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:22" ht="15.75" customHeight="1">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -3903,7 +4040,7 @@
       <c r="U105" s="11"/>
       <c r="V105" s="11"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:22" ht="15.75" customHeight="1">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -3927,7 +4064,7 @@
       <c r="U106" s="11"/>
       <c r="V106" s="11"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:22" ht="15.75" customHeight="1">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -3951,7 +4088,7 @@
       <c r="U107" s="11"/>
       <c r="V107" s="11"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:22" ht="15.75" customHeight="1">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -3975,7 +4112,7 @@
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:22" ht="15.75" customHeight="1">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -3999,7 +4136,7 @@
       <c r="U109" s="11"/>
       <c r="V109" s="11"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:22" ht="15.75" customHeight="1">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -4023,7 +4160,7 @@
       <c r="U110" s="11"/>
       <c r="V110" s="11"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:22" ht="15.75" customHeight="1">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -4047,7 +4184,7 @@
       <c r="U111" s="11"/>
       <c r="V111" s="11"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:22" ht="15.75" customHeight="1">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -4071,7 +4208,7 @@
       <c r="U112" s="11"/>
       <c r="V112" s="11"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:22" ht="15.75" customHeight="1">
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
@@ -4095,7 +4232,7 @@
       <c r="U113" s="11"/>
       <c r="V113" s="11"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:22" ht="15.75" customHeight="1">
       <c r="A114" s="8"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
@@ -4119,7 +4256,7 @@
       <c r="U114" s="11"/>
       <c r="V114" s="11"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:22" ht="15.75" customHeight="1">
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
@@ -4143,7 +4280,7 @@
       <c r="U115" s="11"/>
       <c r="V115" s="11"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:22" ht="15.75" customHeight="1">
       <c r="A116" s="8"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
@@ -4167,7 +4304,7 @@
       <c r="U116" s="11"/>
       <c r="V116" s="11"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:22" ht="15.75" customHeight="1">
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
@@ -4191,7 +4328,7 @@
       <c r="U117" s="11"/>
       <c r="V117" s="11"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:22" ht="15.75" customHeight="1">
       <c r="A118" s="8"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
@@ -4215,7 +4352,7 @@
       <c r="U118" s="11"/>
       <c r="V118" s="11"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:22" ht="15.75" customHeight="1">
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
@@ -4239,7 +4376,7 @@
       <c r="U119" s="11"/>
       <c r="V119" s="11"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:22" ht="15.75" customHeight="1">
       <c r="A120" s="8"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
@@ -4263,7 +4400,7 @@
       <c r="U120" s="11"/>
       <c r="V120" s="11"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:22" ht="15.75" customHeight="1">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -4287,7 +4424,7 @@
       <c r="U121" s="11"/>
       <c r="V121" s="11"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:22" ht="15.75" customHeight="1">
       <c r="A122" s="8"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -4311,7 +4448,7 @@
       <c r="U122" s="11"/>
       <c r="V122" s="11"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:22" ht="15.75" customHeight="1">
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
@@ -4335,7 +4472,7 @@
       <c r="U123" s="11"/>
       <c r="V123" s="11"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:22" ht="15.75" customHeight="1">
       <c r="A124" s="8"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
@@ -4359,7 +4496,7 @@
       <c r="U124" s="11"/>
       <c r="V124" s="11"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:22" ht="15.75" customHeight="1">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -4383,7 +4520,7 @@
       <c r="U125" s="11"/>
       <c r="V125" s="11"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:22" ht="15.75" customHeight="1">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
@@ -4407,7 +4544,7 @@
       <c r="U126" s="11"/>
       <c r="V126" s="11"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:22" ht="15.75" customHeight="1">
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
@@ -4431,7 +4568,7 @@
       <c r="U127" s="11"/>
       <c r="V127" s="11"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:22" ht="15.75" customHeight="1">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
@@ -4455,7 +4592,7 @@
       <c r="U128" s="11"/>
       <c r="V128" s="11"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:22" ht="15.75" customHeight="1">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
@@ -4479,7 +4616,7 @@
       <c r="U129" s="11"/>
       <c r="V129" s="11"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:22" ht="15.75" customHeight="1">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
@@ -4503,7 +4640,7 @@
       <c r="U130" s="11"/>
       <c r="V130" s="11"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:22" ht="15.75" customHeight="1">
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
@@ -4527,7 +4664,7 @@
       <c r="U131" s="11"/>
       <c r="V131" s="11"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:22" ht="15.75" customHeight="1">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -4551,7 +4688,7 @@
       <c r="U132" s="11"/>
       <c r="V132" s="11"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:22" ht="15.75" customHeight="1">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -4575,7 +4712,7 @@
       <c r="U133" s="11"/>
       <c r="V133" s="11"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:22" ht="15.75" customHeight="1">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -4599,7 +4736,7 @@
       <c r="U134" s="11"/>
       <c r="V134" s="11"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:22" ht="15.75" customHeight="1">
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -4623,7 +4760,7 @@
       <c r="U135" s="11"/>
       <c r="V135" s="11"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:22" ht="15.75" customHeight="1">
       <c r="A136" s="8"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -4647,7 +4784,7 @@
       <c r="U136" s="11"/>
       <c r="V136" s="11"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:22" ht="15.75" customHeight="1">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -4671,7 +4808,7 @@
       <c r="U137" s="11"/>
       <c r="V137" s="11"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:22" ht="15.75" customHeight="1">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -4695,7 +4832,7 @@
       <c r="U138" s="11"/>
       <c r="V138" s="11"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:22" ht="15.75" customHeight="1">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
@@ -4719,7 +4856,7 @@
       <c r="U139" s="11"/>
       <c r="V139" s="11"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:22" ht="15.75" customHeight="1">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
@@ -4743,7 +4880,7 @@
       <c r="U140" s="11"/>
       <c r="V140" s="11"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:22" ht="15.75" customHeight="1">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
@@ -4767,7 +4904,7 @@
       <c r="U141" s="11"/>
       <c r="V141" s="11"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:22" ht="15.75" customHeight="1">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
@@ -4791,7 +4928,7 @@
       <c r="U142" s="11"/>
       <c r="V142" s="11"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:22" ht="15.75" customHeight="1">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
@@ -4815,7 +4952,7 @@
       <c r="U143" s="11"/>
       <c r="V143" s="11"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:22" ht="15.75" customHeight="1">
       <c r="A144" s="8"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
@@ -4839,7 +4976,7 @@
       <c r="U144" s="11"/>
       <c r="V144" s="11"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:22" ht="15.75" customHeight="1">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
@@ -4863,7 +5000,7 @@
       <c r="U145" s="11"/>
       <c r="V145" s="11"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:22" ht="15.75" customHeight="1">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
@@ -4887,7 +5024,7 @@
       <c r="U146" s="11"/>
       <c r="V146" s="11"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:22" ht="15.75" customHeight="1">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -4911,7 +5048,7 @@
       <c r="U147" s="11"/>
       <c r="V147" s="11"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:22" ht="15.75" customHeight="1">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
@@ -4935,7 +5072,7 @@
       <c r="U148" s="11"/>
       <c r="V148" s="11"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:22" ht="15.75" customHeight="1">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -4959,7 +5096,7 @@
       <c r="U149" s="11"/>
       <c r="V149" s="11"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:22" ht="15.75" customHeight="1">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -4983,7 +5120,7 @@
       <c r="U150" s="11"/>
       <c r="V150" s="11"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:22" ht="15.75" customHeight="1">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -5007,7 +5144,7 @@
       <c r="U151" s="11"/>
       <c r="V151" s="11"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:22" ht="15.75" customHeight="1">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -5031,7 +5168,7 @@
       <c r="U152" s="11"/>
       <c r="V152" s="11"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:22" ht="15.75" customHeight="1">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -5055,7 +5192,7 @@
       <c r="U153" s="11"/>
       <c r="V153" s="11"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:22" ht="15.75" customHeight="1">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -5079,7 +5216,7 @@
       <c r="U154" s="11"/>
       <c r="V154" s="11"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:22" ht="15.75" customHeight="1">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -5103,7 +5240,7 @@
       <c r="U155" s="11"/>
       <c r="V155" s="11"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:22" ht="15.75" customHeight="1">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -5127,7 +5264,7 @@
       <c r="U156" s="11"/>
       <c r="V156" s="11"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:22" ht="15.75" customHeight="1">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -5151,7 +5288,7 @@
       <c r="U157" s="11"/>
       <c r="V157" s="11"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:22" ht="15.75" customHeight="1">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -5175,7 +5312,7 @@
       <c r="U158" s="11"/>
       <c r="V158" s="11"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:22" ht="15.75" customHeight="1">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -5199,7 +5336,7 @@
       <c r="U159" s="11"/>
       <c r="V159" s="11"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:22" ht="15.75" customHeight="1">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -5223,7 +5360,7 @@
       <c r="U160" s="11"/>
       <c r="V160" s="11"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:22" ht="15.75" customHeight="1">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -5247,7 +5384,7 @@
       <c r="U161" s="11"/>
       <c r="V161" s="11"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:22" ht="15.75" customHeight="1">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -5271,7 +5408,7 @@
       <c r="U162" s="11"/>
       <c r="V162" s="11"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:22" ht="15.75" customHeight="1">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -5295,7 +5432,7 @@
       <c r="U163" s="11"/>
       <c r="V163" s="11"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:22" ht="15.75" customHeight="1">
       <c r="A164" s="8"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -5319,7 +5456,7 @@
       <c r="U164" s="11"/>
       <c r="V164" s="11"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:22" ht="15.75" customHeight="1">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
@@ -5343,7 +5480,7 @@
       <c r="U165" s="11"/>
       <c r="V165" s="11"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:22" ht="15.75" customHeight="1">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
@@ -5367,7 +5504,7 @@
       <c r="U166" s="11"/>
       <c r="V166" s="11"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:22" ht="15.75" customHeight="1">
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
@@ -5391,7 +5528,7 @@
       <c r="U167" s="11"/>
       <c r="V167" s="11"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:22" ht="15.75" customHeight="1">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
@@ -5415,7 +5552,7 @@
       <c r="U168" s="11"/>
       <c r="V168" s="11"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:22" ht="15.75" customHeight="1">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
@@ -5439,7 +5576,7 @@
       <c r="U169" s="11"/>
       <c r="V169" s="11"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:22" ht="15.75" customHeight="1">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
@@ -5463,7 +5600,7 @@
       <c r="U170" s="11"/>
       <c r="V170" s="11"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:22" ht="15.75" customHeight="1">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
@@ -5487,7 +5624,7 @@
       <c r="U171" s="11"/>
       <c r="V171" s="11"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:22" ht="15.75" customHeight="1">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
@@ -5511,7 +5648,7 @@
       <c r="U172" s="11"/>
       <c r="V172" s="11"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:22" ht="15.75" customHeight="1">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
@@ -5535,7 +5672,7 @@
       <c r="U173" s="11"/>
       <c r="V173" s="11"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:22" ht="15.75" customHeight="1">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
@@ -5559,7 +5696,7 @@
       <c r="U174" s="11"/>
       <c r="V174" s="11"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:22" ht="15.75" customHeight="1">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
@@ -5583,7 +5720,7 @@
       <c r="U175" s="11"/>
       <c r="V175" s="11"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:22" ht="15.75" customHeight="1">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
@@ -5607,7 +5744,7 @@
       <c r="U176" s="11"/>
       <c r="V176" s="11"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:22" ht="15.75" customHeight="1">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
@@ -5631,7 +5768,7 @@
       <c r="U177" s="11"/>
       <c r="V177" s="11"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:22" ht="15.75" customHeight="1">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -5655,7 +5792,7 @@
       <c r="U178" s="11"/>
       <c r="V178" s="11"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:22" ht="15.75" customHeight="1">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
@@ -5679,7 +5816,7 @@
       <c r="U179" s="11"/>
       <c r="V179" s="11"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:22" ht="15.75" customHeight="1">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
@@ -5703,7 +5840,7 @@
       <c r="U180" s="11"/>
       <c r="V180" s="11"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:22" ht="15.75" customHeight="1">
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -5727,7 +5864,7 @@
       <c r="U181" s="11"/>
       <c r="V181" s="11"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:22" ht="15.75" customHeight="1">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
@@ -5751,7 +5888,7 @@
       <c r="U182" s="11"/>
       <c r="V182" s="11"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:22" ht="15.75" customHeight="1">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
@@ -5775,7 +5912,7 @@
       <c r="U183" s="11"/>
       <c r="V183" s="11"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:22" ht="15.75" customHeight="1">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
@@ -5799,7 +5936,7 @@
       <c r="U184" s="11"/>
       <c r="V184" s="11"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:22" ht="15.75" customHeight="1">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -5823,7 +5960,7 @@
       <c r="U185" s="11"/>
       <c r="V185" s="11"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:22" ht="15.75" customHeight="1">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
@@ -5847,7 +5984,7 @@
       <c r="U186" s="11"/>
       <c r="V186" s="11"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:22" ht="15.75" customHeight="1">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
@@ -5871,7 +6008,7 @@
       <c r="U187" s="11"/>
       <c r="V187" s="11"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:22" ht="15.75" customHeight="1">
       <c r="A188" s="8"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -5895,7 +6032,7 @@
       <c r="U188" s="11"/>
       <c r="V188" s="11"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:22" ht="15.75" customHeight="1">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
@@ -5919,7 +6056,7 @@
       <c r="U189" s="11"/>
       <c r="V189" s="11"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:22" ht="15.75" customHeight="1">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -5943,7 +6080,7 @@
       <c r="U190" s="11"/>
       <c r="V190" s="11"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:22" ht="15.75" customHeight="1">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -5967,7 +6104,7 @@
       <c r="U191" s="11"/>
       <c r="V191" s="11"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:22" ht="15.75" customHeight="1">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -5991,7 +6128,7 @@
       <c r="U192" s="11"/>
       <c r="V192" s="11"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:22" ht="15.75" customHeight="1">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -6015,7 +6152,7 @@
       <c r="U193" s="11"/>
       <c r="V193" s="11"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:22" ht="15.75" customHeight="1">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -6039,7 +6176,7 @@
       <c r="U194" s="11"/>
       <c r="V194" s="11"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:22" ht="15.75" customHeight="1">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -6063,7 +6200,7 @@
       <c r="U195" s="11"/>
       <c r="V195" s="11"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:22" ht="15.75" customHeight="1">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -6087,7 +6224,7 @@
       <c r="U196" s="11"/>
       <c r="V196" s="11"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:22" ht="15.75" customHeight="1">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -6111,7 +6248,7 @@
       <c r="U197" s="11"/>
       <c r="V197" s="11"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:22" ht="15.75" customHeight="1">
       <c r="A198" s="8"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -6135,7 +6272,7 @@
       <c r="U198" s="11"/>
       <c r="V198" s="11"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:22" ht="15.75" customHeight="1">
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -6159,7 +6296,7 @@
       <c r="U199" s="11"/>
       <c r="V199" s="11"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:22" ht="15.75" customHeight="1">
       <c r="A200" s="8"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -6183,7 +6320,7 @@
       <c r="U200" s="11"/>
       <c r="V200" s="11"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:22" ht="15.75" customHeight="1">
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -6207,7 +6344,7 @@
       <c r="U201" s="11"/>
       <c r="V201" s="11"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:22" ht="15.75" customHeight="1">
       <c r="A202" s="8"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -6231,7 +6368,7 @@
       <c r="U202" s="11"/>
       <c r="V202" s="11"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:22" ht="15.75" customHeight="1">
       <c r="A203" s="8"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -6255,7 +6392,7 @@
       <c r="U203" s="11"/>
       <c r="V203" s="11"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:22" ht="15.75" customHeight="1">
       <c r="A204" s="8"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -6279,7 +6416,7 @@
       <c r="U204" s="11"/>
       <c r="V204" s="11"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:22" ht="15.75" customHeight="1">
       <c r="A205" s="8"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -6303,7 +6440,7 @@
       <c r="U205" s="11"/>
       <c r="V205" s="11"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:22" ht="15.75" customHeight="1">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -6327,7 +6464,7 @@
       <c r="U206" s="11"/>
       <c r="V206" s="11"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:22" ht="15.75" customHeight="1">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -6351,7 +6488,7 @@
       <c r="U207" s="11"/>
       <c r="V207" s="11"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:22" ht="15.75" customHeight="1">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -6375,7 +6512,7 @@
       <c r="U208" s="11"/>
       <c r="V208" s="11"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:22" ht="15.75" customHeight="1">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -6399,7 +6536,7 @@
       <c r="U209" s="11"/>
       <c r="V209" s="11"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:22" ht="15.75" customHeight="1">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -6423,7 +6560,7 @@
       <c r="U210" s="11"/>
       <c r="V210" s="11"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:22" ht="15.75" customHeight="1">
       <c r="A211" s="8"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -6447,7 +6584,7 @@
       <c r="U211" s="11"/>
       <c r="V211" s="11"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:22" ht="15.75" customHeight="1">
       <c r="A212" s="8"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -6471,7 +6608,7 @@
       <c r="U212" s="11"/>
       <c r="V212" s="11"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:22" ht="15.75" customHeight="1">
       <c r="A213" s="8"/>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -6495,7 +6632,7 @@
       <c r="U213" s="11"/>
       <c r="V213" s="11"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:22" ht="15.75" customHeight="1">
       <c r="A214" s="8"/>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -6519,7 +6656,7 @@
       <c r="U214" s="11"/>
       <c r="V214" s="11"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:22" ht="15.75" customHeight="1">
       <c r="A215" s="8"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -6543,7 +6680,7 @@
       <c r="U215" s="11"/>
       <c r="V215" s="11"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:22" ht="15.75" customHeight="1">
       <c r="A216" s="8"/>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -6567,7 +6704,7 @@
       <c r="U216" s="11"/>
       <c r="V216" s="11"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:22" ht="15.75" customHeight="1">
       <c r="A217" s="8"/>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -6591,7 +6728,7 @@
       <c r="U217" s="11"/>
       <c r="V217" s="11"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:22" ht="15.75" customHeight="1">
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -6615,7 +6752,7 @@
       <c r="U218" s="11"/>
       <c r="V218" s="11"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:22" ht="15.75" customHeight="1">
       <c r="A219" s="8"/>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -6639,7 +6776,7 @@
       <c r="U219" s="11"/>
       <c r="V219" s="11"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:22" ht="15.75" customHeight="1">
       <c r="A220" s="18"/>
       <c r="B220" s="18"/>
       <c r="C220" s="18"/>
@@ -6663,7 +6800,7 @@
       <c r="U220" s="11"/>
       <c r="V220" s="11"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:22" ht="15.75" customHeight="1">
       <c r="A221" s="18"/>
       <c r="B221" s="18"/>
       <c r="C221" s="18"/>
@@ -6687,7 +6824,7 @@
       <c r="U221" s="11"/>
       <c r="V221" s="11"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:22" ht="15.75" customHeight="1">
       <c r="A222" s="18"/>
       <c r="B222" s="18"/>
       <c r="C222" s="18"/>
@@ -6711,7 +6848,7 @@
       <c r="U222" s="11"/>
       <c r="V222" s="11"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:22" ht="15.75" customHeight="1">
       <c r="A223" s="18"/>
       <c r="B223" s="18"/>
       <c r="C223" s="18"/>
@@ -6735,3900 +6872,3899 @@
       <c r="U223" s="11"/>
       <c r="V223" s="11"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:22" ht="15.75" customHeight="1">
       <c r="T224" s="11"/>
       <c r="U224" s="11"/>
       <c r="V224" s="11"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="20:22" ht="15.75" customHeight="1">
       <c r="T225" s="11"/>
       <c r="U225" s="11"/>
       <c r="V225" s="11"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="20:22" ht="15.75" customHeight="1">
       <c r="T226" s="11"/>
       <c r="U226" s="11"/>
       <c r="V226" s="11"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="20:22" ht="15.75" customHeight="1">
       <c r="T227" s="11"/>
       <c r="U227" s="11"/>
       <c r="V227" s="11"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="20:22" ht="15.75" customHeight="1">
       <c r="T228" s="11"/>
       <c r="U228" s="11"/>
       <c r="V228" s="11"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="20:22" ht="15.75" customHeight="1">
       <c r="T229" s="11"/>
       <c r="U229" s="11"/>
       <c r="V229" s="11"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="20:22" ht="15.75" customHeight="1">
       <c r="T230" s="11"/>
       <c r="U230" s="11"/>
       <c r="V230" s="11"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="20:22" ht="15.75" customHeight="1">
       <c r="T231" s="11"/>
       <c r="U231" s="11"/>
       <c r="V231" s="11"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="20:22" ht="15.75" customHeight="1">
       <c r="T232" s="11"/>
       <c r="U232" s="11"/>
       <c r="V232" s="11"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="20:22" ht="15.75" customHeight="1">
       <c r="T233" s="11"/>
       <c r="U233" s="11"/>
       <c r="V233" s="11"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="20:22" ht="15.75" customHeight="1">
       <c r="T234" s="11"/>
       <c r="U234" s="11"/>
       <c r="V234" s="11"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="20:22" ht="15.75" customHeight="1">
       <c r="T235" s="11"/>
       <c r="U235" s="11"/>
       <c r="V235" s="11"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="20:22" ht="15.75" customHeight="1">
       <c r="T236" s="11"/>
       <c r="U236" s="11"/>
       <c r="V236" s="11"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="20:22" ht="15.75" customHeight="1">
       <c r="T237" s="11"/>
       <c r="U237" s="11"/>
       <c r="V237" s="11"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="20:22" ht="15.75" customHeight="1">
       <c r="T238" s="11"/>
       <c r="U238" s="11"/>
       <c r="V238" s="11"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="20:22" ht="15.75" customHeight="1">
       <c r="T239" s="11"/>
       <c r="U239" s="11"/>
       <c r="V239" s="11"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="20:22" ht="15.75" customHeight="1">
       <c r="T240" s="11"/>
       <c r="U240" s="11"/>
       <c r="V240" s="11"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="20:22" ht="15.75" customHeight="1">
       <c r="T241" s="11"/>
       <c r="U241" s="11"/>
       <c r="V241" s="11"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="20:22" ht="15.75" customHeight="1">
       <c r="T242" s="11"/>
       <c r="U242" s="11"/>
       <c r="V242" s="11"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="20:22" ht="15.75" customHeight="1">
       <c r="T243" s="11"/>
       <c r="U243" s="11"/>
       <c r="V243" s="11"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="20:22" ht="15.75" customHeight="1">
       <c r="T244" s="11"/>
       <c r="U244" s="11"/>
       <c r="V244" s="11"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="20:22" ht="15.75" customHeight="1">
       <c r="T245" s="11"/>
       <c r="U245" s="11"/>
       <c r="V245" s="11"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="20:22" ht="15.75" customHeight="1">
       <c r="T246" s="11"/>
       <c r="U246" s="11"/>
       <c r="V246" s="11"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="20:22" ht="15.75" customHeight="1">
       <c r="T247" s="11"/>
       <c r="U247" s="11"/>
       <c r="V247" s="11"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="20:22" ht="15.75" customHeight="1">
       <c r="T248" s="11"/>
       <c r="U248" s="11"/>
       <c r="V248" s="11"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="20:22" ht="15.75" customHeight="1">
       <c r="T249" s="11"/>
       <c r="U249" s="11"/>
       <c r="V249" s="11"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="20:22" ht="15.75" customHeight="1">
       <c r="T250" s="11"/>
       <c r="U250" s="11"/>
       <c r="V250" s="11"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="20:22" ht="15.75" customHeight="1">
       <c r="T251" s="11"/>
       <c r="U251" s="11"/>
       <c r="V251" s="11"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="20:22" ht="15.75" customHeight="1">
       <c r="T252" s="11"/>
       <c r="U252" s="11"/>
       <c r="V252" s="11"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="20:22" ht="15.75" customHeight="1">
       <c r="T253" s="11"/>
       <c r="U253" s="11"/>
       <c r="V253" s="11"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="20:22" ht="15.75" customHeight="1">
       <c r="T254" s="11"/>
       <c r="U254" s="11"/>
       <c r="V254" s="11"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="20:22" ht="15.75" customHeight="1">
       <c r="T255" s="11"/>
       <c r="U255" s="11"/>
       <c r="V255" s="11"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="20:22" ht="15.75" customHeight="1">
       <c r="T256" s="11"/>
       <c r="U256" s="11"/>
       <c r="V256" s="11"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="20:22" ht="15.75" customHeight="1">
       <c r="T257" s="11"/>
       <c r="U257" s="11"/>
       <c r="V257" s="11"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="20:22" ht="15.75" customHeight="1">
       <c r="T258" s="11"/>
       <c r="U258" s="11"/>
       <c r="V258" s="11"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="20:22" ht="15.75" customHeight="1">
       <c r="T259" s="11"/>
       <c r="U259" s="11"/>
       <c r="V259" s="11"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="20:22" ht="15.75" customHeight="1">
       <c r="T260" s="11"/>
       <c r="U260" s="11"/>
       <c r="V260" s="11"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="20:22" ht="15.75" customHeight="1">
       <c r="T261" s="11"/>
       <c r="U261" s="11"/>
       <c r="V261" s="11"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="20:22" ht="15.75" customHeight="1">
       <c r="T262" s="11"/>
       <c r="U262" s="11"/>
       <c r="V262" s="11"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="20:22" ht="15.75" customHeight="1">
       <c r="T263" s="11"/>
       <c r="U263" s="11"/>
       <c r="V263" s="11"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="20:22" ht="15.75" customHeight="1">
       <c r="T264" s="11"/>
       <c r="U264" s="11"/>
       <c r="V264" s="11"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="20:22" ht="15.75" customHeight="1">
       <c r="T265" s="11"/>
       <c r="U265" s="11"/>
       <c r="V265" s="11"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="20:22" ht="15.75" customHeight="1">
       <c r="T266" s="11"/>
       <c r="U266" s="11"/>
       <c r="V266" s="11"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="20:22" ht="15.75" customHeight="1">
       <c r="T267" s="11"/>
       <c r="U267" s="11"/>
       <c r="V267" s="11"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="20:22" ht="15.75" customHeight="1">
       <c r="T268" s="11"/>
       <c r="U268" s="11"/>
       <c r="V268" s="11"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="20:22" ht="15.75" customHeight="1">
       <c r="T269" s="11"/>
       <c r="U269" s="11"/>
       <c r="V269" s="11"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="20:22" ht="15.75" customHeight="1">
       <c r="T270" s="11"/>
       <c r="U270" s="11"/>
       <c r="V270" s="11"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="20:22" ht="15.75" customHeight="1">
       <c r="T271" s="11"/>
       <c r="U271" s="11"/>
       <c r="V271" s="11"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="20:22" ht="15.75" customHeight="1">
       <c r="T272" s="11"/>
       <c r="U272" s="11"/>
       <c r="V272" s="11"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="20:22" ht="15.75" customHeight="1">
       <c r="T273" s="11"/>
       <c r="U273" s="11"/>
       <c r="V273" s="11"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="20:22" ht="15.75" customHeight="1">
       <c r="T274" s="11"/>
       <c r="U274" s="11"/>
       <c r="V274" s="11"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="20:22" ht="15.75" customHeight="1">
       <c r="T275" s="11"/>
       <c r="U275" s="11"/>
       <c r="V275" s="11"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="20:22" ht="15.75" customHeight="1">
       <c r="T276" s="11"/>
       <c r="U276" s="11"/>
       <c r="V276" s="11"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="20:22" ht="15.75" customHeight="1">
       <c r="T277" s="11"/>
       <c r="U277" s="11"/>
       <c r="V277" s="11"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="20:22" ht="15.75" customHeight="1">
       <c r="T278" s="11"/>
       <c r="U278" s="11"/>
       <c r="V278" s="11"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="20:22" ht="15.75" customHeight="1">
       <c r="T279" s="11"/>
       <c r="U279" s="11"/>
       <c r="V279" s="11"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="20:22" ht="15.75" customHeight="1">
       <c r="T280" s="11"/>
       <c r="U280" s="11"/>
       <c r="V280" s="11"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="20:22" ht="15.75" customHeight="1">
       <c r="T281" s="11"/>
       <c r="U281" s="11"/>
       <c r="V281" s="11"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="20:22" ht="15.75" customHeight="1">
       <c r="T282" s="11"/>
       <c r="U282" s="11"/>
       <c r="V282" s="11"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="20:22" ht="15.75" customHeight="1">
       <c r="T283" s="11"/>
       <c r="U283" s="11"/>
       <c r="V283" s="11"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="20:22" ht="15.75" customHeight="1">
       <c r="T284" s="11"/>
       <c r="U284" s="11"/>
       <c r="V284" s="11"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="20:22" ht="15.75" customHeight="1">
       <c r="T285" s="11"/>
       <c r="U285" s="11"/>
       <c r="V285" s="11"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="20:22" ht="15.75" customHeight="1">
       <c r="T286" s="11"/>
       <c r="U286" s="11"/>
       <c r="V286" s="11"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="20:22" ht="15.75" customHeight="1">
       <c r="T287" s="11"/>
       <c r="U287" s="11"/>
       <c r="V287" s="11"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="20:22" ht="15.75" customHeight="1">
       <c r="T288" s="11"/>
       <c r="U288" s="11"/>
       <c r="V288" s="11"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="20:22" ht="15.75" customHeight="1">
       <c r="T289" s="11"/>
       <c r="U289" s="11"/>
       <c r="V289" s="11"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="20:22" ht="15.75" customHeight="1">
       <c r="T290" s="11"/>
       <c r="U290" s="11"/>
       <c r="V290" s="11"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="20:22" ht="15.75" customHeight="1">
       <c r="T291" s="11"/>
       <c r="U291" s="11"/>
       <c r="V291" s="11"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="20:22" ht="15.75" customHeight="1">
       <c r="T292" s="11"/>
       <c r="U292" s="11"/>
       <c r="V292" s="11"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="20:22" ht="15.75" customHeight="1">
       <c r="T293" s="11"/>
       <c r="U293" s="11"/>
       <c r="V293" s="11"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="20:22" ht="15.75" customHeight="1">
       <c r="T294" s="11"/>
       <c r="U294" s="11"/>
       <c r="V294" s="11"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="20:22" ht="15.75" customHeight="1">
       <c r="T295" s="11"/>
       <c r="U295" s="11"/>
       <c r="V295" s="11"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="20:22" ht="15.75" customHeight="1">
       <c r="T296" s="11"/>
       <c r="U296" s="11"/>
       <c r="V296" s="11"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="20:22" ht="15.75" customHeight="1">
       <c r="T297" s="11"/>
       <c r="U297" s="11"/>
       <c r="V297" s="11"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="20:22" ht="15.75" customHeight="1">
       <c r="T298" s="11"/>
       <c r="U298" s="11"/>
       <c r="V298" s="11"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="20:22" ht="15.75" customHeight="1">
       <c r="T299" s="11"/>
       <c r="U299" s="11"/>
       <c r="V299" s="11"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="20:22" ht="15.75" customHeight="1">
       <c r="T300" s="11"/>
       <c r="U300" s="11"/>
       <c r="V300" s="11"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="20:22" ht="15.75" customHeight="1">
       <c r="T301" s="11"/>
       <c r="U301" s="11"/>
       <c r="V301" s="11"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="20:22" ht="15.75" customHeight="1">
       <c r="T302" s="11"/>
       <c r="U302" s="11"/>
       <c r="V302" s="11"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="20:22" ht="15.75" customHeight="1">
       <c r="T303" s="11"/>
       <c r="U303" s="11"/>
       <c r="V303" s="11"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="20:22" ht="15.75" customHeight="1">
       <c r="T304" s="11"/>
       <c r="U304" s="11"/>
       <c r="V304" s="11"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="20:22" ht="15.75" customHeight="1">
       <c r="T305" s="11"/>
       <c r="U305" s="11"/>
       <c r="V305" s="11"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="20:22" ht="15.75" customHeight="1">
       <c r="T306" s="11"/>
       <c r="U306" s="11"/>
       <c r="V306" s="11"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="20:22" ht="15.75" customHeight="1">
       <c r="T307" s="11"/>
       <c r="U307" s="11"/>
       <c r="V307" s="11"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="20:22" ht="15.75" customHeight="1">
       <c r="T308" s="11"/>
       <c r="U308" s="11"/>
       <c r="V308" s="11"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="20:22" ht="15.75" customHeight="1">
       <c r="T309" s="11"/>
       <c r="U309" s="11"/>
       <c r="V309" s="11"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="20:22" ht="15.75" customHeight="1">
       <c r="T310" s="11"/>
       <c r="U310" s="11"/>
       <c r="V310" s="11"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="20:22" ht="15.75" customHeight="1">
       <c r="T311" s="11"/>
       <c r="U311" s="11"/>
       <c r="V311" s="11"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="20:22" ht="15.75" customHeight="1">
       <c r="T312" s="11"/>
       <c r="U312" s="11"/>
       <c r="V312" s="11"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="20:22" ht="15.75" customHeight="1">
       <c r="T313" s="11"/>
       <c r="U313" s="11"/>
       <c r="V313" s="11"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="20:22" ht="15.75" customHeight="1">
       <c r="T314" s="11"/>
       <c r="U314" s="11"/>
       <c r="V314" s="11"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="20:22" ht="15.75" customHeight="1">
       <c r="T315" s="11"/>
       <c r="U315" s="11"/>
       <c r="V315" s="11"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="20:22" ht="15.75" customHeight="1">
       <c r="T316" s="11"/>
       <c r="U316" s="11"/>
       <c r="V316" s="11"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="20:22" ht="15.75" customHeight="1">
       <c r="T317" s="11"/>
       <c r="U317" s="11"/>
       <c r="V317" s="11"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="20:22" ht="15.75" customHeight="1">
       <c r="T318" s="11"/>
       <c r="U318" s="11"/>
       <c r="V318" s="11"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="20:22" ht="15.75" customHeight="1">
       <c r="T319" s="11"/>
       <c r="U319" s="11"/>
       <c r="V319" s="11"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="20:22" ht="15.75" customHeight="1">
       <c r="T320" s="11"/>
       <c r="U320" s="11"/>
       <c r="V320" s="11"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="20:22" ht="15.75" customHeight="1">
       <c r="T321" s="11"/>
       <c r="U321" s="11"/>
       <c r="V321" s="11"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="20:22" ht="15.75" customHeight="1">
       <c r="T322" s="11"/>
       <c r="U322" s="11"/>
       <c r="V322" s="11"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="20:22" ht="15.75" customHeight="1">
       <c r="T323" s="11"/>
       <c r="U323" s="11"/>
       <c r="V323" s="11"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="20:22" ht="15.75" customHeight="1">
       <c r="T324" s="11"/>
       <c r="U324" s="11"/>
       <c r="V324" s="11"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="20:22" ht="15.75" customHeight="1">
       <c r="T325" s="11"/>
       <c r="U325" s="11"/>
       <c r="V325" s="11"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="20:22" ht="15.75" customHeight="1">
       <c r="T326" s="11"/>
       <c r="U326" s="11"/>
       <c r="V326" s="11"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="20:22" ht="15.75" customHeight="1">
       <c r="T327" s="11"/>
       <c r="U327" s="11"/>
       <c r="V327" s="11"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="20:22" ht="15.75" customHeight="1">
       <c r="T328" s="11"/>
       <c r="U328" s="11"/>
       <c r="V328" s="11"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="20:22" ht="15.75" customHeight="1">
       <c r="T329" s="11"/>
       <c r="U329" s="11"/>
       <c r="V329" s="11"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="20:22" ht="15.75" customHeight="1">
       <c r="T330" s="11"/>
       <c r="U330" s="11"/>
       <c r="V330" s="11"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="20:22" ht="15.75" customHeight="1">
       <c r="T331" s="11"/>
       <c r="U331" s="11"/>
       <c r="V331" s="11"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="20:22" ht="15.75" customHeight="1">
       <c r="T332" s="11"/>
       <c r="U332" s="11"/>
       <c r="V332" s="11"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="20:22" ht="15.75" customHeight="1">
       <c r="T333" s="11"/>
       <c r="U333" s="11"/>
       <c r="V333" s="11"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="20:22" ht="15.75" customHeight="1">
       <c r="T334" s="11"/>
       <c r="U334" s="11"/>
       <c r="V334" s="11"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="20:22" ht="15.75" customHeight="1">
       <c r="T335" s="11"/>
       <c r="U335" s="11"/>
       <c r="V335" s="11"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="20:22" ht="15.75" customHeight="1">
       <c r="T336" s="11"/>
       <c r="U336" s="11"/>
       <c r="V336" s="11"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="20:22" ht="15.75" customHeight="1">
       <c r="T337" s="11"/>
       <c r="U337" s="11"/>
       <c r="V337" s="11"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="20:22" ht="15.75" customHeight="1">
       <c r="T338" s="11"/>
       <c r="U338" s="11"/>
       <c r="V338" s="11"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="20:22" ht="15.75" customHeight="1">
       <c r="T339" s="11"/>
       <c r="U339" s="11"/>
       <c r="V339" s="11"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="20:22" ht="15.75" customHeight="1">
       <c r="T340" s="11"/>
       <c r="U340" s="11"/>
       <c r="V340" s="11"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="20:22" ht="15.75" customHeight="1">
       <c r="T341" s="11"/>
       <c r="U341" s="11"/>
       <c r="V341" s="11"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="20:22" ht="15.75" customHeight="1">
       <c r="T342" s="11"/>
       <c r="U342" s="11"/>
       <c r="V342" s="11"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="20:22" ht="15.75" customHeight="1">
       <c r="T343" s="11"/>
       <c r="U343" s="11"/>
       <c r="V343" s="11"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="20:22" ht="15.75" customHeight="1">
       <c r="T344" s="11"/>
       <c r="U344" s="11"/>
       <c r="V344" s="11"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="20:22" ht="15.75" customHeight="1">
       <c r="T345" s="11"/>
       <c r="U345" s="11"/>
       <c r="V345" s="11"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="20:22" ht="15.75" customHeight="1">
       <c r="T346" s="11"/>
       <c r="U346" s="11"/>
       <c r="V346" s="11"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="20:22" ht="15.75" customHeight="1">
       <c r="T347" s="11"/>
       <c r="U347" s="11"/>
       <c r="V347" s="11"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="20:22" ht="15.75" customHeight="1">
       <c r="T348" s="11"/>
       <c r="U348" s="11"/>
       <c r="V348" s="11"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="20:22" ht="15.75" customHeight="1">
       <c r="T349" s="11"/>
       <c r="U349" s="11"/>
       <c r="V349" s="11"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="20:22" ht="15.75" customHeight="1">
       <c r="T350" s="11"/>
       <c r="U350" s="11"/>
       <c r="V350" s="11"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="20:22" ht="15.75" customHeight="1">
       <c r="T351" s="11"/>
       <c r="U351" s="11"/>
       <c r="V351" s="11"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="20:22" ht="15.75" customHeight="1">
       <c r="T352" s="11"/>
       <c r="U352" s="11"/>
       <c r="V352" s="11"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="20:22" ht="15.75" customHeight="1">
       <c r="T353" s="11"/>
       <c r="U353" s="11"/>
       <c r="V353" s="11"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="20:22" ht="15.75" customHeight="1">
       <c r="T354" s="11"/>
       <c r="U354" s="11"/>
       <c r="V354" s="11"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="20:22" ht="15.75" customHeight="1">
       <c r="T355" s="11"/>
       <c r="U355" s="11"/>
       <c r="V355" s="11"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="20:22" ht="15.75" customHeight="1">
       <c r="T356" s="11"/>
       <c r="U356" s="11"/>
       <c r="V356" s="11"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="20:22" ht="15.75" customHeight="1">
       <c r="T357" s="11"/>
       <c r="U357" s="11"/>
       <c r="V357" s="11"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="20:22" ht="15.75" customHeight="1">
       <c r="T358" s="11"/>
       <c r="U358" s="11"/>
       <c r="V358" s="11"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="20:22" ht="15.75" customHeight="1">
       <c r="T359" s="11"/>
       <c r="U359" s="11"/>
       <c r="V359" s="11"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="20:22" ht="15.75" customHeight="1">
       <c r="T360" s="11"/>
       <c r="U360" s="11"/>
       <c r="V360" s="11"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="20:22" ht="15.75" customHeight="1">
       <c r="T361" s="11"/>
       <c r="U361" s="11"/>
       <c r="V361" s="11"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="20:22" ht="15.75" customHeight="1">
       <c r="T362" s="11"/>
       <c r="U362" s="11"/>
       <c r="V362" s="11"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="20:22" ht="15.75" customHeight="1">
       <c r="T363" s="11"/>
       <c r="U363" s="11"/>
       <c r="V363" s="11"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="20:22" ht="15.75" customHeight="1">
       <c r="T364" s="11"/>
       <c r="U364" s="11"/>
       <c r="V364" s="11"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="20:22" ht="15.75" customHeight="1">
       <c r="T365" s="11"/>
       <c r="U365" s="11"/>
       <c r="V365" s="11"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="20:22" ht="15.75" customHeight="1">
       <c r="T366" s="11"/>
       <c r="U366" s="11"/>
       <c r="V366" s="11"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="20:22" ht="15.75" customHeight="1">
       <c r="T367" s="11"/>
       <c r="U367" s="11"/>
       <c r="V367" s="11"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="20:22" ht="15.75" customHeight="1">
       <c r="T368" s="11"/>
       <c r="U368" s="11"/>
       <c r="V368" s="11"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="20:22" ht="15.75" customHeight="1">
       <c r="T369" s="11"/>
       <c r="U369" s="11"/>
       <c r="V369" s="11"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="20:22" ht="15.75" customHeight="1">
       <c r="T370" s="11"/>
       <c r="U370" s="11"/>
       <c r="V370" s="11"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="20:22" ht="15.75" customHeight="1">
       <c r="T371" s="11"/>
       <c r="U371" s="11"/>
       <c r="V371" s="11"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="20:22" ht="15.75" customHeight="1">
       <c r="T372" s="11"/>
       <c r="U372" s="11"/>
       <c r="V372" s="11"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="20:22" ht="15.75" customHeight="1">
       <c r="T373" s="11"/>
       <c r="U373" s="11"/>
       <c r="V373" s="11"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="20:22" ht="15.75" customHeight="1">
       <c r="T374" s="11"/>
       <c r="U374" s="11"/>
       <c r="V374" s="11"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="20:22" ht="15.75" customHeight="1">
       <c r="T375" s="11"/>
       <c r="U375" s="11"/>
       <c r="V375" s="11"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="20:22" ht="15.75" customHeight="1">
       <c r="T376" s="11"/>
       <c r="U376" s="11"/>
       <c r="V376" s="11"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="20:22" ht="15.75" customHeight="1">
       <c r="T377" s="11"/>
       <c r="U377" s="11"/>
       <c r="V377" s="11"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="20:22" ht="15.75" customHeight="1">
       <c r="T378" s="11"/>
       <c r="U378" s="11"/>
       <c r="V378" s="11"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="20:22" ht="15.75" customHeight="1">
       <c r="T379" s="11"/>
       <c r="U379" s="11"/>
       <c r="V379" s="11"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="20:22" ht="15.75" customHeight="1">
       <c r="T380" s="11"/>
       <c r="U380" s="11"/>
       <c r="V380" s="11"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="20:22" ht="15.75" customHeight="1">
       <c r="T381" s="11"/>
       <c r="U381" s="11"/>
       <c r="V381" s="11"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="20:22" ht="15.75" customHeight="1">
       <c r="T382" s="11"/>
       <c r="U382" s="11"/>
       <c r="V382" s="11"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="20:22" ht="15.75" customHeight="1">
       <c r="T383" s="11"/>
       <c r="U383" s="11"/>
       <c r="V383" s="11"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="20:22" ht="15.75" customHeight="1">
       <c r="T384" s="11"/>
       <c r="U384" s="11"/>
       <c r="V384" s="11"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="20:22" ht="15.75" customHeight="1">
       <c r="T385" s="11"/>
       <c r="U385" s="11"/>
       <c r="V385" s="11"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="20:22" ht="15.75" customHeight="1">
       <c r="T386" s="11"/>
       <c r="U386" s="11"/>
       <c r="V386" s="11"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="20:22" ht="15.75" customHeight="1">
       <c r="T387" s="11"/>
       <c r="U387" s="11"/>
       <c r="V387" s="11"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="20:22" ht="15.75" customHeight="1">
       <c r="T388" s="11"/>
       <c r="U388" s="11"/>
       <c r="V388" s="11"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="20:22" ht="15.75" customHeight="1">
       <c r="T389" s="11"/>
       <c r="U389" s="11"/>
       <c r="V389" s="11"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="20:22" ht="15.75" customHeight="1">
       <c r="T390" s="11"/>
       <c r="U390" s="11"/>
       <c r="V390" s="11"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="20:22" ht="15.75" customHeight="1">
       <c r="T391" s="11"/>
       <c r="U391" s="11"/>
       <c r="V391" s="11"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="20:22" ht="15.75" customHeight="1">
       <c r="T392" s="11"/>
       <c r="U392" s="11"/>
       <c r="V392" s="11"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="20:22" ht="15.75" customHeight="1">
       <c r="T393" s="11"/>
       <c r="U393" s="11"/>
       <c r="V393" s="11"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="20:22" ht="15.75" customHeight="1">
       <c r="T394" s="11"/>
       <c r="U394" s="11"/>
       <c r="V394" s="11"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="20:22" ht="15.75" customHeight="1">
       <c r="T395" s="11"/>
       <c r="U395" s="11"/>
       <c r="V395" s="11"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="20:22" ht="15.75" customHeight="1">
       <c r="T396" s="11"/>
       <c r="U396" s="11"/>
       <c r="V396" s="11"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="20:22" ht="15.75" customHeight="1">
       <c r="T397" s="11"/>
       <c r="U397" s="11"/>
       <c r="V397" s="11"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="20:22" ht="15.75" customHeight="1">
       <c r="T398" s="11"/>
       <c r="U398" s="11"/>
       <c r="V398" s="11"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="20:22" ht="15.75" customHeight="1">
       <c r="T399" s="11"/>
       <c r="U399" s="11"/>
       <c r="V399" s="11"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="20:22" ht="15.75" customHeight="1">
       <c r="T400" s="11"/>
       <c r="U400" s="11"/>
       <c r="V400" s="11"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="20:22" ht="15.75" customHeight="1">
       <c r="T401" s="11"/>
       <c r="U401" s="11"/>
       <c r="V401" s="11"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="20:22" ht="15.75" customHeight="1">
       <c r="T402" s="11"/>
       <c r="U402" s="11"/>
       <c r="V402" s="11"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="20:22" ht="15.75" customHeight="1">
       <c r="T403" s="11"/>
       <c r="U403" s="11"/>
       <c r="V403" s="11"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="20:22" ht="15.75" customHeight="1">
       <c r="T404" s="11"/>
       <c r="U404" s="11"/>
       <c r="V404" s="11"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="20:22" ht="15.75" customHeight="1">
       <c r="T405" s="11"/>
       <c r="U405" s="11"/>
       <c r="V405" s="11"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="20:22" ht="15.75" customHeight="1">
       <c r="T406" s="11"/>
       <c r="U406" s="11"/>
       <c r="V406" s="11"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="20:22" ht="15.75" customHeight="1">
       <c r="T407" s="11"/>
       <c r="U407" s="11"/>
       <c r="V407" s="11"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="20:22" ht="15.75" customHeight="1">
       <c r="T408" s="11"/>
       <c r="U408" s="11"/>
       <c r="V408" s="11"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="20:22" ht="15.75" customHeight="1">
       <c r="T409" s="11"/>
       <c r="U409" s="11"/>
       <c r="V409" s="11"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="20:22" ht="15.75" customHeight="1">
       <c r="T410" s="11"/>
       <c r="U410" s="11"/>
       <c r="V410" s="11"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="20:22" ht="15.75" customHeight="1">
       <c r="T411" s="11"/>
       <c r="U411" s="11"/>
       <c r="V411" s="11"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="20:22" ht="15.75" customHeight="1">
       <c r="T412" s="11"/>
       <c r="U412" s="11"/>
       <c r="V412" s="11"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="20:22" ht="15.75" customHeight="1">
       <c r="T413" s="11"/>
       <c r="U413" s="11"/>
       <c r="V413" s="11"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="20:22" ht="15.75" customHeight="1">
       <c r="T414" s="11"/>
       <c r="U414" s="11"/>
       <c r="V414" s="11"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="20:22" ht="15.75" customHeight="1">
       <c r="T415" s="11"/>
       <c r="U415" s="11"/>
       <c r="V415" s="11"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="20:22" ht="15.75" customHeight="1">
       <c r="T416" s="11"/>
       <c r="U416" s="11"/>
       <c r="V416" s="11"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="20:22" ht="15.75" customHeight="1">
       <c r="T417" s="11"/>
       <c r="U417" s="11"/>
       <c r="V417" s="11"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="20:22" ht="15.75" customHeight="1">
       <c r="T418" s="11"/>
       <c r="U418" s="11"/>
       <c r="V418" s="11"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="20:22" ht="15.75" customHeight="1">
       <c r="T419" s="11"/>
       <c r="U419" s="11"/>
       <c r="V419" s="11"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="20:22" ht="15.75" customHeight="1">
       <c r="T420" s="11"/>
       <c r="U420" s="11"/>
       <c r="V420" s="11"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="20:22" ht="15.75" customHeight="1">
       <c r="T421" s="11"/>
       <c r="U421" s="11"/>
       <c r="V421" s="11"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="20:22" ht="15.75" customHeight="1">
       <c r="T422" s="11"/>
       <c r="U422" s="11"/>
       <c r="V422" s="11"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="20:22" ht="15.75" customHeight="1">
       <c r="T423" s="11"/>
       <c r="U423" s="11"/>
       <c r="V423" s="11"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="20:22" ht="15.75" customHeight="1">
       <c r="T424" s="11"/>
       <c r="U424" s="11"/>
       <c r="V424" s="11"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="20:22" ht="15.75" customHeight="1">
       <c r="T425" s="11"/>
       <c r="U425" s="11"/>
       <c r="V425" s="11"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="20:22" ht="15.75" customHeight="1">
       <c r="T426" s="11"/>
       <c r="U426" s="11"/>
       <c r="V426" s="11"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="20:22" ht="15.75" customHeight="1">
       <c r="T427" s="11"/>
       <c r="U427" s="11"/>
       <c r="V427" s="11"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="20:22" ht="15.75" customHeight="1">
       <c r="T428" s="11"/>
       <c r="U428" s="11"/>
       <c r="V428" s="11"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="20:22" ht="15.75" customHeight="1">
       <c r="T429" s="11"/>
       <c r="U429" s="11"/>
       <c r="V429" s="11"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="20:22" ht="15.75" customHeight="1">
       <c r="T430" s="11"/>
       <c r="U430" s="11"/>
       <c r="V430" s="11"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="20:22" ht="15.75" customHeight="1">
       <c r="T431" s="11"/>
       <c r="U431" s="11"/>
       <c r="V431" s="11"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="20:22" ht="15.75" customHeight="1">
       <c r="T432" s="11"/>
       <c r="U432" s="11"/>
       <c r="V432" s="11"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="20:22" ht="15.75" customHeight="1">
       <c r="T433" s="11"/>
       <c r="U433" s="11"/>
       <c r="V433" s="11"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="20:22" ht="15.75" customHeight="1">
       <c r="T434" s="11"/>
       <c r="U434" s="11"/>
       <c r="V434" s="11"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="20:22" ht="15.75" customHeight="1">
       <c r="T435" s="11"/>
       <c r="U435" s="11"/>
       <c r="V435" s="11"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="20:22" ht="15.75" customHeight="1">
       <c r="T436" s="11"/>
       <c r="U436" s="11"/>
       <c r="V436" s="11"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="20:22" ht="15.75" customHeight="1">
       <c r="T437" s="11"/>
       <c r="U437" s="11"/>
       <c r="V437" s="11"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="20:22" ht="15.75" customHeight="1">
       <c r="T438" s="11"/>
       <c r="U438" s="11"/>
       <c r="V438" s="11"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="20:22" ht="15.75" customHeight="1">
       <c r="T439" s="11"/>
       <c r="U439" s="11"/>
       <c r="V439" s="11"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="20:22" ht="15.75" customHeight="1">
       <c r="T440" s="11"/>
       <c r="U440" s="11"/>
       <c r="V440" s="11"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="20:22" ht="15.75" customHeight="1">
       <c r="T441" s="11"/>
       <c r="U441" s="11"/>
       <c r="V441" s="11"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="20:22" ht="15.75" customHeight="1">
       <c r="T442" s="11"/>
       <c r="U442" s="11"/>
       <c r="V442" s="11"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="20:22" ht="15.75" customHeight="1">
       <c r="T443" s="11"/>
       <c r="U443" s="11"/>
       <c r="V443" s="11"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="20:22" ht="15.75" customHeight="1">
       <c r="T444" s="11"/>
       <c r="U444" s="11"/>
       <c r="V444" s="11"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="20:22" ht="15.75" customHeight="1">
       <c r="T445" s="11"/>
       <c r="U445" s="11"/>
       <c r="V445" s="11"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="20:22" ht="15.75" customHeight="1">
       <c r="T446" s="11"/>
       <c r="U446" s="11"/>
       <c r="V446" s="11"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="20:22" ht="15.75" customHeight="1">
       <c r="T447" s="11"/>
       <c r="U447" s="11"/>
       <c r="V447" s="11"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="20:22" ht="15.75" customHeight="1">
       <c r="T448" s="11"/>
       <c r="U448" s="11"/>
       <c r="V448" s="11"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="20:22" ht="15.75" customHeight="1">
       <c r="T449" s="11"/>
       <c r="U449" s="11"/>
       <c r="V449" s="11"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="20:22" ht="15.75" customHeight="1">
       <c r="T450" s="11"/>
       <c r="U450" s="11"/>
       <c r="V450" s="11"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="20:22" ht="15.75" customHeight="1">
       <c r="T451" s="11"/>
       <c r="U451" s="11"/>
       <c r="V451" s="11"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="20:22" ht="15.75" customHeight="1">
       <c r="T452" s="11"/>
       <c r="U452" s="11"/>
       <c r="V452" s="11"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="20:22" ht="15.75" customHeight="1">
       <c r="T453" s="11"/>
       <c r="U453" s="11"/>
       <c r="V453" s="11"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="20:22" ht="15.75" customHeight="1">
       <c r="T454" s="11"/>
       <c r="U454" s="11"/>
       <c r="V454" s="11"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="20:22" ht="15.75" customHeight="1">
       <c r="T455" s="11"/>
       <c r="U455" s="11"/>
       <c r="V455" s="11"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="20:22" ht="15.75" customHeight="1">
       <c r="T456" s="11"/>
       <c r="U456" s="11"/>
       <c r="V456" s="11"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="20:22" ht="15.75" customHeight="1">
       <c r="T457" s="11"/>
       <c r="U457" s="11"/>
       <c r="V457" s="11"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="20:22" ht="15.75" customHeight="1">
       <c r="T458" s="11"/>
       <c r="U458" s="11"/>
       <c r="V458" s="11"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="20:22" ht="15.75" customHeight="1">
       <c r="T459" s="11"/>
       <c r="U459" s="11"/>
       <c r="V459" s="11"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="20:22" ht="15.75" customHeight="1">
       <c r="T460" s="11"/>
       <c r="U460" s="11"/>
       <c r="V460" s="11"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="20:22" ht="15.75" customHeight="1">
       <c r="T461" s="11"/>
       <c r="U461" s="11"/>
       <c r="V461" s="11"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="20:22" ht="15.75" customHeight="1">
       <c r="T462" s="11"/>
       <c r="U462" s="11"/>
       <c r="V462" s="11"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="20:22" ht="15.75" customHeight="1">
       <c r="T463" s="11"/>
       <c r="U463" s="11"/>
       <c r="V463" s="11"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="20:22" ht="15.75" customHeight="1">
       <c r="T464" s="11"/>
       <c r="U464" s="11"/>
       <c r="V464" s="11"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="20:22" ht="15.75" customHeight="1">
       <c r="T465" s="11"/>
       <c r="U465" s="11"/>
       <c r="V465" s="11"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="20:22" ht="15.75" customHeight="1">
       <c r="T466" s="11"/>
       <c r="U466" s="11"/>
       <c r="V466" s="11"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="20:22" ht="15.75" customHeight="1">
       <c r="T467" s="11"/>
       <c r="U467" s="11"/>
       <c r="V467" s="11"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="20:22" ht="15.75" customHeight="1">
       <c r="T468" s="11"/>
       <c r="U468" s="11"/>
       <c r="V468" s="11"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="20:22" ht="15.75" customHeight="1">
       <c r="T469" s="11"/>
       <c r="U469" s="11"/>
       <c r="V469" s="11"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="20:22" ht="15.75" customHeight="1">
       <c r="T470" s="11"/>
       <c r="U470" s="11"/>
       <c r="V470" s="11"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="20:22" ht="15.75" customHeight="1">
       <c r="T471" s="11"/>
       <c r="U471" s="11"/>
       <c r="V471" s="11"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="20:22" ht="15.75" customHeight="1">
       <c r="T472" s="11"/>
       <c r="U472" s="11"/>
       <c r="V472" s="11"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="20:22" ht="15.75" customHeight="1">
       <c r="T473" s="11"/>
       <c r="U473" s="11"/>
       <c r="V473" s="11"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="20:22" ht="15.75" customHeight="1">
       <c r="T474" s="11"/>
       <c r="U474" s="11"/>
       <c r="V474" s="11"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="20:22" ht="15.75" customHeight="1">
       <c r="T475" s="11"/>
       <c r="U475" s="11"/>
       <c r="V475" s="11"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="20:22" ht="15.75" customHeight="1">
       <c r="T476" s="11"/>
       <c r="U476" s="11"/>
       <c r="V476" s="11"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="20:22" ht="15.75" customHeight="1">
       <c r="T477" s="11"/>
       <c r="U477" s="11"/>
       <c r="V477" s="11"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="20:22" ht="15.75" customHeight="1">
       <c r="T478" s="11"/>
       <c r="U478" s="11"/>
       <c r="V478" s="11"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="20:22" ht="15.75" customHeight="1">
       <c r="T479" s="11"/>
       <c r="U479" s="11"/>
       <c r="V479" s="11"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="20:22" ht="15.75" customHeight="1">
       <c r="T480" s="11"/>
       <c r="U480" s="11"/>
       <c r="V480" s="11"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="20:22" ht="15.75" customHeight="1">
       <c r="T481" s="11"/>
       <c r="U481" s="11"/>
       <c r="V481" s="11"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="20:22" ht="15.75" customHeight="1">
       <c r="T482" s="11"/>
       <c r="U482" s="11"/>
       <c r="V482" s="11"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="20:22" ht="15.75" customHeight="1">
       <c r="T483" s="11"/>
       <c r="U483" s="11"/>
       <c r="V483" s="11"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="20:22" ht="15.75" customHeight="1">
       <c r="T484" s="11"/>
       <c r="U484" s="11"/>
       <c r="V484" s="11"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="20:22" ht="15.75" customHeight="1">
       <c r="T485" s="11"/>
       <c r="U485" s="11"/>
       <c r="V485" s="11"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="20:22" ht="15.75" customHeight="1">
       <c r="T486" s="11"/>
       <c r="U486" s="11"/>
       <c r="V486" s="11"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="20:22" ht="15.75" customHeight="1">
       <c r="T487" s="11"/>
       <c r="U487" s="11"/>
       <c r="V487" s="11"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="20:22" ht="15.75" customHeight="1">
       <c r="T488" s="11"/>
       <c r="U488" s="11"/>
       <c r="V488" s="11"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="20:22" ht="15.75" customHeight="1">
       <c r="T489" s="11"/>
       <c r="U489" s="11"/>
       <c r="V489" s="11"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="20:22" ht="15.75" customHeight="1">
       <c r="T490" s="11"/>
       <c r="U490" s="11"/>
       <c r="V490" s="11"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="20:22" ht="15.75" customHeight="1">
       <c r="T491" s="11"/>
       <c r="U491" s="11"/>
       <c r="V491" s="11"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="20:22" ht="15.75" customHeight="1">
       <c r="T492" s="11"/>
       <c r="U492" s="11"/>
       <c r="V492" s="11"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="20:22" ht="15.75" customHeight="1">
       <c r="T493" s="11"/>
       <c r="U493" s="11"/>
       <c r="V493" s="11"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="20:22" ht="15.75" customHeight="1">
       <c r="T494" s="11"/>
       <c r="U494" s="11"/>
       <c r="V494" s="11"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="20:22" ht="15.75" customHeight="1">
       <c r="T495" s="11"/>
       <c r="U495" s="11"/>
       <c r="V495" s="11"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="20:22" ht="15.75" customHeight="1">
       <c r="T496" s="11"/>
       <c r="U496" s="11"/>
       <c r="V496" s="11"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="20:22" ht="15.75" customHeight="1">
       <c r="T497" s="11"/>
       <c r="U497" s="11"/>
       <c r="V497" s="11"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="20:22" ht="15.75" customHeight="1">
       <c r="T498" s="11"/>
       <c r="U498" s="11"/>
       <c r="V498" s="11"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="20:22" ht="15.75" customHeight="1">
       <c r="T499" s="11"/>
       <c r="U499" s="11"/>
       <c r="V499" s="11"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="20:22" ht="15.75" customHeight="1">
       <c r="T500" s="11"/>
       <c r="U500" s="11"/>
       <c r="V500" s="11"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="20:22" ht="15.75" customHeight="1">
       <c r="T501" s="11"/>
       <c r="U501" s="11"/>
       <c r="V501" s="11"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="20:22" ht="15.75" customHeight="1">
       <c r="T502" s="11"/>
       <c r="U502" s="11"/>
       <c r="V502" s="11"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="20:22" ht="15.75" customHeight="1">
       <c r="T503" s="11"/>
       <c r="U503" s="11"/>
       <c r="V503" s="11"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="20:22" ht="15.75" customHeight="1">
       <c r="T504" s="11"/>
       <c r="U504" s="11"/>
       <c r="V504" s="11"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="20:22" ht="15.75" customHeight="1">
       <c r="T505" s="11"/>
       <c r="U505" s="11"/>
       <c r="V505" s="11"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="20:22" ht="15.75" customHeight="1">
       <c r="T506" s="11"/>
       <c r="U506" s="11"/>
       <c r="V506" s="11"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="20:22" ht="15.75" customHeight="1">
       <c r="T507" s="11"/>
       <c r="U507" s="11"/>
       <c r="V507" s="11"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="20:22" ht="15.75" customHeight="1">
       <c r="T508" s="11"/>
       <c r="U508" s="11"/>
       <c r="V508" s="11"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="20:22" ht="15.75" customHeight="1">
       <c r="T509" s="11"/>
       <c r="U509" s="11"/>
       <c r="V509" s="11"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="20:22" ht="15.75" customHeight="1">
       <c r="T510" s="11"/>
       <c r="U510" s="11"/>
       <c r="V510" s="11"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="20:22" ht="15.75" customHeight="1">
       <c r="T511" s="11"/>
       <c r="U511" s="11"/>
       <c r="V511" s="11"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="20:22" ht="15.75" customHeight="1">
       <c r="T512" s="11"/>
       <c r="U512" s="11"/>
       <c r="V512" s="11"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="20:22" ht="15.75" customHeight="1">
       <c r="T513" s="11"/>
       <c r="U513" s="11"/>
       <c r="V513" s="11"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="20:22" ht="15.75" customHeight="1">
       <c r="T514" s="11"/>
       <c r="U514" s="11"/>
       <c r="V514" s="11"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="20:22" ht="15.75" customHeight="1">
       <c r="T515" s="11"/>
       <c r="U515" s="11"/>
       <c r="V515" s="11"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="20:22" ht="15.75" customHeight="1">
       <c r="T516" s="11"/>
       <c r="U516" s="11"/>
       <c r="V516" s="11"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="20:22" ht="15.75" customHeight="1">
       <c r="T517" s="11"/>
       <c r="U517" s="11"/>
       <c r="V517" s="11"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="20:22" ht="15.75" customHeight="1">
       <c r="T518" s="11"/>
       <c r="U518" s="11"/>
       <c r="V518" s="11"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="20:22" ht="15.75" customHeight="1">
       <c r="T519" s="11"/>
       <c r="U519" s="11"/>
       <c r="V519" s="11"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="20:22" ht="15.75" customHeight="1">
       <c r="T520" s="11"/>
       <c r="U520" s="11"/>
       <c r="V520" s="11"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="20:22" ht="15.75" customHeight="1">
       <c r="T521" s="11"/>
       <c r="U521" s="11"/>
       <c r="V521" s="11"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="20:22" ht="15.75" customHeight="1">
       <c r="T522" s="11"/>
       <c r="U522" s="11"/>
       <c r="V522" s="11"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="20:22" ht="15.75" customHeight="1">
       <c r="T523" s="11"/>
       <c r="U523" s="11"/>
       <c r="V523" s="11"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="20:22" ht="15.75" customHeight="1">
       <c r="T524" s="11"/>
       <c r="U524" s="11"/>
       <c r="V524" s="11"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="20:22" ht="15.75" customHeight="1">
       <c r="T525" s="11"/>
       <c r="U525" s="11"/>
       <c r="V525" s="11"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="20:22" ht="15.75" customHeight="1">
       <c r="T526" s="11"/>
       <c r="U526" s="11"/>
       <c r="V526" s="11"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="20:22" ht="15.75" customHeight="1">
       <c r="T527" s="11"/>
       <c r="U527" s="11"/>
       <c r="V527" s="11"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="20:22" ht="15.75" customHeight="1">
       <c r="T528" s="11"/>
       <c r="U528" s="11"/>
       <c r="V528" s="11"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="20:22" ht="15.75" customHeight="1">
       <c r="T529" s="11"/>
       <c r="U529" s="11"/>
       <c r="V529" s="11"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="20:22" ht="15.75" customHeight="1">
       <c r="T530" s="11"/>
       <c r="U530" s="11"/>
       <c r="V530" s="11"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="20:22" ht="15.75" customHeight="1">
       <c r="T531" s="11"/>
       <c r="U531" s="11"/>
       <c r="V531" s="11"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="20:22" ht="15.75" customHeight="1">
       <c r="T532" s="11"/>
       <c r="U532" s="11"/>
       <c r="V532" s="11"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="20:22" ht="15.75" customHeight="1">
       <c r="T533" s="11"/>
       <c r="U533" s="11"/>
       <c r="V533" s="11"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="20:22" ht="15.75" customHeight="1">
       <c r="T534" s="11"/>
       <c r="U534" s="11"/>
       <c r="V534" s="11"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="20:22" ht="15.75" customHeight="1">
       <c r="T535" s="11"/>
       <c r="U535" s="11"/>
       <c r="V535" s="11"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="20:22" ht="15.75" customHeight="1">
       <c r="T536" s="11"/>
       <c r="U536" s="11"/>
       <c r="V536" s="11"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="20:22" ht="15.75" customHeight="1">
       <c r="T537" s="11"/>
       <c r="U537" s="11"/>
       <c r="V537" s="11"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="20:22" ht="15.75" customHeight="1">
       <c r="T538" s="11"/>
       <c r="U538" s="11"/>
       <c r="V538" s="11"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="20:22" ht="15.75" customHeight="1">
       <c r="T539" s="11"/>
       <c r="U539" s="11"/>
       <c r="V539" s="11"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="20:22" ht="15.75" customHeight="1">
       <c r="T540" s="11"/>
       <c r="U540" s="11"/>
       <c r="V540" s="11"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="20:22" ht="15.75" customHeight="1">
       <c r="T541" s="11"/>
       <c r="U541" s="11"/>
       <c r="V541" s="11"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="20:22" ht="15.75" customHeight="1">
       <c r="T542" s="11"/>
       <c r="U542" s="11"/>
       <c r="V542" s="11"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="20:22" ht="15.75" customHeight="1">
       <c r="T543" s="11"/>
       <c r="U543" s="11"/>
       <c r="V543" s="11"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="20:22" ht="15.75" customHeight="1">
       <c r="T544" s="11"/>
       <c r="U544" s="11"/>
       <c r="V544" s="11"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="20:22" ht="15.75" customHeight="1">
       <c r="T545" s="11"/>
       <c r="U545" s="11"/>
       <c r="V545" s="11"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="20:22" ht="15.75" customHeight="1">
       <c r="T546" s="11"/>
       <c r="U546" s="11"/>
       <c r="V546" s="11"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="20:22" ht="15.75" customHeight="1">
       <c r="T547" s="11"/>
       <c r="U547" s="11"/>
       <c r="V547" s="11"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="20:22" ht="15.75" customHeight="1">
       <c r="T548" s="11"/>
       <c r="U548" s="11"/>
       <c r="V548" s="11"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="20:22" ht="15.75" customHeight="1">
       <c r="T549" s="11"/>
       <c r="U549" s="11"/>
       <c r="V549" s="11"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="20:22" ht="15.75" customHeight="1">
       <c r="T550" s="11"/>
       <c r="U550" s="11"/>
       <c r="V550" s="11"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="20:22" ht="15.75" customHeight="1">
       <c r="T551" s="11"/>
       <c r="U551" s="11"/>
       <c r="V551" s="11"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="20:22" ht="15.75" customHeight="1">
       <c r="T552" s="11"/>
       <c r="U552" s="11"/>
       <c r="V552" s="11"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="20:22" ht="15.75" customHeight="1">
       <c r="T553" s="11"/>
       <c r="U553" s="11"/>
       <c r="V553" s="11"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="20:22" ht="15.75" customHeight="1">
       <c r="T554" s="11"/>
       <c r="U554" s="11"/>
       <c r="V554" s="11"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="20:22" ht="15.75" customHeight="1">
       <c r="T555" s="11"/>
       <c r="U555" s="11"/>
       <c r="V555" s="11"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="20:22" ht="15.75" customHeight="1">
       <c r="T556" s="11"/>
       <c r="U556" s="11"/>
       <c r="V556" s="11"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="20:22" ht="15.75" customHeight="1">
       <c r="T557" s="11"/>
       <c r="U557" s="11"/>
       <c r="V557" s="11"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="20:22" ht="15.75" customHeight="1">
       <c r="T558" s="11"/>
       <c r="U558" s="11"/>
       <c r="V558" s="11"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="20:22" ht="15.75" customHeight="1">
       <c r="T559" s="11"/>
       <c r="U559" s="11"/>
       <c r="V559" s="11"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="20:22" ht="15.75" customHeight="1">
       <c r="T560" s="11"/>
       <c r="U560" s="11"/>
       <c r="V560" s="11"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="20:22" ht="15.75" customHeight="1">
       <c r="T561" s="11"/>
       <c r="U561" s="11"/>
       <c r="V561" s="11"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="20:22" ht="15.75" customHeight="1">
       <c r="T562" s="11"/>
       <c r="U562" s="11"/>
       <c r="V562" s="11"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="20:22" ht="15.75" customHeight="1">
       <c r="T563" s="11"/>
       <c r="U563" s="11"/>
       <c r="V563" s="11"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="20:22" ht="15.75" customHeight="1">
       <c r="T564" s="11"/>
       <c r="U564" s="11"/>
       <c r="V564" s="11"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="20:22" ht="15.75" customHeight="1">
       <c r="T565" s="11"/>
       <c r="U565" s="11"/>
       <c r="V565" s="11"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="20:22" ht="15.75" customHeight="1">
       <c r="T566" s="11"/>
       <c r="U566" s="11"/>
       <c r="V566" s="11"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="20:22" ht="15.75" customHeight="1">
       <c r="T567" s="11"/>
       <c r="U567" s="11"/>
       <c r="V567" s="11"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="20:22" ht="15.75" customHeight="1">
       <c r="T568" s="11"/>
       <c r="U568" s="11"/>
       <c r="V568" s="11"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="20:22" ht="15.75" customHeight="1">
       <c r="T569" s="11"/>
       <c r="U569" s="11"/>
       <c r="V569" s="11"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="20:22" ht="15.75" customHeight="1">
       <c r="T570" s="11"/>
       <c r="U570" s="11"/>
       <c r="V570" s="11"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="20:22" ht="15.75" customHeight="1">
       <c r="T571" s="11"/>
       <c r="U571" s="11"/>
       <c r="V571" s="11"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="20:22" ht="15.75" customHeight="1">
       <c r="T572" s="11"/>
       <c r="U572" s="11"/>
       <c r="V572" s="11"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="20:22" ht="15.75" customHeight="1">
       <c r="T573" s="11"/>
       <c r="U573" s="11"/>
       <c r="V573" s="11"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="20:22" ht="15.75" customHeight="1">
       <c r="T574" s="11"/>
       <c r="U574" s="11"/>
       <c r="V574" s="11"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="20:22" ht="15.75" customHeight="1">
       <c r="T575" s="11"/>
       <c r="U575" s="11"/>
       <c r="V575" s="11"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="20:22" ht="15.75" customHeight="1">
       <c r="T576" s="11"/>
       <c r="U576" s="11"/>
       <c r="V576" s="11"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="20:22" ht="15.75" customHeight="1">
       <c r="T577" s="11"/>
       <c r="U577" s="11"/>
       <c r="V577" s="11"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="20:22" ht="15.75" customHeight="1">
       <c r="T578" s="11"/>
       <c r="U578" s="11"/>
       <c r="V578" s="11"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="20:22" ht="15.75" customHeight="1">
       <c r="T579" s="11"/>
       <c r="U579" s="11"/>
       <c r="V579" s="11"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="20:22" ht="15.75" customHeight="1">
       <c r="T580" s="11"/>
       <c r="U580" s="11"/>
       <c r="V580" s="11"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="20:22" ht="15.75" customHeight="1">
       <c r="T581" s="11"/>
       <c r="U581" s="11"/>
       <c r="V581" s="11"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="20:22" ht="15.75" customHeight="1">
       <c r="T582" s="11"/>
       <c r="U582" s="11"/>
       <c r="V582" s="11"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="20:22" ht="15.75" customHeight="1">
       <c r="T583" s="11"/>
       <c r="U583" s="11"/>
       <c r="V583" s="11"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="20:22" ht="15.75" customHeight="1">
       <c r="T584" s="11"/>
       <c r="U584" s="11"/>
       <c r="V584" s="11"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="20:22" ht="15.75" customHeight="1">
       <c r="T585" s="11"/>
       <c r="U585" s="11"/>
       <c r="V585" s="11"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="20:22" ht="15.75" customHeight="1">
       <c r="T586" s="11"/>
       <c r="U586" s="11"/>
       <c r="V586" s="11"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="20:22" ht="15.75" customHeight="1">
       <c r="T587" s="11"/>
       <c r="U587" s="11"/>
       <c r="V587" s="11"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="20:22" ht="15.75" customHeight="1">
       <c r="T588" s="11"/>
       <c r="U588" s="11"/>
       <c r="V588" s="11"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="20:22" ht="15.75" customHeight="1">
       <c r="T589" s="11"/>
       <c r="U589" s="11"/>
       <c r="V589" s="11"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="20:22" ht="15.75" customHeight="1">
       <c r="T590" s="11"/>
       <c r="U590" s="11"/>
       <c r="V590" s="11"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="20:22" ht="15.75" customHeight="1">
       <c r="T591" s="11"/>
       <c r="U591" s="11"/>
       <c r="V591" s="11"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="20:22" ht="15.75" customHeight="1">
       <c r="T592" s="11"/>
       <c r="U592" s="11"/>
       <c r="V592" s="11"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="20:22" ht="15.75" customHeight="1">
       <c r="T593" s="11"/>
       <c r="U593" s="11"/>
       <c r="V593" s="11"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="20:22" ht="15.75" customHeight="1">
       <c r="T594" s="11"/>
       <c r="U594" s="11"/>
       <c r="V594" s="11"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="20:22" ht="15.75" customHeight="1">
       <c r="T595" s="11"/>
       <c r="U595" s="11"/>
       <c r="V595" s="11"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="20:22" ht="15.75" customHeight="1">
       <c r="T596" s="11"/>
       <c r="U596" s="11"/>
       <c r="V596" s="11"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="20:22" ht="15.75" customHeight="1">
       <c r="T597" s="11"/>
       <c r="U597" s="11"/>
       <c r="V597" s="11"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="20:22" ht="15.75" customHeight="1">
       <c r="T598" s="11"/>
       <c r="U598" s="11"/>
       <c r="V598" s="11"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="20:22" ht="15.75" customHeight="1">
       <c r="T599" s="11"/>
       <c r="U599" s="11"/>
       <c r="V599" s="11"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="20:22" ht="15.75" customHeight="1">
       <c r="T600" s="11"/>
       <c r="U600" s="11"/>
       <c r="V600" s="11"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="20:22" ht="15.75" customHeight="1">
       <c r="T601" s="11"/>
       <c r="U601" s="11"/>
       <c r="V601" s="11"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="20:22" ht="15.75" customHeight="1">
       <c r="T602" s="11"/>
       <c r="U602" s="11"/>
       <c r="V602" s="11"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="20:22" ht="15.75" customHeight="1">
       <c r="T603" s="11"/>
       <c r="U603" s="11"/>
       <c r="V603" s="11"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="20:22" ht="15.75" customHeight="1">
       <c r="T604" s="11"/>
       <c r="U604" s="11"/>
       <c r="V604" s="11"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="20:22" ht="15.75" customHeight="1">
       <c r="T605" s="11"/>
       <c r="U605" s="11"/>
       <c r="V605" s="11"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="20:22" ht="15.75" customHeight="1">
       <c r="T606" s="11"/>
       <c r="U606" s="11"/>
       <c r="V606" s="11"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="20:22" ht="15.75" customHeight="1">
       <c r="T607" s="11"/>
       <c r="U607" s="11"/>
       <c r="V607" s="11"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="20:22" ht="15.75" customHeight="1">
       <c r="T608" s="11"/>
       <c r="U608" s="11"/>
       <c r="V608" s="11"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="20:22" ht="15.75" customHeight="1">
       <c r="T609" s="11"/>
       <c r="U609" s="11"/>
       <c r="V609" s="11"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="20:22" ht="15.75" customHeight="1">
       <c r="T610" s="11"/>
       <c r="U610" s="11"/>
       <c r="V610" s="11"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="20:22" ht="15.75" customHeight="1">
       <c r="T611" s="11"/>
       <c r="U611" s="11"/>
       <c r="V611" s="11"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="20:22" ht="15.75" customHeight="1">
       <c r="T612" s="11"/>
       <c r="U612" s="11"/>
       <c r="V612" s="11"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="20:22" ht="15.75" customHeight="1">
       <c r="T613" s="11"/>
       <c r="U613" s="11"/>
       <c r="V613" s="11"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="20:22" ht="15.75" customHeight="1">
       <c r="T614" s="11"/>
       <c r="U614" s="11"/>
       <c r="V614" s="11"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="20:22" ht="15.75" customHeight="1">
       <c r="T615" s="11"/>
       <c r="U615" s="11"/>
       <c r="V615" s="11"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="20:22" ht="15.75" customHeight="1">
       <c r="T616" s="11"/>
       <c r="U616" s="11"/>
       <c r="V616" s="11"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="20:22" ht="15.75" customHeight="1">
       <c r="T617" s="11"/>
       <c r="U617" s="11"/>
       <c r="V617" s="11"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="20:22" ht="15.75" customHeight="1">
       <c r="T618" s="11"/>
       <c r="U618" s="11"/>
       <c r="V618" s="11"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="20:22" ht="15.75" customHeight="1">
       <c r="T619" s="11"/>
       <c r="U619" s="11"/>
       <c r="V619" s="11"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="20:22" ht="15.75" customHeight="1">
       <c r="T620" s="11"/>
       <c r="U620" s="11"/>
       <c r="V620" s="11"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="20:22" ht="15.75" customHeight="1">
       <c r="T621" s="11"/>
       <c r="U621" s="11"/>
       <c r="V621" s="11"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="20:22" ht="15.75" customHeight="1">
       <c r="T622" s="11"/>
       <c r="U622" s="11"/>
       <c r="V622" s="11"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="20:22" ht="15.75" customHeight="1">
       <c r="T623" s="11"/>
       <c r="U623" s="11"/>
       <c r="V623" s="11"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="20:22" ht="15.75" customHeight="1">
       <c r="T624" s="11"/>
       <c r="U624" s="11"/>
       <c r="V624" s="11"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="20:22" ht="15.75" customHeight="1">
       <c r="T625" s="11"/>
       <c r="U625" s="11"/>
       <c r="V625" s="11"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="20:22" ht="15.75" customHeight="1">
       <c r="T626" s="11"/>
       <c r="U626" s="11"/>
       <c r="V626" s="11"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="20:22" ht="15.75" customHeight="1">
       <c r="T627" s="11"/>
       <c r="U627" s="11"/>
       <c r="V627" s="11"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="20:22" ht="15.75" customHeight="1">
       <c r="T628" s="11"/>
       <c r="U628" s="11"/>
       <c r="V628" s="11"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="20:22" ht="15.75" customHeight="1">
       <c r="T629" s="11"/>
       <c r="U629" s="11"/>
       <c r="V629" s="11"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="20:22" ht="15.75" customHeight="1">
       <c r="T630" s="11"/>
       <c r="U630" s="11"/>
       <c r="V630" s="11"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="20:22" ht="15.75" customHeight="1">
       <c r="T631" s="11"/>
       <c r="U631" s="11"/>
       <c r="V631" s="11"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="20:22" ht="15.75" customHeight="1">
       <c r="T632" s="11"/>
       <c r="U632" s="11"/>
       <c r="V632" s="11"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="20:22" ht="15.75" customHeight="1">
       <c r="T633" s="11"/>
       <c r="U633" s="11"/>
       <c r="V633" s="11"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="20:22" ht="15.75" customHeight="1">
       <c r="T634" s="11"/>
       <c r="U634" s="11"/>
       <c r="V634" s="11"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="20:22" ht="15.75" customHeight="1">
       <c r="T635" s="11"/>
       <c r="U635" s="11"/>
       <c r="V635" s="11"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="20:22" ht="15.75" customHeight="1">
       <c r="T636" s="11"/>
       <c r="U636" s="11"/>
       <c r="V636" s="11"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="20:22" ht="15.75" customHeight="1">
       <c r="T637" s="11"/>
       <c r="U637" s="11"/>
       <c r="V637" s="11"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="20:22" ht="15.75" customHeight="1">
       <c r="T638" s="11"/>
       <c r="U638" s="11"/>
       <c r="V638" s="11"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="20:22" ht="15.75" customHeight="1">
       <c r="T639" s="11"/>
       <c r="U639" s="11"/>
       <c r="V639" s="11"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="20:22" ht="15.75" customHeight="1">
       <c r="T640" s="11"/>
       <c r="U640" s="11"/>
       <c r="V640" s="11"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="20:22" ht="15.75" customHeight="1">
       <c r="T641" s="11"/>
       <c r="U641" s="11"/>
       <c r="V641" s="11"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="20:22" ht="15.75" customHeight="1">
       <c r="T642" s="11"/>
       <c r="U642" s="11"/>
       <c r="V642" s="11"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="20:22" ht="15.75" customHeight="1">
       <c r="T643" s="11"/>
       <c r="U643" s="11"/>
       <c r="V643" s="11"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="20:22" ht="15.75" customHeight="1">
       <c r="T644" s="11"/>
       <c r="U644" s="11"/>
       <c r="V644" s="11"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="20:22" ht="15.75" customHeight="1">
       <c r="T645" s="11"/>
       <c r="U645" s="11"/>
       <c r="V645" s="11"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="20:22" ht="15.75" customHeight="1">
       <c r="T646" s="11"/>
       <c r="U646" s="11"/>
       <c r="V646" s="11"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="20:22" ht="15.75" customHeight="1">
       <c r="T647" s="11"/>
       <c r="U647" s="11"/>
       <c r="V647" s="11"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="20:22" ht="15.75" customHeight="1">
       <c r="T648" s="11"/>
       <c r="U648" s="11"/>
       <c r="V648" s="11"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="20:22" ht="15.75" customHeight="1">
       <c r="T649" s="11"/>
       <c r="U649" s="11"/>
       <c r="V649" s="11"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="20:22" ht="15.75" customHeight="1">
       <c r="T650" s="11"/>
       <c r="U650" s="11"/>
       <c r="V650" s="11"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="20:22" ht="15.75" customHeight="1">
       <c r="T651" s="11"/>
       <c r="U651" s="11"/>
       <c r="V651" s="11"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="20:22" ht="15.75" customHeight="1">
       <c r="T652" s="11"/>
       <c r="U652" s="11"/>
       <c r="V652" s="11"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="20:22" ht="15.75" customHeight="1">
       <c r="T653" s="11"/>
       <c r="U653" s="11"/>
       <c r="V653" s="11"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="20:22" ht="15.75" customHeight="1">
       <c r="T654" s="11"/>
       <c r="U654" s="11"/>
       <c r="V654" s="11"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="20:22" ht="15.75" customHeight="1">
       <c r="T655" s="11"/>
       <c r="U655" s="11"/>
       <c r="V655" s="11"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="20:22" ht="15.75" customHeight="1">
       <c r="T656" s="11"/>
       <c r="U656" s="11"/>
       <c r="V656" s="11"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="20:22" ht="15.75" customHeight="1">
       <c r="T657" s="11"/>
       <c r="U657" s="11"/>
       <c r="V657" s="11"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="20:22" ht="15.75" customHeight="1">
       <c r="T658" s="11"/>
       <c r="U658" s="11"/>
       <c r="V658" s="11"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="20:22" ht="15.75" customHeight="1">
       <c r="T659" s="11"/>
       <c r="U659" s="11"/>
       <c r="V659" s="11"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="20:22" ht="15.75" customHeight="1">
       <c r="T660" s="11"/>
       <c r="U660" s="11"/>
       <c r="V660" s="11"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="20:22" ht="15.75" customHeight="1">
       <c r="T661" s="11"/>
       <c r="U661" s="11"/>
       <c r="V661" s="11"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="20:22" ht="15.75" customHeight="1">
       <c r="T662" s="11"/>
       <c r="U662" s="11"/>
       <c r="V662" s="11"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="20:22" ht="15.75" customHeight="1">
       <c r="T663" s="11"/>
       <c r="U663" s="11"/>
       <c r="V663" s="11"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="20:22" ht="15.75" customHeight="1">
       <c r="T664" s="11"/>
       <c r="U664" s="11"/>
       <c r="V664" s="11"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="20:22" ht="15.75" customHeight="1">
       <c r="T665" s="11"/>
       <c r="U665" s="11"/>
       <c r="V665" s="11"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="20:22" ht="15.75" customHeight="1">
       <c r="T666" s="11"/>
       <c r="U666" s="11"/>
       <c r="V666" s="11"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="20:22" ht="15.75" customHeight="1">
       <c r="T667" s="11"/>
       <c r="U667" s="11"/>
       <c r="V667" s="11"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="20:22" ht="15.75" customHeight="1">
       <c r="T668" s="11"/>
       <c r="U668" s="11"/>
       <c r="V668" s="11"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="20:22" ht="15.75" customHeight="1">
       <c r="T669" s="11"/>
       <c r="U669" s="11"/>
       <c r="V669" s="11"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="20:22" ht="15.75" customHeight="1">
       <c r="T670" s="11"/>
       <c r="U670" s="11"/>
       <c r="V670" s="11"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="20:22" ht="15.75" customHeight="1">
       <c r="T671" s="11"/>
       <c r="U671" s="11"/>
       <c r="V671" s="11"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="20:22" ht="15.75" customHeight="1">
       <c r="T672" s="11"/>
       <c r="U672" s="11"/>
       <c r="V672" s="11"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="20:22" ht="15.75" customHeight="1">
       <c r="T673" s="11"/>
       <c r="U673" s="11"/>
       <c r="V673" s="11"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="20:22" ht="15.75" customHeight="1">
       <c r="T674" s="11"/>
       <c r="U674" s="11"/>
       <c r="V674" s="11"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="20:22" ht="15.75" customHeight="1">
       <c r="T675" s="11"/>
       <c r="U675" s="11"/>
       <c r="V675" s="11"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="20:22" ht="15.75" customHeight="1">
       <c r="T676" s="11"/>
       <c r="U676" s="11"/>
       <c r="V676" s="11"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="20:22" ht="15.75" customHeight="1">
       <c r="T677" s="11"/>
       <c r="U677" s="11"/>
       <c r="V677" s="11"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="20:22" ht="15.75" customHeight="1">
       <c r="T678" s="11"/>
       <c r="U678" s="11"/>
       <c r="V678" s="11"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="20:22" ht="15.75" customHeight="1">
       <c r="T679" s="11"/>
       <c r="U679" s="11"/>
       <c r="V679" s="11"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="20:22" ht="15.75" customHeight="1">
       <c r="T680" s="11"/>
       <c r="U680" s="11"/>
       <c r="V680" s="11"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="20:22" ht="15.75" customHeight="1">
       <c r="T681" s="11"/>
       <c r="U681" s="11"/>
       <c r="V681" s="11"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="20:22" ht="15.75" customHeight="1">
       <c r="T682" s="11"/>
       <c r="U682" s="11"/>
       <c r="V682" s="11"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="20:22" ht="15.75" customHeight="1">
       <c r="T683" s="11"/>
       <c r="U683" s="11"/>
       <c r="V683" s="11"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="20:22" ht="15.75" customHeight="1">
       <c r="T684" s="11"/>
       <c r="U684" s="11"/>
       <c r="V684" s="11"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="20:22" ht="15.75" customHeight="1">
       <c r="T685" s="11"/>
       <c r="U685" s="11"/>
       <c r="V685" s="11"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="20:22" ht="15.75" customHeight="1">
       <c r="T686" s="11"/>
       <c r="U686" s="11"/>
       <c r="V686" s="11"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="20:22" ht="15.75" customHeight="1">
       <c r="T687" s="11"/>
       <c r="U687" s="11"/>
       <c r="V687" s="11"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="20:22" ht="15.75" customHeight="1">
       <c r="T688" s="11"/>
       <c r="U688" s="11"/>
       <c r="V688" s="11"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="20:22" ht="15.75" customHeight="1">
       <c r="T689" s="11"/>
       <c r="U689" s="11"/>
       <c r="V689" s="11"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="20:22" ht="15.75" customHeight="1">
       <c r="T690" s="11"/>
       <c r="U690" s="11"/>
       <c r="V690" s="11"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="20:22" ht="15.75" customHeight="1">
       <c r="T691" s="11"/>
       <c r="U691" s="11"/>
       <c r="V691" s="11"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="20:22" ht="15.75" customHeight="1">
       <c r="T692" s="11"/>
       <c r="U692" s="11"/>
       <c r="V692" s="11"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="20:22" ht="15.75" customHeight="1">
       <c r="T693" s="11"/>
       <c r="U693" s="11"/>
       <c r="V693" s="11"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="20:22" ht="15.75" customHeight="1">
       <c r="T694" s="11"/>
       <c r="U694" s="11"/>
       <c r="V694" s="11"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="20:22" ht="15.75" customHeight="1">
       <c r="T695" s="11"/>
       <c r="U695" s="11"/>
       <c r="V695" s="11"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="20:22" ht="15.75" customHeight="1">
       <c r="T696" s="11"/>
       <c r="U696" s="11"/>
       <c r="V696" s="11"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="20:22" ht="15.75" customHeight="1">
       <c r="T697" s="11"/>
       <c r="U697" s="11"/>
       <c r="V697" s="11"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="20:22" ht="15.75" customHeight="1">
       <c r="T698" s="11"/>
       <c r="U698" s="11"/>
       <c r="V698" s="11"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="20:22" ht="15.75" customHeight="1">
       <c r="T699" s="11"/>
       <c r="U699" s="11"/>
       <c r="V699" s="11"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="20:22" ht="15.75" customHeight="1">
       <c r="T700" s="11"/>
       <c r="U700" s="11"/>
       <c r="V700" s="11"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="20:22" ht="15.75" customHeight="1">
       <c r="T701" s="11"/>
       <c r="U701" s="11"/>
       <c r="V701" s="11"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="20:22" ht="15.75" customHeight="1">
       <c r="T702" s="11"/>
       <c r="U702" s="11"/>
       <c r="V702" s="11"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="20:22" ht="15.75" customHeight="1">
       <c r="T703" s="11"/>
       <c r="U703" s="11"/>
       <c r="V703" s="11"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="20:22" ht="15.75" customHeight="1">
       <c r="T704" s="11"/>
       <c r="U704" s="11"/>
       <c r="V704" s="11"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="20:22" ht="15.75" customHeight="1">
       <c r="T705" s="11"/>
       <c r="U705" s="11"/>
       <c r="V705" s="11"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="20:22" ht="15.75" customHeight="1">
       <c r="T706" s="11"/>
       <c r="U706" s="11"/>
       <c r="V706" s="11"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="20:22" ht="15.75" customHeight="1">
       <c r="T707" s="11"/>
       <c r="U707" s="11"/>
       <c r="V707" s="11"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="20:22" ht="15.75" customHeight="1">
       <c r="T708" s="11"/>
       <c r="U708" s="11"/>
       <c r="V708" s="11"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="20:22" ht="15.75" customHeight="1">
       <c r="T709" s="11"/>
       <c r="U709" s="11"/>
       <c r="V709" s="11"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="20:22" ht="15.75" customHeight="1">
       <c r="T710" s="11"/>
       <c r="U710" s="11"/>
       <c r="V710" s="11"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="20:22" ht="15.75" customHeight="1">
       <c r="T711" s="11"/>
       <c r="U711" s="11"/>
       <c r="V711" s="11"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="20:22" ht="15.75" customHeight="1">
       <c r="T712" s="11"/>
       <c r="U712" s="11"/>
       <c r="V712" s="11"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="20:22" ht="15.75" customHeight="1">
       <c r="T713" s="11"/>
       <c r="U713" s="11"/>
       <c r="V713" s="11"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="20:22" ht="15.75" customHeight="1">
       <c r="T714" s="11"/>
       <c r="U714" s="11"/>
       <c r="V714" s="11"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="20:22" ht="15.75" customHeight="1">
       <c r="T715" s="11"/>
       <c r="U715" s="11"/>
       <c r="V715" s="11"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="20:22" ht="15.75" customHeight="1">
       <c r="T716" s="11"/>
       <c r="U716" s="11"/>
       <c r="V716" s="11"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="20:22" ht="15.75" customHeight="1">
       <c r="T717" s="11"/>
       <c r="U717" s="11"/>
       <c r="V717" s="11"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="20:22" ht="15.75" customHeight="1">
       <c r="T718" s="11"/>
       <c r="U718" s="11"/>
       <c r="V718" s="11"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="20:22" ht="15.75" customHeight="1">
       <c r="T719" s="11"/>
       <c r="U719" s="11"/>
       <c r="V719" s="11"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="20:22" ht="15.75" customHeight="1">
       <c r="T720" s="11"/>
       <c r="U720" s="11"/>
       <c r="V720" s="11"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="20:22" ht="15.75" customHeight="1">
       <c r="T721" s="11"/>
       <c r="U721" s="11"/>
       <c r="V721" s="11"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="20:22" ht="15.75" customHeight="1">
       <c r="T722" s="11"/>
       <c r="U722" s="11"/>
       <c r="V722" s="11"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="20:22" ht="15.75" customHeight="1">
       <c r="T723" s="11"/>
       <c r="U723" s="11"/>
       <c r="V723" s="11"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="20:22" ht="15.75" customHeight="1">
       <c r="T724" s="11"/>
       <c r="U724" s="11"/>
       <c r="V724" s="11"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="20:22" ht="15.75" customHeight="1">
       <c r="T725" s="11"/>
       <c r="U725" s="11"/>
       <c r="V725" s="11"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="20:22" ht="15.75" customHeight="1">
       <c r="T726" s="11"/>
       <c r="U726" s="11"/>
       <c r="V726" s="11"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="20:22" ht="15.75" customHeight="1">
       <c r="T727" s="11"/>
       <c r="U727" s="11"/>
       <c r="V727" s="11"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="20:22" ht="15.75" customHeight="1">
       <c r="T728" s="11"/>
       <c r="U728" s="11"/>
       <c r="V728" s="11"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="20:22" ht="15.75" customHeight="1">
       <c r="T729" s="11"/>
       <c r="U729" s="11"/>
       <c r="V729" s="11"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="20:22" ht="15.75" customHeight="1">
       <c r="T730" s="11"/>
       <c r="U730" s="11"/>
       <c r="V730" s="11"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="20:22" ht="15.75" customHeight="1">
       <c r="T731" s="11"/>
       <c r="U731" s="11"/>
       <c r="V731" s="11"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="20:22" ht="15.75" customHeight="1">
       <c r="T732" s="11"/>
       <c r="U732" s="11"/>
       <c r="V732" s="11"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="20:22" ht="15.75" customHeight="1">
       <c r="T733" s="11"/>
       <c r="U733" s="11"/>
       <c r="V733" s="11"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="20:22" ht="15.75" customHeight="1">
       <c r="T734" s="11"/>
       <c r="U734" s="11"/>
       <c r="V734" s="11"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="20:22" ht="15.75" customHeight="1">
       <c r="T735" s="11"/>
       <c r="U735" s="11"/>
       <c r="V735" s="11"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="20:22" ht="15.75" customHeight="1">
       <c r="T736" s="11"/>
       <c r="U736" s="11"/>
       <c r="V736" s="11"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="20:22" ht="15.75" customHeight="1">
       <c r="T737" s="11"/>
       <c r="U737" s="11"/>
       <c r="V737" s="11"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="20:22" ht="15.75" customHeight="1">
       <c r="T738" s="11"/>
       <c r="U738" s="11"/>
       <c r="V738" s="11"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="20:22" ht="15.75" customHeight="1">
       <c r="T739" s="11"/>
       <c r="U739" s="11"/>
       <c r="V739" s="11"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="20:22" ht="15.75" customHeight="1">
       <c r="T740" s="11"/>
       <c r="U740" s="11"/>
       <c r="V740" s="11"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="20:22" ht="15.75" customHeight="1">
       <c r="T741" s="11"/>
       <c r="U741" s="11"/>
       <c r="V741" s="11"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="20:22" ht="15.75" customHeight="1">
       <c r="T742" s="11"/>
       <c r="U742" s="11"/>
       <c r="V742" s="11"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="20:22" ht="15.75" customHeight="1">
       <c r="T743" s="11"/>
       <c r="U743" s="11"/>
       <c r="V743" s="11"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="20:22" ht="15.75" customHeight="1">
       <c r="T744" s="11"/>
       <c r="U744" s="11"/>
       <c r="V744" s="11"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="20:22" ht="15.75" customHeight="1">
       <c r="T745" s="11"/>
       <c r="U745" s="11"/>
       <c r="V745" s="11"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="20:22" ht="15.75" customHeight="1">
       <c r="T746" s="11"/>
       <c r="U746" s="11"/>
       <c r="V746" s="11"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="20:22" ht="15.75" customHeight="1">
       <c r="T747" s="11"/>
       <c r="U747" s="11"/>
       <c r="V747" s="11"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="20:22" ht="15.75" customHeight="1">
       <c r="T748" s="11"/>
       <c r="U748" s="11"/>
       <c r="V748" s="11"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="20:22" ht="15.75" customHeight="1">
       <c r="T749" s="11"/>
       <c r="U749" s="11"/>
       <c r="V749" s="11"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="20:22" ht="15.75" customHeight="1">
       <c r="T750" s="11"/>
       <c r="U750" s="11"/>
       <c r="V750" s="11"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="20:22" ht="15.75" customHeight="1">
       <c r="T751" s="11"/>
       <c r="U751" s="11"/>
       <c r="V751" s="11"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="20:22" ht="15.75" customHeight="1">
       <c r="T752" s="11"/>
       <c r="U752" s="11"/>
       <c r="V752" s="11"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="20:22" ht="15.75" customHeight="1">
       <c r="T753" s="11"/>
       <c r="U753" s="11"/>
       <c r="V753" s="11"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="20:22" ht="15.75" customHeight="1">
       <c r="T754" s="11"/>
       <c r="U754" s="11"/>
       <c r="V754" s="11"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="20:22" ht="15.75" customHeight="1">
       <c r="T755" s="11"/>
       <c r="U755" s="11"/>
       <c r="V755" s="11"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="20:22" ht="15.75" customHeight="1">
       <c r="T756" s="11"/>
       <c r="U756" s="11"/>
       <c r="V756" s="11"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="20:22" ht="15.75" customHeight="1">
       <c r="T757" s="11"/>
       <c r="U757" s="11"/>
       <c r="V757" s="11"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="20:22" ht="15.75" customHeight="1">
       <c r="T758" s="11"/>
       <c r="U758" s="11"/>
       <c r="V758" s="11"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="20:22" ht="15.75" customHeight="1">
       <c r="T759" s="11"/>
       <c r="U759" s="11"/>
       <c r="V759" s="11"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="20:22" ht="15.75" customHeight="1">
       <c r="T760" s="11"/>
       <c r="U760" s="11"/>
       <c r="V760" s="11"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="20:22" ht="15.75" customHeight="1">
       <c r="T761" s="11"/>
       <c r="U761" s="11"/>
       <c r="V761" s="11"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="20:22" ht="15.75" customHeight="1">
       <c r="T762" s="11"/>
       <c r="U762" s="11"/>
       <c r="V762" s="11"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="20:22" ht="15.75" customHeight="1">
       <c r="T763" s="11"/>
       <c r="U763" s="11"/>
       <c r="V763" s="11"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="20:22" ht="15.75" customHeight="1">
       <c r="T764" s="11"/>
       <c r="U764" s="11"/>
       <c r="V764" s="11"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="20:22" ht="15.75" customHeight="1">
       <c r="T765" s="11"/>
       <c r="U765" s="11"/>
       <c r="V765" s="11"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="20:22" ht="15.75" customHeight="1">
       <c r="T766" s="11"/>
       <c r="U766" s="11"/>
       <c r="V766" s="11"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="20:22" ht="15.75" customHeight="1">
       <c r="T767" s="11"/>
       <c r="U767" s="11"/>
       <c r="V767" s="11"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="20:22" ht="15.75" customHeight="1">
       <c r="T768" s="11"/>
       <c r="U768" s="11"/>
       <c r="V768" s="11"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="20:22" ht="15.75" customHeight="1">
       <c r="T769" s="11"/>
       <c r="U769" s="11"/>
       <c r="V769" s="11"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="20:22" ht="15.75" customHeight="1">
       <c r="T770" s="11"/>
       <c r="U770" s="11"/>
       <c r="V770" s="11"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="20:22" ht="15.75" customHeight="1">
       <c r="T771" s="11"/>
       <c r="U771" s="11"/>
       <c r="V771" s="11"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="20:22" ht="15.75" customHeight="1">
       <c r="T772" s="11"/>
       <c r="U772" s="11"/>
       <c r="V772" s="11"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="20:22" ht="15.75" customHeight="1">
       <c r="T773" s="11"/>
       <c r="U773" s="11"/>
       <c r="V773" s="11"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="20:22" ht="15.75" customHeight="1">
       <c r="T774" s="11"/>
       <c r="U774" s="11"/>
       <c r="V774" s="11"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="20:22" ht="15.75" customHeight="1">
       <c r="T775" s="11"/>
       <c r="U775" s="11"/>
       <c r="V775" s="11"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="20:22" ht="15.75" customHeight="1">
       <c r="T776" s="11"/>
       <c r="U776" s="11"/>
       <c r="V776" s="11"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="20:22" ht="15.75" customHeight="1">
       <c r="T777" s="11"/>
       <c r="U777" s="11"/>
       <c r="V777" s="11"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="20:22" ht="15.75" customHeight="1">
       <c r="T778" s="11"/>
       <c r="U778" s="11"/>
       <c r="V778" s="11"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="20:22" ht="15.75" customHeight="1">
       <c r="T779" s="11"/>
       <c r="U779" s="11"/>
       <c r="V779" s="11"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="20:22" ht="15.75" customHeight="1">
       <c r="T780" s="11"/>
       <c r="U780" s="11"/>
       <c r="V780" s="11"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="20:22" ht="15.75" customHeight="1">
       <c r="T781" s="11"/>
       <c r="U781" s="11"/>
       <c r="V781" s="11"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="20:22" ht="15.75" customHeight="1">
       <c r="T782" s="11"/>
       <c r="U782" s="11"/>
       <c r="V782" s="11"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="20:22" ht="15.75" customHeight="1">
       <c r="T783" s="11"/>
       <c r="U783" s="11"/>
       <c r="V783" s="11"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="20:22" ht="15.75" customHeight="1">
       <c r="T784" s="11"/>
       <c r="U784" s="11"/>
       <c r="V784" s="11"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="20:22" ht="15.75" customHeight="1">
       <c r="T785" s="11"/>
       <c r="U785" s="11"/>
       <c r="V785" s="11"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="20:22" ht="15.75" customHeight="1">
       <c r="T786" s="11"/>
       <c r="U786" s="11"/>
       <c r="V786" s="11"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="20:22" ht="15.75" customHeight="1">
       <c r="T787" s="11"/>
       <c r="U787" s="11"/>
       <c r="V787" s="11"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="20:22" ht="15.75" customHeight="1">
       <c r="T788" s="11"/>
       <c r="U788" s="11"/>
       <c r="V788" s="11"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="20:22" ht="15.75" customHeight="1">
       <c r="T789" s="11"/>
       <c r="U789" s="11"/>
       <c r="V789" s="11"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="20:22" ht="15.75" customHeight="1">
       <c r="T790" s="11"/>
       <c r="U790" s="11"/>
       <c r="V790" s="11"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="20:22" ht="15.75" customHeight="1">
       <c r="T791" s="11"/>
       <c r="U791" s="11"/>
       <c r="V791" s="11"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="20:22" ht="15.75" customHeight="1">
       <c r="T792" s="11"/>
       <c r="U792" s="11"/>
       <c r="V792" s="11"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="20:22" ht="15.75" customHeight="1">
       <c r="T793" s="11"/>
       <c r="U793" s="11"/>
       <c r="V793" s="11"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="20:22" ht="15.75" customHeight="1">
       <c r="T794" s="11"/>
       <c r="U794" s="11"/>
       <c r="V794" s="11"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="20:22" ht="15.75" customHeight="1">
       <c r="T795" s="11"/>
       <c r="U795" s="11"/>
       <c r="V795" s="11"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="20:22" ht="15.75" customHeight="1">
       <c r="T796" s="11"/>
       <c r="U796" s="11"/>
       <c r="V796" s="11"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="20:22" ht="15.75" customHeight="1">
       <c r="T797" s="11"/>
       <c r="U797" s="11"/>
       <c r="V797" s="11"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="20:22" ht="15.75" customHeight="1">
       <c r="T798" s="11"/>
       <c r="U798" s="11"/>
       <c r="V798" s="11"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="20:22" ht="15.75" customHeight="1">
       <c r="T799" s="11"/>
       <c r="U799" s="11"/>
       <c r="V799" s="11"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="20:22" ht="15.75" customHeight="1">
       <c r="T800" s="11"/>
       <c r="U800" s="11"/>
       <c r="V800" s="11"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="20:22" ht="15.75" customHeight="1">
       <c r="T801" s="11"/>
       <c r="U801" s="11"/>
       <c r="V801" s="11"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="20:22" ht="15.75" customHeight="1">
       <c r="T802" s="11"/>
       <c r="U802" s="11"/>
       <c r="V802" s="11"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="20:22" ht="15.75" customHeight="1">
       <c r="T803" s="11"/>
       <c r="U803" s="11"/>
       <c r="V803" s="11"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="20:22" ht="15.75" customHeight="1">
       <c r="T804" s="11"/>
       <c r="U804" s="11"/>
       <c r="V804" s="11"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="20:22" ht="15.75" customHeight="1">
       <c r="T805" s="11"/>
       <c r="U805" s="11"/>
       <c r="V805" s="11"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="20:22" ht="15.75" customHeight="1">
       <c r="T806" s="11"/>
       <c r="U806" s="11"/>
       <c r="V806" s="11"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="20:22" ht="15.75" customHeight="1">
       <c r="T807" s="11"/>
       <c r="U807" s="11"/>
       <c r="V807" s="11"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="20:22" ht="15.75" customHeight="1">
       <c r="T808" s="11"/>
       <c r="U808" s="11"/>
       <c r="V808" s="11"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="20:22" ht="15.75" customHeight="1">
       <c r="T809" s="11"/>
       <c r="U809" s="11"/>
       <c r="V809" s="11"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="20:22" ht="15.75" customHeight="1">
       <c r="T810" s="11"/>
       <c r="U810" s="11"/>
       <c r="V810" s="11"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="20:22" ht="15.75" customHeight="1">
       <c r="T811" s="11"/>
       <c r="U811" s="11"/>
       <c r="V811" s="11"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="20:22" ht="15.75" customHeight="1">
       <c r="T812" s="11"/>
       <c r="U812" s="11"/>
       <c r="V812" s="11"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="20:22" ht="15.75" customHeight="1">
       <c r="T813" s="11"/>
       <c r="U813" s="11"/>
       <c r="V813" s="11"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="20:22" ht="15.75" customHeight="1">
       <c r="T814" s="11"/>
       <c r="U814" s="11"/>
       <c r="V814" s="11"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="20:22" ht="15.75" customHeight="1">
       <c r="T815" s="11"/>
       <c r="U815" s="11"/>
       <c r="V815" s="11"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="20:22" ht="15.75" customHeight="1">
       <c r="T816" s="11"/>
       <c r="U816" s="11"/>
       <c r="V816" s="11"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="20:22" ht="15.75" customHeight="1">
       <c r="T817" s="11"/>
       <c r="U817" s="11"/>
       <c r="V817" s="11"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="20:22" ht="15.75" customHeight="1">
       <c r="T818" s="11"/>
       <c r="U818" s="11"/>
       <c r="V818" s="11"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="20:22" ht="15.75" customHeight="1">
       <c r="T819" s="11"/>
       <c r="U819" s="11"/>
       <c r="V819" s="11"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="20:22" ht="15.75" customHeight="1">
       <c r="T820" s="11"/>
       <c r="U820" s="11"/>
       <c r="V820" s="11"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="20:22" ht="15.75" customHeight="1">
       <c r="T821" s="11"/>
       <c r="U821" s="11"/>
       <c r="V821" s="11"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="20:22" ht="15.75" customHeight="1">
       <c r="T822" s="11"/>
       <c r="U822" s="11"/>
       <c r="V822" s="11"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="20:22" ht="15.75" customHeight="1">
       <c r="T823" s="11"/>
       <c r="U823" s="11"/>
       <c r="V823" s="11"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="20:22" ht="15.75" customHeight="1">
       <c r="T824" s="11"/>
       <c r="U824" s="11"/>
       <c r="V824" s="11"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="20:22" ht="15.75" customHeight="1">
       <c r="T825" s="11"/>
       <c r="U825" s="11"/>
       <c r="V825" s="11"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="20:22" ht="15.75" customHeight="1">
       <c r="T826" s="11"/>
       <c r="U826" s="11"/>
       <c r="V826" s="11"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="20:22" ht="15.75" customHeight="1">
       <c r="T827" s="11"/>
       <c r="U827" s="11"/>
       <c r="V827" s="11"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="20:22" ht="15.75" customHeight="1">
       <c r="T828" s="11"/>
       <c r="U828" s="11"/>
       <c r="V828" s="11"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="20:22" ht="15.75" customHeight="1">
       <c r="T829" s="11"/>
       <c r="U829" s="11"/>
       <c r="V829" s="11"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="20:22" ht="15.75" customHeight="1">
       <c r="T830" s="11"/>
       <c r="U830" s="11"/>
       <c r="V830" s="11"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="20:22" ht="15.75" customHeight="1">
       <c r="T831" s="11"/>
       <c r="U831" s="11"/>
       <c r="V831" s="11"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="20:22" ht="15.75" customHeight="1">
       <c r="T832" s="11"/>
       <c r="U832" s="11"/>
       <c r="V832" s="11"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="20:22" ht="15.75" customHeight="1">
       <c r="T833" s="11"/>
       <c r="U833" s="11"/>
       <c r="V833" s="11"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="20:22" ht="15.75" customHeight="1">
       <c r="T834" s="11"/>
       <c r="U834" s="11"/>
       <c r="V834" s="11"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="20:22" ht="15.75" customHeight="1">
       <c r="T835" s="11"/>
       <c r="U835" s="11"/>
       <c r="V835" s="11"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="20:22" ht="15.75" customHeight="1">
       <c r="T836" s="11"/>
       <c r="U836" s="11"/>
       <c r="V836" s="11"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="20:22" ht="15.75" customHeight="1">
       <c r="T837" s="11"/>
       <c r="U837" s="11"/>
       <c r="V837" s="11"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="20:22" ht="15.75" customHeight="1">
       <c r="T838" s="11"/>
       <c r="U838" s="11"/>
       <c r="V838" s="11"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="20:22" ht="15.75" customHeight="1">
       <c r="T839" s="11"/>
       <c r="U839" s="11"/>
       <c r="V839" s="11"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="20:22" ht="15.75" customHeight="1">
       <c r="T840" s="11"/>
       <c r="U840" s="11"/>
       <c r="V840" s="11"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="20:22" ht="15.75" customHeight="1">
       <c r="T841" s="11"/>
       <c r="U841" s="11"/>
       <c r="V841" s="11"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="20:22" ht="15.75" customHeight="1">
       <c r="T842" s="11"/>
       <c r="U842" s="11"/>
       <c r="V842" s="11"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="20:22" ht="15.75" customHeight="1">
       <c r="T843" s="11"/>
       <c r="U843" s="11"/>
       <c r="V843" s="11"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="20:22" ht="15.75" customHeight="1">
       <c r="T844" s="11"/>
       <c r="U844" s="11"/>
       <c r="V844" s="11"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="20:22" ht="15.75" customHeight="1">
       <c r="T845" s="11"/>
       <c r="U845" s="11"/>
       <c r="V845" s="11"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="20:22" ht="15.75" customHeight="1">
       <c r="T846" s="11"/>
       <c r="U846" s="11"/>
       <c r="V846" s="11"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="20:22" ht="15.75" customHeight="1">
       <c r="T847" s="11"/>
       <c r="U847" s="11"/>
       <c r="V847" s="11"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="20:22" ht="15.75" customHeight="1">
       <c r="T848" s="11"/>
       <c r="U848" s="11"/>
       <c r="V848" s="11"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="20:22" ht="15.75" customHeight="1">
       <c r="T849" s="11"/>
       <c r="U849" s="11"/>
       <c r="V849" s="11"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="20:22" ht="15.75" customHeight="1">
       <c r="T850" s="11"/>
       <c r="U850" s="11"/>
       <c r="V850" s="11"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="20:22" ht="15.75" customHeight="1">
       <c r="T851" s="11"/>
       <c r="U851" s="11"/>
       <c r="V851" s="11"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="20:22" ht="15.75" customHeight="1">
       <c r="T852" s="11"/>
       <c r="U852" s="11"/>
       <c r="V852" s="11"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="20:22" ht="15.75" customHeight="1">
       <c r="T853" s="11"/>
       <c r="U853" s="11"/>
       <c r="V853" s="11"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="20:22" ht="15.75" customHeight="1">
       <c r="T854" s="11"/>
       <c r="U854" s="11"/>
       <c r="V854" s="11"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="20:22" ht="15.75" customHeight="1">
       <c r="T855" s="11"/>
       <c r="U855" s="11"/>
       <c r="V855" s="11"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="20:22" ht="15.75" customHeight="1">
       <c r="T856" s="11"/>
       <c r="U856" s="11"/>
       <c r="V856" s="11"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="20:22" ht="15.75" customHeight="1">
       <c r="T857" s="11"/>
       <c r="U857" s="11"/>
       <c r="V857" s="11"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="20:22" ht="15.75" customHeight="1">
       <c r="T858" s="11"/>
       <c r="U858" s="11"/>
       <c r="V858" s="11"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="20:22" ht="15.75" customHeight="1">
       <c r="T859" s="11"/>
       <c r="U859" s="11"/>
       <c r="V859" s="11"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="20:22" ht="15.75" customHeight="1">
       <c r="T860" s="11"/>
       <c r="U860" s="11"/>
       <c r="V860" s="11"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="20:22" ht="15.75" customHeight="1">
       <c r="T861" s="11"/>
       <c r="U861" s="11"/>
       <c r="V861" s="11"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="20:22" ht="15.75" customHeight="1">
       <c r="T862" s="11"/>
       <c r="U862" s="11"/>
       <c r="V862" s="11"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="20:22" ht="15.75" customHeight="1">
       <c r="T863" s="11"/>
       <c r="U863" s="11"/>
       <c r="V863" s="11"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="20:22" ht="15.75" customHeight="1">
       <c r="T864" s="11"/>
       <c r="U864" s="11"/>
       <c r="V864" s="11"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="20:22" ht="15.75" customHeight="1">
       <c r="T865" s="11"/>
       <c r="U865" s="11"/>
       <c r="V865" s="11"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="20:22" ht="15.75" customHeight="1">
       <c r="T866" s="11"/>
       <c r="U866" s="11"/>
       <c r="V866" s="11"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="20:22" ht="15.75" customHeight="1">
       <c r="T867" s="11"/>
       <c r="U867" s="11"/>
       <c r="V867" s="11"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="20:22" ht="15.75" customHeight="1">
       <c r="T868" s="11"/>
       <c r="U868" s="11"/>
       <c r="V868" s="11"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="20:22" ht="15.75" customHeight="1">
       <c r="T869" s="11"/>
       <c r="U869" s="11"/>
       <c r="V869" s="11"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="20:22" ht="15.75" customHeight="1">
       <c r="T870" s="11"/>
       <c r="U870" s="11"/>
       <c r="V870" s="11"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="20:22" ht="15.75" customHeight="1">
       <c r="T871" s="11"/>
       <c r="U871" s="11"/>
       <c r="V871" s="11"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="20:22" ht="15.75" customHeight="1">
       <c r="T872" s="11"/>
       <c r="U872" s="11"/>
       <c r="V872" s="11"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="20:22" ht="15.75" customHeight="1">
       <c r="T873" s="11"/>
       <c r="U873" s="11"/>
       <c r="V873" s="11"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="20:22" ht="15.75" customHeight="1">
       <c r="T874" s="11"/>
       <c r="U874" s="11"/>
       <c r="V874" s="11"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="20:22" ht="15.75" customHeight="1">
       <c r="T875" s="11"/>
       <c r="U875" s="11"/>
       <c r="V875" s="11"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="20:22" ht="15.75" customHeight="1">
       <c r="T876" s="11"/>
       <c r="U876" s="11"/>
       <c r="V876" s="11"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="20:22" ht="15.75" customHeight="1">
       <c r="T877" s="11"/>
       <c r="U877" s="11"/>
       <c r="V877" s="11"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="20:22" ht="15.75" customHeight="1">
       <c r="T878" s="11"/>
       <c r="U878" s="11"/>
       <c r="V878" s="11"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="20:22" ht="15.75" customHeight="1">
       <c r="T879" s="11"/>
       <c r="U879" s="11"/>
       <c r="V879" s="11"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="20:22" ht="15.75" customHeight="1">
       <c r="T880" s="11"/>
       <c r="U880" s="11"/>
       <c r="V880" s="11"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="20:22" ht="15.75" customHeight="1">
       <c r="T881" s="11"/>
       <c r="U881" s="11"/>
       <c r="V881" s="11"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="20:22" ht="15.75" customHeight="1">
       <c r="T882" s="11"/>
       <c r="U882" s="11"/>
       <c r="V882" s="11"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="20:22" ht="15.75" customHeight="1">
       <c r="T883" s="11"/>
       <c r="U883" s="11"/>
       <c r="V883" s="11"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="20:22" ht="15.75" customHeight="1">
       <c r="T884" s="11"/>
       <c r="U884" s="11"/>
       <c r="V884" s="11"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="20:22" ht="15.75" customHeight="1">
       <c r="T885" s="11"/>
       <c r="U885" s="11"/>
       <c r="V885" s="11"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="20:22" ht="15.75" customHeight="1">
       <c r="T886" s="11"/>
       <c r="U886" s="11"/>
       <c r="V886" s="11"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="20:22" ht="15.75" customHeight="1">
       <c r="T887" s="11"/>
       <c r="U887" s="11"/>
       <c r="V887" s="11"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="20:22" ht="15.75" customHeight="1">
       <c r="T888" s="11"/>
       <c r="U888" s="11"/>
       <c r="V888" s="11"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="20:22" ht="15.75" customHeight="1">
       <c r="T889" s="11"/>
       <c r="U889" s="11"/>
       <c r="V889" s="11"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="20:22" ht="15.75" customHeight="1">
       <c r="T890" s="11"/>
       <c r="U890" s="11"/>
       <c r="V890" s="11"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="20:22" ht="15.75" customHeight="1">
       <c r="T891" s="11"/>
       <c r="U891" s="11"/>
       <c r="V891" s="11"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="20:22" ht="15.75" customHeight="1">
       <c r="T892" s="11"/>
       <c r="U892" s="11"/>
       <c r="V892" s="11"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="20:22" ht="15.75" customHeight="1">
       <c r="T893" s="11"/>
       <c r="U893" s="11"/>
       <c r="V893" s="11"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="20:22" ht="15.75" customHeight="1">
       <c r="T894" s="11"/>
       <c r="U894" s="11"/>
       <c r="V894" s="11"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="20:22" ht="15.75" customHeight="1">
       <c r="T895" s="11"/>
       <c r="U895" s="11"/>
       <c r="V895" s="11"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="20:22" ht="15.75" customHeight="1">
       <c r="T896" s="11"/>
       <c r="U896" s="11"/>
       <c r="V896" s="11"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="20:22" ht="15.75" customHeight="1">
       <c r="T897" s="11"/>
       <c r="U897" s="11"/>
       <c r="V897" s="11"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="20:22" ht="15.75" customHeight="1">
       <c r="T898" s="11"/>
       <c r="U898" s="11"/>
       <c r="V898" s="11"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="20:22" ht="15.75" customHeight="1">
       <c r="T899" s="11"/>
       <c r="U899" s="11"/>
       <c r="V899" s="11"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="20:22" ht="15.75" customHeight="1">
       <c r="T900" s="11"/>
       <c r="U900" s="11"/>
       <c r="V900" s="11"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="20:22" ht="15.75" customHeight="1">
       <c r="T901" s="11"/>
       <c r="U901" s="11"/>
       <c r="V901" s="11"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="20:22" ht="15.75" customHeight="1">
       <c r="T902" s="11"/>
       <c r="U902" s="11"/>
       <c r="V902" s="11"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="20:22" ht="15.75" customHeight="1">
       <c r="T903" s="11"/>
       <c r="U903" s="11"/>
       <c r="V903" s="11"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="20:22" ht="15.75" customHeight="1">
       <c r="T904" s="11"/>
       <c r="U904" s="11"/>
       <c r="V904" s="11"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="20:22" ht="15.75" customHeight="1">
       <c r="T905" s="11"/>
       <c r="U905" s="11"/>
       <c r="V905" s="11"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="20:22" ht="15.75" customHeight="1">
       <c r="T906" s="11"/>
       <c r="U906" s="11"/>
       <c r="V906" s="11"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="20:22" ht="15.75" customHeight="1">
       <c r="T907" s="11"/>
       <c r="U907" s="11"/>
       <c r="V907" s="11"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="20:22" ht="15.75" customHeight="1">
       <c r="T908" s="11"/>
       <c r="U908" s="11"/>
       <c r="V908" s="11"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="20:22" ht="15.75" customHeight="1">
       <c r="T909" s="11"/>
       <c r="U909" s="11"/>
       <c r="V909" s="11"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="20:22" ht="15.75" customHeight="1">
       <c r="T910" s="11"/>
       <c r="U910" s="11"/>
       <c r="V910" s="11"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="20:22" ht="15.75" customHeight="1">
       <c r="T911" s="11"/>
       <c r="U911" s="11"/>
       <c r="V911" s="11"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="20:22" ht="15.75" customHeight="1">
       <c r="T912" s="11"/>
       <c r="U912" s="11"/>
       <c r="V912" s="11"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="20:22" ht="15.75" customHeight="1">
       <c r="T913" s="11"/>
       <c r="U913" s="11"/>
       <c r="V913" s="11"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="20:22" ht="15.75" customHeight="1">
       <c r="T914" s="11"/>
       <c r="U914" s="11"/>
       <c r="V914" s="11"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="20:22" ht="15.75" customHeight="1">
       <c r="T915" s="11"/>
       <c r="U915" s="11"/>
       <c r="V915" s="11"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="20:22" ht="15.75" customHeight="1">
       <c r="T916" s="11"/>
       <c r="U916" s="11"/>
       <c r="V916" s="11"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="20:22" ht="15.75" customHeight="1">
       <c r="T917" s="11"/>
       <c r="U917" s="11"/>
       <c r="V917" s="11"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="20:22" ht="15.75" customHeight="1">
       <c r="T918" s="11"/>
       <c r="U918" s="11"/>
       <c r="V918" s="11"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="20:22" ht="15.75" customHeight="1">
       <c r="T919" s="11"/>
       <c r="U919" s="11"/>
       <c r="V919" s="11"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="20:22" ht="15.75" customHeight="1">
       <c r="T920" s="11"/>
       <c r="U920" s="11"/>
       <c r="V920" s="11"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="20:22" ht="15.75" customHeight="1">
       <c r="T921" s="11"/>
       <c r="U921" s="11"/>
       <c r="V921" s="11"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="20:22" ht="15.75" customHeight="1">
       <c r="T922" s="11"/>
       <c r="U922" s="11"/>
       <c r="V922" s="11"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="20:22" ht="15.75" customHeight="1">
       <c r="T923" s="11"/>
       <c r="U923" s="11"/>
       <c r="V923" s="11"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="20:22" ht="15.75" customHeight="1">
       <c r="T924" s="11"/>
       <c r="U924" s="11"/>
       <c r="V924" s="11"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="20:22" ht="15.75" customHeight="1">
       <c r="T925" s="11"/>
       <c r="U925" s="11"/>
       <c r="V925" s="11"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="20:22" ht="15.75" customHeight="1">
       <c r="T926" s="11"/>
       <c r="U926" s="11"/>
       <c r="V926" s="11"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="20:22" ht="15.75" customHeight="1">
       <c r="T927" s="11"/>
       <c r="U927" s="11"/>
       <c r="V927" s="11"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="20:22" ht="15.75" customHeight="1">
       <c r="T928" s="11"/>
       <c r="U928" s="11"/>
       <c r="V928" s="11"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="20:22" ht="15.75" customHeight="1">
       <c r="T929" s="11"/>
       <c r="U929" s="11"/>
       <c r="V929" s="11"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="20:22" ht="15.75" customHeight="1">
       <c r="T930" s="11"/>
       <c r="U930" s="11"/>
       <c r="V930" s="11"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="20:22" ht="15.75" customHeight="1">
       <c r="T931" s="11"/>
       <c r="U931" s="11"/>
       <c r="V931" s="11"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="20:22" ht="15.75" customHeight="1">
       <c r="T932" s="11"/>
       <c r="U932" s="11"/>
       <c r="V932" s="11"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="20:22" ht="15.75" customHeight="1">
       <c r="T933" s="11"/>
       <c r="U933" s="11"/>
       <c r="V933" s="11"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="20:22" ht="15.75" customHeight="1">
       <c r="T934" s="11"/>
       <c r="U934" s="11"/>
       <c r="V934" s="11"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="20:22" ht="15.75" customHeight="1">
       <c r="T935" s="11"/>
       <c r="U935" s="11"/>
       <c r="V935" s="11"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="20:22" ht="15.75" customHeight="1">
       <c r="T936" s="11"/>
       <c r="U936" s="11"/>
       <c r="V936" s="11"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="20:22" ht="15.75" customHeight="1">
       <c r="T937" s="11"/>
       <c r="U937" s="11"/>
       <c r="V937" s="11"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="20:22" ht="15.75" customHeight="1">
       <c r="T938" s="11"/>
       <c r="U938" s="11"/>
       <c r="V938" s="11"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="20:22" ht="15.75" customHeight="1">
       <c r="T939" s="11"/>
       <c r="U939" s="11"/>
       <c r="V939" s="11"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="20:22" ht="15.75" customHeight="1">
       <c r="T940" s="11"/>
       <c r="U940" s="11"/>
       <c r="V940" s="11"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="20:22" ht="15.75" customHeight="1">
       <c r="T941" s="11"/>
       <c r="U941" s="11"/>
       <c r="V941" s="11"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="20:22" ht="15.75" customHeight="1">
       <c r="T942" s="11"/>
       <c r="U942" s="11"/>
       <c r="V942" s="11"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="20:22" ht="15.75" customHeight="1">
       <c r="T943" s="11"/>
       <c r="U943" s="11"/>
       <c r="V943" s="11"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="20:22" ht="15.75" customHeight="1">
       <c r="T944" s="11"/>
       <c r="U944" s="11"/>
       <c r="V944" s="11"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="20:22" ht="15.75" customHeight="1">
       <c r="T945" s="11"/>
       <c r="U945" s="11"/>
       <c r="V945" s="11"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="20:22" ht="15.75" customHeight="1">
       <c r="T946" s="11"/>
       <c r="U946" s="11"/>
       <c r="V946" s="11"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="20:22" ht="15.75" customHeight="1">
       <c r="T947" s="11"/>
       <c r="U947" s="11"/>
       <c r="V947" s="11"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="20:22" ht="15.75" customHeight="1">
       <c r="T948" s="11"/>
       <c r="U948" s="11"/>
       <c r="V948" s="11"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="20:22" ht="15.75" customHeight="1">
       <c r="T949" s="11"/>
       <c r="U949" s="11"/>
       <c r="V949" s="11"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="20:22" ht="15.75" customHeight="1">
       <c r="T950" s="11"/>
       <c r="U950" s="11"/>
       <c r="V950" s="11"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="20:22" ht="15.75" customHeight="1">
       <c r="T951" s="11"/>
       <c r="U951" s="11"/>
       <c r="V951" s="11"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="20:22" ht="15.75" customHeight="1">
       <c r="T952" s="11"/>
       <c r="U952" s="11"/>
       <c r="V952" s="11"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="20:22" ht="15.75" customHeight="1">
       <c r="T953" s="11"/>
       <c r="U953" s="11"/>
       <c r="V953" s="11"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="20:22" ht="15.75" customHeight="1">
       <c r="T954" s="11"/>
       <c r="U954" s="11"/>
       <c r="V954" s="11"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="20:22" ht="15.75" customHeight="1">
       <c r="T955" s="11"/>
       <c r="U955" s="11"/>
       <c r="V955" s="11"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="20:22" ht="15.75" customHeight="1">
       <c r="T956" s="11"/>
       <c r="U956" s="11"/>
       <c r="V956" s="11"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="20:22" ht="15.75" customHeight="1">
       <c r="T957" s="11"/>
       <c r="U957" s="11"/>
       <c r="V957" s="11"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="20:22" ht="15.75" customHeight="1">
       <c r="T958" s="11"/>
       <c r="U958" s="11"/>
       <c r="V958" s="11"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="20:22" ht="15.75" customHeight="1">
       <c r="T959" s="11"/>
       <c r="U959" s="11"/>
       <c r="V959" s="11"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="20:22" ht="15.75" customHeight="1">
       <c r="T960" s="11"/>
       <c r="U960" s="11"/>
       <c r="V960" s="11"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="20:22" ht="15.75" customHeight="1">
       <c r="T961" s="11"/>
       <c r="U961" s="11"/>
       <c r="V961" s="11"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="20:22" ht="15.75" customHeight="1">
       <c r="T962" s="11"/>
       <c r="U962" s="11"/>
       <c r="V962" s="11"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="20:22" ht="15.75" customHeight="1">
       <c r="T963" s="11"/>
       <c r="U963" s="11"/>
       <c r="V963" s="11"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="20:22" ht="15.75" customHeight="1">
       <c r="T964" s="11"/>
       <c r="U964" s="11"/>
       <c r="V964" s="11"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="20:22" ht="15.75" customHeight="1">
       <c r="T965" s="11"/>
       <c r="U965" s="11"/>
       <c r="V965" s="11"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="20:22" ht="15.75" customHeight="1">
       <c r="T966" s="11"/>
       <c r="U966" s="11"/>
       <c r="V966" s="11"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="20:22" ht="15.75" customHeight="1">
       <c r="T967" s="11"/>
       <c r="U967" s="11"/>
       <c r="V967" s="11"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="20:22" ht="15.75" customHeight="1">
       <c r="T968" s="11"/>
       <c r="U968" s="11"/>
       <c r="V968" s="11"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="20:22" ht="15.75" customHeight="1">
       <c r="T969" s="11"/>
       <c r="U969" s="11"/>
       <c r="V969" s="11"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="20:22" ht="15.75" customHeight="1">
       <c r="T970" s="11"/>
       <c r="U970" s="11"/>
       <c r="V970" s="11"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="20:22" ht="15.75" customHeight="1">
       <c r="T971" s="11"/>
       <c r="U971" s="11"/>
       <c r="V971" s="11"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="20:22" ht="15.75" customHeight="1">
       <c r="T972" s="11"/>
       <c r="U972" s="11"/>
       <c r="V972" s="11"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="20:22" ht="15.75" customHeight="1">
       <c r="T973" s="11"/>
       <c r="U973" s="11"/>
       <c r="V973" s="11"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="20:22" ht="15.75" customHeight="1">
       <c r="T974" s="11"/>
       <c r="U974" s="11"/>
       <c r="V974" s="11"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="20:22" ht="15.75" customHeight="1">
       <c r="T975" s="11"/>
       <c r="U975" s="11"/>
       <c r="V975" s="11"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="20:22" ht="15.75" customHeight="1">
       <c r="T976" s="11"/>
       <c r="U976" s="11"/>
       <c r="V976" s="11"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="20:22" ht="15.75" customHeight="1">
       <c r="T977" s="11"/>
       <c r="U977" s="11"/>
       <c r="V977" s="11"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="20:22" ht="15.75" customHeight="1">
       <c r="T978" s="11"/>
       <c r="U978" s="11"/>
       <c r="V978" s="11"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="20:22" ht="15.75" customHeight="1">
       <c r="T979" s="11"/>
       <c r="U979" s="11"/>
       <c r="V979" s="11"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="20:22" ht="15.75" customHeight="1">
       <c r="T980" s="11"/>
       <c r="U980" s="11"/>
       <c r="V980" s="11"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="20:22" ht="15.75" customHeight="1">
       <c r="T981" s="11"/>
       <c r="U981" s="11"/>
       <c r="V981" s="11"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="20:22" ht="15.75" customHeight="1">
       <c r="T982" s="11"/>
       <c r="U982" s="11"/>
       <c r="V982" s="11"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="20:22" ht="15.75" customHeight="1">
       <c r="T983" s="11"/>
       <c r="U983" s="11"/>
       <c r="V983" s="11"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="20:22" ht="15.75" customHeight="1">
       <c r="T984" s="11"/>
       <c r="U984" s="11"/>
       <c r="V984" s="11"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="20:22" ht="15.75" customHeight="1">
       <c r="T985" s="11"/>
       <c r="U985" s="11"/>
       <c r="V985" s="11"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="20:22" ht="15.75" customHeight="1">
       <c r="T986" s="11"/>
       <c r="U986" s="11"/>
       <c r="V986" s="11"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="20:22" ht="15.75" customHeight="1">
       <c r="T987" s="11"/>
       <c r="U987" s="11"/>
       <c r="V987" s="11"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="20:22" ht="15.75" customHeight="1">
       <c r="T988" s="11"/>
       <c r="U988" s="11"/>
       <c r="V988" s="11"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="20:22" ht="15.75" customHeight="1">
       <c r="T989" s="11"/>
       <c r="U989" s="11"/>
       <c r="V989" s="11"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="20:22" ht="15.75" customHeight="1">
       <c r="T990" s="11"/>
       <c r="U990" s="11"/>
       <c r="V990" s="11"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="20:22" ht="15.75" customHeight="1">
       <c r="T991" s="11"/>
       <c r="U991" s="11"/>
       <c r="V991" s="11"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="20:22" ht="15.75" customHeight="1">
       <c r="T992" s="11"/>
       <c r="U992" s="11"/>
       <c r="V992" s="11"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="20:22" ht="15.75" customHeight="1">
       <c r="T993" s="11"/>
       <c r="U993" s="11"/>
       <c r="V993" s="11"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="20:22" ht="15.75" customHeight="1">
       <c r="T994" s="11"/>
       <c r="U994" s="11"/>
       <c r="V994" s="11"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="20:22" ht="15.75" customHeight="1">
       <c r="T995" s="11"/>
       <c r="U995" s="11"/>
       <c r="V995" s="11"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="20:22" ht="15.75" customHeight="1">
       <c r="T996" s="11"/>
       <c r="U996" s="11"/>
       <c r="V996" s="11"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="20:22" ht="15.75" customHeight="1">
       <c r="T997" s="11"/>
       <c r="U997" s="11"/>
       <c r="V997" s="11"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="20:22" ht="15.75" customHeight="1">
       <c r="T998" s="11"/>
       <c r="U998" s="11"/>
       <c r="V998" s="11"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="20:22" ht="15.75" customHeight="1">
       <c r="T999" s="11"/>
       <c r="U999" s="11"/>
       <c r="V999" s="11"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="20:22" ht="15.75" customHeight="1">
       <c r="T1000" s="11"/>
       <c r="U1000" s="11"/>
       <c r="V1000" s="11"/>
     </row>
-    <row r="1001" ht="15.75" customHeight="1">
+    <row r="1001" spans="20:22" ht="15.75" customHeight="1">
       <c r="T1001" s="11"/>
       <c r="U1001" s="11"/>
       <c r="V1001" s="11"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
   <si>
     <t>아이디</t>
   </si>
@@ -172,7 +172,7 @@
     <t>Fire</t>
   </si>
   <si>
-    <t>Player/Projectile/Fire Arrow</t>
+    <t>Scholar/FireArrowEffect</t>
   </si>
   <si>
     <t>Basic</t>
@@ -190,7 +190,7 @@
     <t>Cold</t>
   </si>
   <si>
-    <t>Player/Projectile/Ice Arrow</t>
+    <t>Scholar/IceArrowEffect</t>
   </si>
   <si>
     <t>skill_scholar_basic_earth</t>
@@ -205,7 +205,7 @@
     <t>Physical</t>
   </si>
   <si>
-    <t>Player/Projectile/Stone Arrow</t>
+    <t>Scholar/StoneArrowEffect</t>
   </si>
   <si>
     <t>skill_scholar_basic_air</t>
@@ -220,7 +220,7 @@
     <t>Electric</t>
   </si>
   <si>
-    <t>Player/Projectile/Electric Arrow</t>
+    <t>Scholar/ElectricArrowEffect</t>
   </si>
   <si>
     <t>skill_scholar_basic_magic</t>
@@ -235,7 +235,19 @@
     <t>Magic</t>
   </si>
   <si>
-    <t>Player/Projectile/Magic Arrow</t>
+    <t>Scholar/MagicArrowEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_magic_upgrade</t>
+  </si>
+  <si>
+    <t>강화 마력 화살</t>
+  </si>
+  <si>
+    <t>마력 화살 보다 한 층 더 강한 강화 마력 화살 입니다.</t>
+  </si>
+  <si>
+    <t>Scholar/UpgradedMagicArrowEffect</t>
   </si>
   <si>
     <t>skill_scholar_special_fire</t>
@@ -247,7 +259,7 @@
     <t>마우스 위치에 원소 폭발을 일으켜 몰려 있는 적을 정리합니다.</t>
   </si>
   <si>
-    <t>Player/Skill/Scholar_AOE/Fire Explosion</t>
+    <t>Scholar/FireExplosionEffect</t>
   </si>
   <si>
     <t>Special</t>
@@ -259,7 +271,7 @@
     <t>냉기 폭발</t>
   </si>
   <si>
-    <t>Player/Skill/Scholar_AOE/Ice Explosion</t>
+    <t>Scholar/IceExplosionEffect</t>
   </si>
   <si>
     <t>skill_scholar_special_earth</t>
@@ -268,7 +280,7 @@
     <t>대지 폭발</t>
   </si>
   <si>
-    <t>Player/Skill/Scholar_AOE/Earth Explosion</t>
+    <t>Scholar/EarthExplosionEffect</t>
   </si>
   <si>
     <t>skill_scholar_special_air</t>
@@ -277,7 +289,7 @@
     <t>전기 폭발</t>
   </si>
   <si>
-    <t>Player/Skill/Scholar_AOE/Electric Explosion</t>
+    <t>Scholar/ElectricExplosionEffect</t>
   </si>
   <si>
     <t>skill_scholar_special_magic</t>
@@ -286,7 +298,7 @@
     <t>마력 폭발</t>
   </si>
   <si>
-    <t>Player/Skill/Scholar_AOE/Magic Explosion</t>
+    <t>Scholar/MagicExplosionEffect</t>
   </si>
   <si>
     <t>skill_scholar_ult_summonbarrier</t>
@@ -299,6 +311,9 @@
   </si>
   <si>
     <t>Ally</t>
+  </si>
+  <si>
+    <t>Scholar/Barrier</t>
   </si>
   <si>
     <t>ScholarUltBarrier</t>
@@ -410,7 +425,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -452,6 +467,10 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
@@ -460,7 +479,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,6 +490,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
       </patternFill>
     </fill>
   </fills>
@@ -494,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -525,26 +550,49 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
@@ -1267,694 +1315,710 @@
       <c r="A9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="V9" s="20"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="24">
         <v>45.0</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E10" s="24">
         <v>8.0</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F10" s="24">
         <v>30.0</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16">
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24">
         <v>4.0</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L10" s="24">
         <v>10.0</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="V9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="16">
-        <v>45.0</v>
-      </c>
-      <c r="E10" s="16">
-        <v>8.0</v>
-      </c>
-      <c r="F10" s="16">
-        <v>30.0</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16">
-        <v>4.0</v>
-      </c>
-      <c r="L10" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="M10" s="16"/>
+      <c r="M10" s="24"/>
       <c r="N10" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
       <c r="T10" s="11"/>
       <c r="U10" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="V10" s="11"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="16" t="s">
+      <c r="A11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="16">
+      <c r="B11" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="24">
         <v>45.0</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="24">
         <v>8.0</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="24">
         <v>30.0</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16">
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24">
         <v>4.0</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="24">
         <v>10.0</v>
       </c>
-      <c r="M11" s="16"/>
+      <c r="M11" s="24"/>
       <c r="N11" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
+        <v>58</v>
+      </c>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
       <c r="T11" s="11"/>
       <c r="U11" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="V11" s="11"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="16" t="s">
+      <c r="A12" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="16">
+      <c r="B12" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="24">
         <v>45.0</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="24">
         <v>8.0</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="24">
         <v>30.0</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16">
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24">
         <v>4.0</v>
       </c>
-      <c r="L12" s="16">
+      <c r="L12" s="24">
         <v>10.0</v>
       </c>
-      <c r="M12" s="16"/>
+      <c r="M12" s="24"/>
       <c r="N12" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
+        <v>63</v>
+      </c>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
       <c r="T12" s="11"/>
       <c r="U12" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="V12" s="11"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="16" t="s">
+      <c r="A13" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="B13" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="24">
         <v>45.0</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="24">
         <v>8.0</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="24">
         <v>30.0</v>
       </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16">
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24">
         <v>4.0</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="24">
         <v>10.0</v>
       </c>
-      <c r="M13" s="16"/>
+      <c r="M13" s="24"/>
       <c r="N13" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
+        <v>68</v>
+      </c>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
       <c r="T13" s="11"/>
       <c r="U13" s="12" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="V13" s="11"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16">
+      <c r="C14" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="24">
         <v>45.0</v>
       </c>
-      <c r="F14" s="16">
+      <c r="E14" s="24">
+        <v>8.0</v>
+      </c>
+      <c r="F14" s="24">
+        <v>30.0</v>
+      </c>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="L14" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="V14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24">
+        <v>45.0</v>
+      </c>
+      <c r="F15" s="24">
         <v>60.0</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G15" s="23">
         <v>8.0</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16">
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24">
         <v>5.0</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L15" s="24">
         <v>8.0</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M15" s="24">
         <v>120.0</v>
       </c>
-      <c r="N14" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="O14" s="9"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="V14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="N15" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="O15" s="9"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16">
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="V15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24">
         <v>60.0</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F16" s="24">
         <v>50.0</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="O15" s="9"/>
-      <c r="P15" s="17" t="s">
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="U16" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="V15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
       <c r="V16" s="11"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="16" t="s">
+      <c r="A17" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="16">
+      <c r="C17" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="O17" s="9"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="24">
         <v>20.0</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E18" s="24">
         <v>0.65</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F18" s="24">
         <v>0.0</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G18" s="24">
         <v>3.0</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H18" s="24">
         <v>15.0</v>
       </c>
-      <c r="I17" s="16">
+      <c r="I18" s="24">
         <v>1.0</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J18" s="24">
         <v>1.0</v>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16">
+      <c r="K18" s="24"/>
+      <c r="L18" s="24">
         <v>12.0</v>
       </c>
-      <c r="M17" s="16"/>
-      <c r="N17" s="9" t="s">
+      <c r="M18" s="24"/>
+      <c r="N18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O17" s="9" t="s">
+      <c r="O18" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="U17" s="12" t="s">
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="U18" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="V17" s="12"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="s">
+      <c r="V18" s="12"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="V19" s="12"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="V18" s="12"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="O19" s="9"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D20" s="16">
-        <v>18.0</v>
-      </c>
-      <c r="E20" s="16">
-        <v>0.55</v>
-      </c>
-      <c r="F20" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="L20" s="16">
-        <v>2.5</v>
-      </c>
-      <c r="M20" s="16"/>
-      <c r="N20" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="P20" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
       <c r="T20" s="11"/>
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B21" s="16" t="s">
+      <c r="A21" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="16">
-        <v>32.0</v>
-      </c>
-      <c r="E21" s="16">
-        <v>7.0</v>
-      </c>
-      <c r="F21" s="16">
-        <v>25.0</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16">
-        <v>3.5</v>
-      </c>
-      <c r="L21" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="M21" s="16"/>
+      <c r="C21" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="24">
+        <v>18.0</v>
+      </c>
+      <c r="E21" s="24">
+        <v>0.55</v>
+      </c>
+      <c r="F21" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24">
+        <v>2.0</v>
+      </c>
+      <c r="L21" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="M21" s="24"/>
       <c r="N21" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="12"/>
+      <c r="P21" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="24"/>
+      <c r="T21" s="11"/>
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="D22" s="16">
-        <v>90.0</v>
-      </c>
-      <c r="E22" s="16">
-        <v>45.0</v>
-      </c>
-      <c r="F22" s="16">
-        <v>50.0</v>
-      </c>
-      <c r="G22" s="16">
-        <v>2.0</v>
-      </c>
-      <c r="H22" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="I22" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="16">
-        <v>1.0</v>
-      </c>
-      <c r="K22" s="16">
-        <v>3.0</v>
-      </c>
-      <c r="L22" s="16">
-        <v>10.0</v>
-      </c>
-      <c r="M22" s="16"/>
+      <c r="B22" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D22" s="24">
+        <v>32.0</v>
+      </c>
+      <c r="E22" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="F22" s="24">
+        <v>25.0</v>
+      </c>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24">
+        <v>3.5</v>
+      </c>
+      <c r="L22" s="24">
+        <v>4.5</v>
+      </c>
+      <c r="M22" s="24"/>
       <c r="N22" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="11"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="12"/>
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="16">
-        <v>18.0</v>
-      </c>
-      <c r="E23" s="16">
-        <v>60.0</v>
-      </c>
-      <c r="F23" s="16">
-        <v>55.0</v>
-      </c>
-      <c r="G23" s="16">
-        <v>5.0</v>
-      </c>
-      <c r="H23" s="16">
-        <v>4.0</v>
-      </c>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16">
+      <c r="B23" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="24">
+        <v>90.0</v>
+      </c>
+      <c r="E23" s="24">
+        <v>45.0</v>
+      </c>
+      <c r="F23" s="24">
+        <v>50.0</v>
+      </c>
+      <c r="G23" s="24">
+        <v>2.0</v>
+      </c>
+      <c r="H23" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="I23" s="24">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="24">
         <v>1.0</v>
       </c>
-      <c r="K23" s="16">
-        <v>5.0</v>
-      </c>
-      <c r="L23" s="16">
+      <c r="K23" s="24">
+        <v>3.0</v>
+      </c>
+      <c r="L23" s="24">
         <v>10.0</v>
       </c>
-      <c r="M23" s="16"/>
+      <c r="M23" s="24"/>
       <c r="N23" s="9" t="s">
         <v>51</v>
       </c>
       <c r="O23" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
       <c r="T23" s="11"/>
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
+      <c r="A24" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="24">
+        <v>18.0</v>
+      </c>
+      <c r="E24" s="24">
+        <v>60.0</v>
+      </c>
+      <c r="F24" s="24">
+        <v>55.0</v>
+      </c>
+      <c r="G24" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="H24" s="24">
+        <v>4.0</v>
+      </c>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="K24" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="L24" s="24">
+        <v>10.0</v>
+      </c>
+      <c r="M24" s="24"/>
+      <c r="N24" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="24"/>
       <c r="T24" s="11"/>
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
@@ -6640,102 +6704,121 @@
       <c r="V219" s="11"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="18"/>
-      <c r="B220" s="18"/>
-      <c r="C220" s="18"/>
-      <c r="D220" s="18"/>
-      <c r="E220" s="18"/>
-      <c r="F220" s="18"/>
-      <c r="G220" s="18"/>
-      <c r="H220" s="18"/>
-      <c r="I220" s="18"/>
-      <c r="J220" s="18"/>
-      <c r="K220" s="18"/>
-      <c r="L220" s="18"/>
-      <c r="M220" s="18"/>
-      <c r="N220" s="18"/>
-      <c r="O220" s="18"/>
-      <c r="P220" s="18"/>
-      <c r="Q220" s="18"/>
-      <c r="R220" s="18"/>
-      <c r="S220" s="18"/>
+      <c r="A220" s="8"/>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="8"/>
+      <c r="E220" s="8"/>
+      <c r="F220" s="8"/>
+      <c r="G220" s="9"/>
+      <c r="H220" s="9"/>
+      <c r="I220" s="9"/>
+      <c r="J220" s="8"/>
+      <c r="K220" s="8"/>
+      <c r="L220" s="8"/>
+      <c r="M220" s="8"/>
+      <c r="N220" s="9"/>
+      <c r="O220" s="9"/>
+      <c r="P220" s="8"/>
+      <c r="Q220" s="9"/>
+      <c r="R220" s="9"/>
+      <c r="S220" s="9"/>
       <c r="T220" s="11"/>
       <c r="U220" s="11"/>
       <c r="V220" s="11"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="18"/>
-      <c r="B221" s="18"/>
-      <c r="C221" s="18"/>
-      <c r="D221" s="18"/>
-      <c r="E221" s="18"/>
-      <c r="F221" s="18"/>
-      <c r="G221" s="18"/>
-      <c r="H221" s="18"/>
-      <c r="I221" s="18"/>
-      <c r="J221" s="18"/>
-      <c r="K221" s="18"/>
-      <c r="L221" s="18"/>
-      <c r="M221" s="18"/>
-      <c r="N221" s="18"/>
-      <c r="O221" s="18"/>
-      <c r="P221" s="18"/>
-      <c r="Q221" s="18"/>
-      <c r="R221" s="18"/>
-      <c r="S221" s="18"/>
+      <c r="A221" s="27"/>
+      <c r="B221" s="27"/>
+      <c r="C221" s="27"/>
+      <c r="D221" s="27"/>
+      <c r="E221" s="27"/>
+      <c r="F221" s="27"/>
+      <c r="G221" s="27"/>
+      <c r="H221" s="27"/>
+      <c r="I221" s="27"/>
+      <c r="J221" s="27"/>
+      <c r="K221" s="27"/>
+      <c r="L221" s="27"/>
+      <c r="M221" s="27"/>
+      <c r="N221" s="27"/>
+      <c r="O221" s="27"/>
+      <c r="P221" s="27"/>
+      <c r="Q221" s="27"/>
+      <c r="R221" s="27"/>
+      <c r="S221" s="27"/>
       <c r="T221" s="11"/>
       <c r="U221" s="11"/>
       <c r="V221" s="11"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="18"/>
-      <c r="B222" s="18"/>
-      <c r="C222" s="18"/>
-      <c r="D222" s="18"/>
-      <c r="E222" s="18"/>
-      <c r="F222" s="18"/>
-      <c r="G222" s="18"/>
-      <c r="H222" s="18"/>
-      <c r="I222" s="18"/>
-      <c r="J222" s="18"/>
-      <c r="K222" s="18"/>
-      <c r="L222" s="18"/>
-      <c r="M222" s="18"/>
-      <c r="N222" s="18"/>
-      <c r="O222" s="18"/>
-      <c r="P222" s="18"/>
-      <c r="Q222" s="18"/>
-      <c r="R222" s="18"/>
-      <c r="S222" s="18"/>
+      <c r="A222" s="27"/>
+      <c r="B222" s="27"/>
+      <c r="C222" s="27"/>
+      <c r="D222" s="27"/>
+      <c r="E222" s="27"/>
+      <c r="F222" s="27"/>
+      <c r="G222" s="27"/>
+      <c r="H222" s="27"/>
+      <c r="I222" s="27"/>
+      <c r="J222" s="27"/>
+      <c r="K222" s="27"/>
+      <c r="L222" s="27"/>
+      <c r="M222" s="27"/>
+      <c r="N222" s="27"/>
+      <c r="O222" s="27"/>
+      <c r="P222" s="27"/>
+      <c r="Q222" s="27"/>
+      <c r="R222" s="27"/>
+      <c r="S222" s="27"/>
       <c r="T222" s="11"/>
       <c r="U222" s="11"/>
       <c r="V222" s="11"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="18"/>
-      <c r="B223" s="18"/>
-      <c r="C223" s="18"/>
-      <c r="D223" s="18"/>
-      <c r="E223" s="18"/>
-      <c r="F223" s="18"/>
-      <c r="G223" s="18"/>
-      <c r="H223" s="18"/>
-      <c r="I223" s="18"/>
-      <c r="J223" s="18"/>
-      <c r="K223" s="18"/>
-      <c r="L223" s="18"/>
-      <c r="M223" s="18"/>
-      <c r="N223" s="18"/>
-      <c r="O223" s="18"/>
-      <c r="P223" s="18"/>
-      <c r="Q223" s="18"/>
-      <c r="R223" s="18"/>
-      <c r="S223" s="18"/>
+      <c r="A223" s="27"/>
+      <c r="B223" s="27"/>
+      <c r="C223" s="27"/>
+      <c r="D223" s="27"/>
+      <c r="E223" s="27"/>
+      <c r="F223" s="27"/>
+      <c r="G223" s="27"/>
+      <c r="H223" s="27"/>
+      <c r="I223" s="27"/>
+      <c r="J223" s="27"/>
+      <c r="K223" s="27"/>
+      <c r="L223" s="27"/>
+      <c r="M223" s="27"/>
+      <c r="N223" s="27"/>
+      <c r="O223" s="27"/>
+      <c r="P223" s="27"/>
+      <c r="Q223" s="27"/>
+      <c r="R223" s="27"/>
+      <c r="S223" s="27"/>
       <c r="T223" s="11"/>
       <c r="U223" s="11"/>
       <c r="V223" s="11"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
+      <c r="A224" s="27"/>
+      <c r="B224" s="27"/>
+      <c r="C224" s="27"/>
+      <c r="D224" s="27"/>
+      <c r="E224" s="27"/>
+      <c r="F224" s="27"/>
+      <c r="G224" s="27"/>
+      <c r="H224" s="27"/>
+      <c r="I224" s="27"/>
+      <c r="J224" s="27"/>
+      <c r="K224" s="27"/>
+      <c r="L224" s="27"/>
+      <c r="M224" s="27"/>
+      <c r="N224" s="27"/>
+      <c r="O224" s="27"/>
+      <c r="P224" s="27"/>
+      <c r="Q224" s="27"/>
+      <c r="R224" s="27"/>
+      <c r="S224" s="27"/>
       <c r="T224" s="11"/>
       <c r="U224" s="11"/>
       <c r="V224" s="11"/>
@@ -10624,6 +10707,11 @@
       <c r="T1001" s="11"/>
       <c r="U1001" s="11"/>
       <c r="V1001" s="11"/>
+    </row>
+    <row r="1002" ht="15.75" customHeight="1">
+      <c r="T1002" s="11"/>
+      <c r="U1002" s="11"/>
+      <c r="V1002" s="11"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="137">
   <si>
     <t>아이디</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>buff_berserksoul_petattackspeed, buff_berserksoul_petmaxhealth, buff_berserksoul_petmovespeed</t>
+  </si>
+  <si>
+    <t>Scholar/BererkSoulEffect</t>
   </si>
   <si>
     <t>ScholarUltBerserkSoul</t>
@@ -1670,11 +1673,13 @@
       <c r="P16" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="Q16" s="24"/>
+      <c r="Q16" s="23" t="s">
+        <v>108</v>
+      </c>
       <c r="R16" s="24"/>
       <c r="S16" s="24"/>
       <c r="T16" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U16" s="12" t="s">
         <v>102</v>
@@ -1683,13 +1688,13 @@
     </row>
     <row r="17">
       <c r="A17" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -1702,7 +1707,7 @@
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
       <c r="N17" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="24"/>
@@ -1715,13 +1720,13 @@
     </row>
     <row r="18">
       <c r="A18" s="24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="24">
         <v>20.0</v>
@@ -1760,7 +1765,7 @@
       <c r="R18" s="24"/>
       <c r="S18" s="24"/>
       <c r="T18" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U18" s="12" t="s">
         <v>54</v>
@@ -1769,10 +1774,10 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
@@ -1792,7 +1797,7 @@
       <c r="R19" s="24"/>
       <c r="S19" s="24"/>
       <c r="T19" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="U19" s="12" t="s">
         <v>83</v>
@@ -1801,13 +1806,13 @@
     </row>
     <row r="20">
       <c r="A20" s="24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
@@ -1820,7 +1825,7 @@
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
       <c r="N20" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O20" s="9"/>
       <c r="P20" s="24"/>
@@ -1833,13 +1838,13 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D21" s="24">
         <v>18.0</v>
@@ -1868,7 +1873,7 @@
         <v>63</v>
       </c>
       <c r="P21" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q21" s="24"/>
       <c r="R21" s="24"/>
@@ -1879,13 +1884,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" s="24">
         <v>32.0</v>
@@ -1923,13 +1928,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D23" s="24">
         <v>90.0</v>
@@ -1975,13 +1980,13 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="24" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D24" s="24">
         <v>18.0</v>

--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이태영\Desktop\WanderSoul\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="151">
   <si>
     <t>아이디</t>
   </si>
@@ -70,416 +78,494 @@
     <t>아이콘</t>
   </si>
   <si>
+    <t>슬롯</t>
+  </si>
+  <si>
+    <t>추가 데미지</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string[]</t>
+  </si>
+  <si>
+    <t>stringSkillSlot</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>ManaCost</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>ProjectileSpeed</t>
+  </si>
+  <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>MaxProjectileCount</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>CastRange</t>
+  </si>
+  <si>
+    <t>BarrierAbsorbAmount</t>
+  </si>
+  <si>
+    <t>stringTargetType</t>
+  </si>
+  <si>
+    <t>stringDamageType</t>
+  </si>
+  <si>
+    <t>StatusEffectId</t>
+  </si>
+  <si>
+    <t>VFXPath</t>
+  </si>
+  <si>
+    <t>SFXPath</t>
+  </si>
+  <si>
+    <t>IconPath</t>
+  </si>
+  <si>
+    <t>ExecutionId</t>
+  </si>
+  <si>
+    <t>ExtraDamage</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_fire</t>
+  </si>
+  <si>
+    <t>화염 화살</t>
+  </si>
+  <si>
+    <t>화염 화살을 발사해 적중 지점 주변에 작은 폭발 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Scholar/FireArrowEffect</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_water</t>
+  </si>
+  <si>
+    <t>냉기 화살</t>
+  </si>
+  <si>
+    <t>냉기 화살을 발사해 적을 관통하고 이동을 늦추는 기본 공격입니다.</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>Scholar/IceArrowEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_earth</t>
+  </si>
+  <si>
+    <t>암석 화살</t>
+  </si>
+  <si>
+    <t>느리지만 강한 암석 화살을 발사해 높은 단일 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Scholar/StoneArrowEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_air</t>
+  </si>
+  <si>
+    <t>번개 화살</t>
+  </si>
+  <si>
+    <t>빠른 번개 화살을 짧은 간격으로 발사하는 기본 공격입니다.</t>
+  </si>
+  <si>
+    <t>Electric</t>
+  </si>
+  <si>
+    <t>Scholar/ElectricArrowEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_magic</t>
+  </si>
+  <si>
+    <t>마력 화살</t>
+  </si>
+  <si>
+    <t>균형 잡힌 마력 화살을 발사하고 일정 공격마다 강화 화살로 이어지는 기본 공격입니다.</t>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>Scholar/MagicArrowEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic_magic_upgrade</t>
+  </si>
+  <si>
+    <t>강화 마력 화살</t>
+  </si>
+  <si>
+    <t>마력 화살 보다 한 층 더 강한 강화 마력 화살 입니다.</t>
+  </si>
+  <si>
+    <t>Scholar/UpgradedMagicArrowEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_special_fire</t>
+  </si>
+  <si>
+    <t>화염 폭발</t>
+  </si>
+  <si>
+    <t>마우스 위치에 원소 폭발을 일으켜 몰려 있는 적을 정리합니다.</t>
+  </si>
+  <si>
+    <t>Scholar/FireExplosionEffect</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>skill_scholar_special_water</t>
+  </si>
+  <si>
+    <t>냉기 폭발</t>
+  </si>
+  <si>
+    <t>Scholar/IceExplosionEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_special_earth</t>
+  </si>
+  <si>
+    <t>대지 폭발</t>
+  </si>
+  <si>
+    <t>Scholar/EarthExplosionEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_special_air</t>
+  </si>
+  <si>
+    <t>전기 폭발</t>
+  </si>
+  <si>
+    <t>Scholar/ElectricExplosionEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_special_magic</t>
+  </si>
+  <si>
+    <t>마력 폭발</t>
+  </si>
+  <si>
+    <t>Scholar/MagicExplosionEffect</t>
+  </si>
+  <si>
+    <t>skill_scholar_ult_summonbarrier</t>
+  </si>
+  <si>
+    <t>결계 소환</t>
+  </si>
+  <si>
+    <t>일정 범위에 결계를 소환해 범위 내 아군이 받는 피해를 흡수합니다.</t>
+  </si>
+  <si>
+    <t>Ally</t>
+  </si>
+  <si>
+    <t>Scholar/Barrier</t>
+  </si>
+  <si>
+    <t>ScholarUltBarrier</t>
+  </si>
+  <si>
+    <t>Ultimate</t>
+  </si>
+  <si>
+    <t>skill_scholar_ult_berserksoul</t>
+  </si>
+  <si>
+    <t>소울의 공명</t>
+  </si>
+  <si>
+    <t>일정 시간 동안 동행 펫들을 크게 강화하는 학자 궁극기입니다.</t>
+  </si>
+  <si>
+    <t>Pet</t>
+  </si>
+  <si>
+    <t>buff_berserksoul_petattackspeed, buff_berserksoul_petmaxhealth, buff_berserksoul_petmovespeed</t>
+  </si>
+  <si>
+    <t>Scholar/BererkSoulEffect</t>
+  </si>
+  <si>
+    <t>ScholarUltBerserkSoul</t>
+  </si>
+  <si>
+    <t>skill_scholar_passive</t>
+  </si>
+  <si>
+    <t>영혼 탐구자</t>
+  </si>
+  <si>
+    <t>몬스터 처치 시 뒤틀린 소울 획득량이 증가하는 학자 패시브입니다.</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>skill_scholar_basic</t>
+  </si>
+  <si>
+    <t>원소 화살</t>
+  </si>
+  <si>
+    <t>펫 속성 조합에 따라 속성별 원소 화살 중 하나를 선택하는 대표 Id입니다. 기본값은 마력 화살 기준입니다.</t>
+  </si>
+  <si>
+    <t>ScholarBasic</t>
+  </si>
+  <si>
+    <t>skill_scholar_special</t>
+  </si>
+  <si>
+    <t>원소 폭발</t>
+  </si>
+  <si>
+    <t>ScholarSpecial</t>
+  </si>
+  <si>
+    <t>skill_mercenary_passive</t>
+  </si>
+  <si>
+    <t>용병의 수완</t>
+  </si>
+  <si>
+    <t>의뢰 성공 시 보상과 획득 명성이 증가하는 용병 패시브입니다.</t>
+  </si>
+  <si>
+    <t>skill_mercenary_basic_slash</t>
+  </si>
+  <si>
+    <t>곡검 베기</t>
+  </si>
+  <si>
+    <t>전방을 베어 물리 피해를 주고 출혈 상태이상을 부여할 수 있는 기본 공격입니다.</t>
+  </si>
+  <si>
+    <t>debuff_bleed</t>
+  </si>
+  <si>
+    <t>skill_mercenary_special_whip</t>
+  </si>
+  <si>
+    <t>채찍 휘두르기</t>
+  </si>
+  <si>
+    <t>넓은 전방 범위를 채찍으로 공격해 적을 경직시키고 밀어냅니다.</t>
+  </si>
+  <si>
+    <t>skill_mercenary_ult_finalblow</t>
+  </si>
+  <si>
+    <t>마무리 일격</t>
+  </si>
+  <si>
+    <t>지정 방향으로 강력한 참격을 날려 적에게 큰 물리 피해를 줍니다. 상태이상 중첩 비례 추가 피해는 스킬 코드에서 처리합니다.</t>
+  </si>
+  <si>
+    <t>skill_mercenary_ult_dancestorm</t>
+  </si>
+  <si>
+    <t>폭풍의 춤</t>
+  </si>
+  <si>
+    <t>직선 경로를 따라 이동하는 회오리를 만들어 경로 내 적에게 지속 피해를 줍니다. 끌어당김은 스킬 코드에서 처리합니다.</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_fire</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_water</t>
+  </si>
+  <si>
     <t>익스큐션 ID</t>
-  </si>
-  <si>
-    <t>슬롯</t>
-  </si>
-  <si>
-    <t>추가 데미지</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string[]</t>
-  </si>
-  <si>
-    <t>stringSkillSlot</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Cooldown</t>
-  </si>
-  <si>
-    <t>ManaCost</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>ProjectileSpeed</t>
-  </si>
-  <si>
-    <t>Pierce</t>
-  </si>
-  <si>
-    <t>MaxProjectileCount</t>
-  </si>
-  <si>
-    <t>Radius</t>
-  </si>
-  <si>
-    <t>CastRange</t>
-  </si>
-  <si>
-    <t>BarrierAbsorbAmount</t>
-  </si>
-  <si>
-    <t>stringTargetType</t>
-  </si>
-  <si>
-    <t>stringDamageType</t>
-  </si>
-  <si>
-    <t>StatusEffectId</t>
-  </si>
-  <si>
-    <t>VFXPath</t>
-  </si>
-  <si>
-    <t>SFXPath</t>
-  </si>
-  <si>
-    <t>IconPath</t>
-  </si>
-  <si>
-    <t>ExecutionId</t>
-  </si>
-  <si>
-    <t>ExtraDamage</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic_fire</t>
-  </si>
-  <si>
-    <t>화염 화살</t>
-  </si>
-  <si>
-    <t>화염 화살을 발사해 적중 지점 주변에 작은 폭발 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>Fire</t>
-  </si>
-  <si>
-    <t>Scholar/FireArrowEffect</t>
-  </si>
-  <si>
-    <t>Basic</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic_water</t>
-  </si>
-  <si>
-    <t>냉기 화살</t>
-  </si>
-  <si>
-    <t>냉기 화살을 발사해 적을 관통하고 이동을 늦추는 기본 공격입니다.</t>
-  </si>
-  <si>
-    <t>Cold</t>
-  </si>
-  <si>
-    <t>Scholar/IceArrowEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic_earth</t>
-  </si>
-  <si>
-    <t>암석 화살</t>
-  </si>
-  <si>
-    <t>느리지만 강한 암석 화살을 발사해 높은 단일 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>Physical</t>
-  </si>
-  <si>
-    <t>Scholar/StoneArrowEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic_air</t>
-  </si>
-  <si>
-    <t>번개 화살</t>
-  </si>
-  <si>
-    <t>빠른 번개 화살을 짧은 간격으로 발사하는 기본 공격입니다.</t>
-  </si>
-  <si>
-    <t>Electric</t>
-  </si>
-  <si>
-    <t>Scholar/ElectricArrowEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic_magic</t>
-  </si>
-  <si>
-    <t>마력 화살</t>
-  </si>
-  <si>
-    <t>균형 잡힌 마력 화살을 발사하고 일정 공격마다 강화 화살로 이어지는 기본 공격입니다.</t>
-  </si>
-  <si>
-    <t>Magic</t>
-  </si>
-  <si>
-    <t>Scholar/MagicArrowEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic_magic_upgrade</t>
-  </si>
-  <si>
-    <t>강화 마력 화살</t>
-  </si>
-  <si>
-    <t>마력 화살 보다 한 층 더 강한 강화 마력 화살 입니다.</t>
-  </si>
-  <si>
-    <t>Scholar/UpgradedMagicArrowEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_special_fire</t>
-  </si>
-  <si>
-    <t>화염 폭발</t>
-  </si>
-  <si>
-    <t>마우스 위치에 원소 폭발을 일으켜 몰려 있는 적을 정리합니다.</t>
-  </si>
-  <si>
-    <t>Scholar/FireExplosionEffect</t>
-  </si>
-  <si>
-    <t>Special</t>
-  </si>
-  <si>
-    <t>skill_scholar_special_water</t>
-  </si>
-  <si>
-    <t>냉기 폭발</t>
-  </si>
-  <si>
-    <t>Scholar/IceExplosionEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_special_earth</t>
-  </si>
-  <si>
-    <t>대지 폭발</t>
-  </si>
-  <si>
-    <t>Scholar/EarthExplosionEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_special_air</t>
-  </si>
-  <si>
-    <t>전기 폭발</t>
-  </si>
-  <si>
-    <t>Scholar/ElectricExplosionEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_special_magic</t>
-  </si>
-  <si>
-    <t>마력 폭발</t>
-  </si>
-  <si>
-    <t>Scholar/MagicExplosionEffect</t>
-  </si>
-  <si>
-    <t>skill_scholar_ult_summonbarrier</t>
-  </si>
-  <si>
-    <t>결계 소환</t>
-  </si>
-  <si>
-    <t>일정 범위에 결계를 소환해 범위 내 아군이 받는 피해를 흡수합니다.</t>
-  </si>
-  <si>
-    <t>Ally</t>
-  </si>
-  <si>
-    <t>Scholar/Barrier</t>
-  </si>
-  <si>
-    <t>ScholarUltBarrier</t>
-  </si>
-  <si>
-    <t>Ultimate</t>
-  </si>
-  <si>
-    <t>skill_scholar_ult_berserksoul</t>
-  </si>
-  <si>
-    <t>소울의 공명</t>
-  </si>
-  <si>
-    <t>일정 시간 동안 동행 펫들을 크게 강화하는 학자 궁극기입니다.</t>
-  </si>
-  <si>
-    <t>Pet</t>
-  </si>
-  <si>
-    <t>buff_berserksoul_petattackspeed, buff_berserksoul_petmaxhealth, buff_berserksoul_petmovespeed</t>
-  </si>
-  <si>
-    <t>Scholar/BererkSoulEffect</t>
-  </si>
-  <si>
-    <t>ScholarUltBerserkSoul</t>
-  </si>
-  <si>
-    <t>skill_scholar_passive</t>
-  </si>
-  <si>
-    <t>영혼 탐구자</t>
-  </si>
-  <si>
-    <t>몬스터 처치 시 뒤틀린 소울 획득량이 증가하는 학자 패시브입니다.</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>skill_scholar_basic</t>
-  </si>
-  <si>
-    <t>원소 화살</t>
-  </si>
-  <si>
-    <t>펫 속성 조합에 따라 속성별 원소 화살 중 하나를 선택하는 대표 Id입니다. 기본값은 마력 화살 기준입니다.</t>
-  </si>
-  <si>
-    <t>ScholarBasic</t>
-  </si>
-  <si>
-    <t>skill_scholar_special</t>
-  </si>
-  <si>
-    <t>원소 폭발</t>
-  </si>
-  <si>
-    <t>ScholarSpecial</t>
-  </si>
-  <si>
-    <t>skill_mercenary_passive</t>
-  </si>
-  <si>
-    <t>용병의 수완</t>
-  </si>
-  <si>
-    <t>의뢰 성공 시 보상과 획득 명성이 증가하는 용병 패시브입니다.</t>
-  </si>
-  <si>
-    <t>skill_mercenary_basic_slash</t>
-  </si>
-  <si>
-    <t>곡검 베기</t>
-  </si>
-  <si>
-    <t>전방을 베어 물리 피해를 주고 출혈 상태이상을 부여할 수 있는 기본 공격입니다.</t>
-  </si>
-  <si>
-    <t>debuff_bleed</t>
-  </si>
-  <si>
-    <t>skill_mercenary_special_whip</t>
-  </si>
-  <si>
-    <t>채찍 휘두르기</t>
-  </si>
-  <si>
-    <t>넓은 전방 범위를 채찍으로 공격해 적을 경직시키고 밀어냅니다.</t>
-  </si>
-  <si>
-    <t>skill_mercenary_ult_finalblow</t>
-  </si>
-  <si>
-    <t>마무리 일격</t>
-  </si>
-  <si>
-    <t>지정 방향으로 강력한 참격을 날려 적에게 큰 물리 피해를 줍니다. 상태이상 중첩 비례 추가 피해는 스킬 코드에서 처리합니다.</t>
-  </si>
-  <si>
-    <t>skill_mercenary_ult_dancestorm</t>
-  </si>
-  <si>
-    <t>폭풍의 춤</t>
-  </si>
-  <si>
-    <t>직선 경로를 따라 이동하는 회오리를 만들어 경로 내 적에게 지속 피해를 줍니다. 끌어당김은 스킬 코드에서 처리합니다.</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_earth</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_air</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic_magic</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_fire</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_water</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_earth</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_air</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special_magic</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_ult_summonbarrier_v3</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_ult_berserksoul_sample_B_charge</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_basic</t>
+  </si>
+  <si>
+    <t>Sprites/UI/Icon/skill_scholar_special</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="11">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -487,7 +573,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -503,7 +589,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -517,98 +609,95 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,7 +705,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -806,37 +895,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z1002"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.5"/>
-    <col customWidth="1" min="2" max="2" width="11.5"/>
-    <col customWidth="1" min="3" max="3" width="93.25"/>
-    <col customWidth="1" min="4" max="4" width="5.88"/>
-    <col customWidth="1" min="5" max="6" width="8.75"/>
-    <col customWidth="1" min="7" max="7" width="15.5"/>
-    <col customWidth="1" min="8" max="8" width="12.88"/>
-    <col customWidth="1" min="9" max="9" width="11.5"/>
-    <col customWidth="1" min="10" max="10" width="16.13"/>
-    <col customWidth="1" min="11" max="11" width="14.38"/>
-    <col customWidth="1" min="12" max="12" width="12.0"/>
-    <col customWidth="1" min="13" max="13" width="17.88"/>
-    <col customWidth="1" min="14" max="15" width="15.13"/>
-    <col customWidth="1" min="16" max="16" width="17.88"/>
-    <col customWidth="1" min="17" max="17" width="21.88"/>
-    <col customWidth="1" min="18" max="18" width="7.13"/>
-    <col customWidth="1" min="19" max="19" width="7.63"/>
-    <col customWidth="1" min="22" max="22" width="20.38"/>
+    <col min="1" max="1" width="25.5" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="3" max="3" width="93.25" customWidth="1"/>
+    <col min="4" max="4" width="5.875" customWidth="1"/>
+    <col min="5" max="6" width="8.75" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="11" max="11" width="14.375" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="17.875" customWidth="1"/>
+    <col min="14" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="17.875" customWidth="1"/>
+    <col min="17" max="17" width="32.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="37.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:26" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,434 +984,444 @@
         <v>18</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:26" ht="24" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" ht="24.0" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:26" ht="27.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" ht="27.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:26" ht="14.25">
+      <c r="A4" s="7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="D4" s="7">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8">
         <v>0.6</v>
       </c>
       <c r="F4" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G4" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="9">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I4" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
+      <c r="S4" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="T4" s="11"/>
       <c r="U4" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="14.25">
+      <c r="A5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="V4" s="13">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="D5" s="8">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="E5" s="8">
         <v>0.7</v>
       </c>
       <c r="F5" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="9">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="I5" s="9">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
+      <c r="S5" s="9" t="s">
+        <v>137</v>
+      </c>
       <c r="T5" s="11"/>
       <c r="U5" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V5" s="11"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="14.25">
       <c r="A6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="D6" s="8">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="E6" s="8">
         <v>0.95</v>
       </c>
       <c r="F6" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H6" s="9">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I6" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
+      <c r="S6" s="9" t="s">
+        <v>139</v>
+      </c>
       <c r="T6" s="11"/>
       <c r="U6" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V6" s="11"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="14.25">
       <c r="A7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="D7" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E7" s="8">
         <v>0.35</v>
       </c>
       <c r="F7" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G7" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H7" s="9">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="I7" s="9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
+      <c r="S7" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="T7" s="11"/>
       <c r="U7" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V7" s="11"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="14.25">
       <c r="A8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="D8" s="8">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E8" s="8">
         <v>0.65</v>
       </c>
       <c r="F8" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="9">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="I8" s="9">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="8">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P8" s="14"/>
       <c r="Q8" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
+      <c r="S8" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="T8" s="11"/>
       <c r="U8" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V8" s="11"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="14.25">
       <c r="A9" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="C9" s="15" t="s">
         <v>76</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>77</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -1338,13 +1437,13 @@
       <c r="O9" s="17"/>
       <c r="P9" s="18"/>
       <c r="Q9" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
       <c r="T9" s="20"/>
       <c r="U9" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="V9" s="20"/>
       <c r="W9" s="22"/>
@@ -1352,312 +1451,324 @@
       <c r="Y9" s="22"/>
       <c r="Z9" s="22"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="14.25">
       <c r="A10" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="C10" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>81</v>
-      </c>
       <c r="D10" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E10" s="24">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="24">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G10" s="24"/>
       <c r="H10" s="24"/>
       <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="24">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M10" s="24"/>
       <c r="N10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="P10" s="24"/>
       <c r="Q10" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
+      <c r="S10" s="28" t="s">
+        <v>142</v>
+      </c>
       <c r="T10" s="11"/>
       <c r="U10" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="V10" s="11"/>
+    </row>
+    <row r="11" spans="1:26" ht="14.25">
+      <c r="A11" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="V10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>85</v>
-      </c>
       <c r="C11" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E11" s="24">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F11" s="24">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="24"/>
       <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="24">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P11" s="24"/>
       <c r="Q11" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
+      <c r="S11" s="28" t="s">
+        <v>143</v>
+      </c>
       <c r="T11" s="11"/>
       <c r="U11" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V11" s="11"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="14.25">
       <c r="A12" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>88</v>
-      </c>
       <c r="C12" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E12" s="24">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F12" s="24">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="24"/>
       <c r="I12" s="24"/>
       <c r="J12" s="24"/>
       <c r="K12" s="24">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M12" s="24"/>
       <c r="N12" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P12" s="24"/>
       <c r="Q12" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
+      <c r="S12" s="28" t="s">
+        <v>144</v>
+      </c>
       <c r="T12" s="11"/>
       <c r="U12" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V12" s="11"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="14.25">
       <c r="A13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="24" t="s">
-        <v>91</v>
-      </c>
       <c r="C13" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E13" s="24">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F13" s="24">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
       <c r="I13" s="24"/>
       <c r="J13" s="24"/>
       <c r="K13" s="24">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M13" s="24"/>
       <c r="N13" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P13" s="24"/>
       <c r="Q13" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
+      <c r="S13" s="28" t="s">
+        <v>145</v>
+      </c>
       <c r="T13" s="11"/>
       <c r="U13" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V13" s="11"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="14.25">
       <c r="A14" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="B14" s="24" t="s">
-        <v>94</v>
-      </c>
       <c r="C14" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="E14" s="24">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F14" s="24">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="24">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P14" s="24"/>
       <c r="Q14" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
+      <c r="S14" s="28" t="s">
+        <v>146</v>
+      </c>
       <c r="T14" s="11"/>
       <c r="U14" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V14" s="11"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="13.5">
       <c r="A15" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="C15" s="24" t="s">
         <v>97</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>98</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="F15" s="24">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="G15" s="23">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H15" s="24"/>
       <c r="I15" s="24"/>
       <c r="J15" s="24"/>
       <c r="K15" s="24">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="24">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="M15" s="24">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="24"/>
       <c r="Q15" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="T15" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="12" t="s">
+      <c r="U15" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="U15" s="12" t="s">
+      <c r="V15" s="11"/>
+    </row>
+    <row r="16" spans="1:26" ht="81">
+      <c r="A16" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="V15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="s">
+      <c r="B16" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="C16" s="24" t="s">
         <v>104</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>105</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F16" s="24">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
@@ -1667,34 +1778,34 @@
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
       <c r="N16" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q16" s="23" t="s">
         <v>107</v>
-      </c>
-      <c r="Q16" s="23" t="s">
-        <v>108</v>
       </c>
       <c r="R16" s="24"/>
       <c r="S16" s="24"/>
       <c r="T16" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="V16" s="11"/>
+    </row>
+    <row r="17" spans="1:22" ht="13.5">
+      <c r="A17" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="U16" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="V16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="s">
+      <c r="B17" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="C17" s="24" t="s">
         <v>111</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>112</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -1707,77 +1818,81 @@
       <c r="L17" s="24"/>
       <c r="M17" s="24"/>
       <c r="N17" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="24"/>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
+      <c r="S17" s="24" t="s">
+        <v>148</v>
+      </c>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
       <c r="V17" s="11"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:22" ht="13.5">
       <c r="A18" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="C18" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>116</v>
-      </c>
       <c r="D18" s="24">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="E18" s="24">
         <v>0.65</v>
       </c>
       <c r="F18" s="24">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G18" s="24">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="H18" s="24">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="I18" s="24">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="24">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="24"/>
       <c r="L18" s="24">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="M18" s="24"/>
       <c r="N18" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P18" s="24"/>
       <c r="Q18" s="24"/>
       <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
+      <c r="S18" s="24" t="s">
+        <v>149</v>
+      </c>
       <c r="T18" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="U18" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="V18" s="12"/>
+    </row>
+    <row r="19" spans="1:22" ht="13.5">
+      <c r="A19" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="V18" s="12"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="s">
+      <c r="B19" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>119</v>
       </c>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
@@ -1795,24 +1910,26 @@
       <c r="P19" s="24"/>
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
+      <c r="S19" s="24" t="s">
+        <v>150</v>
+      </c>
       <c r="T19" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="V19" s="12"/>
+    </row>
+    <row r="20" spans="1:22" ht="13.5">
+      <c r="A20" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="U19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="V19" s="12"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="s">
+      <c r="B20" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="C20" s="24" t="s">
         <v>122</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>123</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
@@ -1825,7 +1942,7 @@
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
       <c r="N20" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O20" s="9"/>
       <c r="P20" s="24"/>
@@ -1836,44 +1953,44 @@
       <c r="U20" s="11"/>
       <c r="V20" s="11"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:22" ht="15.75" customHeight="1">
       <c r="A21" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="C21" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>126</v>
-      </c>
       <c r="D21" s="24">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="E21" s="24">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="F21" s="24">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
       <c r="I21" s="24"/>
       <c r="J21" s="24"/>
       <c r="K21" s="24">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="24">
         <v>2.5</v>
       </c>
       <c r="M21" s="24"/>
       <c r="N21" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P21" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q21" s="24"/>
       <c r="R21" s="24"/>
@@ -1882,24 +1999,24 @@
       <c r="U21" s="11"/>
       <c r="V21" s="11"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:22" ht="15.75" customHeight="1">
       <c r="A22" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="C22" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>130</v>
-      </c>
       <c r="D22" s="24">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="E22" s="24">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="24">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
@@ -1913,10 +2030,10 @@
       </c>
       <c r="M22" s="24"/>
       <c r="N22" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P22" s="24"/>
       <c r="Q22" s="24"/>
@@ -1926,49 +2043,49 @@
       <c r="U22" s="11"/>
       <c r="V22" s="11"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:22" ht="15.75" customHeight="1">
       <c r="A23" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="C23" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>133</v>
-      </c>
       <c r="D23" s="24">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="E23" s="24">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="F23" s="24">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="G23" s="24">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="H23" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="I23" s="24">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="24">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="24">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M23" s="24"/>
       <c r="N23" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
@@ -1978,47 +2095,47 @@
       <c r="U23" s="11"/>
       <c r="V23" s="11"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:22" ht="15.75" customHeight="1">
       <c r="A24" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="C24" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>136</v>
-      </c>
       <c r="D24" s="24">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="E24" s="24">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="F24" s="24">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="G24" s="24">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H24" s="24">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I24" s="24"/>
       <c r="J24" s="24">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="24">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="L24" s="24">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="M24" s="24"/>
       <c r="N24" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P24" s="24"/>
       <c r="Q24" s="24"/>
@@ -2028,7 +2145,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="11"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:22" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -2052,7 +2169,7 @@
       <c r="U25" s="11"/>
       <c r="V25" s="11"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:22" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -2076,7 +2193,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:22" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -2100,7 +2217,7 @@
       <c r="U27" s="11"/>
       <c r="V27" s="11"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:22" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -2124,7 +2241,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="11"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:22" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -2148,7 +2265,7 @@
       <c r="U29" s="11"/>
       <c r="V29" s="11"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:22" ht="15.75" customHeight="1">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -2172,7 +2289,7 @@
       <c r="U30" s="11"/>
       <c r="V30" s="11"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:22" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -2196,7 +2313,7 @@
       <c r="U31" s="11"/>
       <c r="V31" s="11"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:22" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -2220,7 +2337,7 @@
       <c r="U32" s="11"/>
       <c r="V32" s="11"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:22" ht="15.75" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -2244,7 +2361,7 @@
       <c r="U33" s="11"/>
       <c r="V33" s="11"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:22" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -2268,7 +2385,7 @@
       <c r="U34" s="11"/>
       <c r="V34" s="11"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:22" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -2292,7 +2409,7 @@
       <c r="U35" s="11"/>
       <c r="V35" s="11"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:22" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2316,7 +2433,7 @@
       <c r="U36" s="11"/>
       <c r="V36" s="11"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:22" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -2340,7 +2457,7 @@
       <c r="U37" s="11"/>
       <c r="V37" s="11"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:22" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -2364,7 +2481,7 @@
       <c r="U38" s="11"/>
       <c r="V38" s="11"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:22" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2388,7 +2505,7 @@
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:22" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -2412,7 +2529,7 @@
       <c r="U40" s="11"/>
       <c r="V40" s="11"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:22" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -2436,7 +2553,7 @@
       <c r="U41" s="11"/>
       <c r="V41" s="11"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:22" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2460,7 +2577,7 @@
       <c r="U42" s="11"/>
       <c r="V42" s="11"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:22" ht="15.75" customHeight="1">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -2484,7 +2601,7 @@
       <c r="U43" s="11"/>
       <c r="V43" s="11"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:22" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -2508,7 +2625,7 @@
       <c r="U44" s="11"/>
       <c r="V44" s="11"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:22" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -2532,7 +2649,7 @@
       <c r="U45" s="11"/>
       <c r="V45" s="11"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:22" ht="15.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -2556,7 +2673,7 @@
       <c r="U46" s="11"/>
       <c r="V46" s="11"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:22" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -2580,7 +2697,7 @@
       <c r="U47" s="11"/>
       <c r="V47" s="11"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:22" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -2604,7 +2721,7 @@
       <c r="U48" s="11"/>
       <c r="V48" s="11"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:22" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -2628,7 +2745,7 @@
       <c r="U49" s="11"/>
       <c r="V49" s="11"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:22" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -2652,7 +2769,7 @@
       <c r="U50" s="11"/>
       <c r="V50" s="11"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:22" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -2676,7 +2793,7 @@
       <c r="U51" s="11"/>
       <c r="V51" s="11"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:22" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -2700,7 +2817,7 @@
       <c r="U52" s="11"/>
       <c r="V52" s="11"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:22" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -2724,7 +2841,7 @@
       <c r="U53" s="11"/>
       <c r="V53" s="11"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:22" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -2748,7 +2865,7 @@
       <c r="U54" s="11"/>
       <c r="V54" s="11"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:22" ht="15.75" customHeight="1">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -2772,7 +2889,7 @@
       <c r="U55" s="11"/>
       <c r="V55" s="11"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:22" ht="15.75" customHeight="1">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -2796,7 +2913,7 @@
       <c r="U56" s="11"/>
       <c r="V56" s="11"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:22" ht="15.75" customHeight="1">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -2820,7 +2937,7 @@
       <c r="U57" s="11"/>
       <c r="V57" s="11"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:22" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -2844,7 +2961,7 @@
       <c r="U58" s="11"/>
       <c r="V58" s="11"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:22" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -2868,7 +2985,7 @@
       <c r="U59" s="11"/>
       <c r="V59" s="11"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:22" ht="15.75" customHeight="1">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -2892,7 +3009,7 @@
       <c r="U60" s="11"/>
       <c r="V60" s="11"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:22" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -2916,7 +3033,7 @@
       <c r="U61" s="11"/>
       <c r="V61" s="11"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:22" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -2940,7 +3057,7 @@
       <c r="U62" s="11"/>
       <c r="V62" s="11"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:22" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -2964,7 +3081,7 @@
       <c r="U63" s="11"/>
       <c r="V63" s="11"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:22" ht="15.75" customHeight="1">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -2988,7 +3105,7 @@
       <c r="U64" s="11"/>
       <c r="V64" s="11"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:22" ht="15.75" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -3012,7 +3129,7 @@
       <c r="U65" s="11"/>
       <c r="V65" s="11"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:22" ht="15.75" customHeight="1">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -3036,7 +3153,7 @@
       <c r="U66" s="11"/>
       <c r="V66" s="11"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:22" ht="15.75" customHeight="1">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -3060,7 +3177,7 @@
       <c r="U67" s="11"/>
       <c r="V67" s="11"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:22" ht="15.75" customHeight="1">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -3084,7 +3201,7 @@
       <c r="U68" s="11"/>
       <c r="V68" s="11"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:22" ht="15.75" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -3108,7 +3225,7 @@
       <c r="U69" s="11"/>
       <c r="V69" s="11"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:22" ht="15.75" customHeight="1">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -3132,7 +3249,7 @@
       <c r="U70" s="11"/>
       <c r="V70" s="11"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:22" ht="15.75" customHeight="1">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -3156,7 +3273,7 @@
       <c r="U71" s="11"/>
       <c r="V71" s="11"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:22" ht="15.75" customHeight="1">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -3180,7 +3297,7 @@
       <c r="U72" s="11"/>
       <c r="V72" s="11"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:22" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -3204,7 +3321,7 @@
       <c r="U73" s="11"/>
       <c r="V73" s="11"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:22" ht="15.75" customHeight="1">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -3228,7 +3345,7 @@
       <c r="U74" s="11"/>
       <c r="V74" s="11"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:22" ht="15.75" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -3252,7 +3369,7 @@
       <c r="U75" s="11"/>
       <c r="V75" s="11"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:22" ht="15.75" customHeight="1">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -3276,7 +3393,7 @@
       <c r="U76" s="11"/>
       <c r="V76" s="11"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:22" ht="15.75" customHeight="1">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -3300,7 +3417,7 @@
       <c r="U77" s="11"/>
       <c r="V77" s="11"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:22" ht="15.75" customHeight="1">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -3324,7 +3441,7 @@
       <c r="U78" s="11"/>
       <c r="V78" s="11"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:22" ht="15.75" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -3348,7 +3465,7 @@
       <c r="U79" s="11"/>
       <c r="V79" s="11"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:22" ht="15.75" customHeight="1">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -3372,7 +3489,7 @@
       <c r="U80" s="11"/>
       <c r="V80" s="11"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:22" ht="15.75" customHeight="1">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -3396,7 +3513,7 @@
       <c r="U81" s="11"/>
       <c r="V81" s="11"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:22" ht="15.75" customHeight="1">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -3420,7 +3537,7 @@
       <c r="U82" s="11"/>
       <c r="V82" s="11"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:22" ht="15.75" customHeight="1">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -3444,7 +3561,7 @@
       <c r="U83" s="11"/>
       <c r="V83" s="11"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:22" ht="15.75" customHeight="1">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -3468,7 +3585,7 @@
       <c r="U84" s="11"/>
       <c r="V84" s="11"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:22" ht="15.75" customHeight="1">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -3492,7 +3609,7 @@
       <c r="U85" s="11"/>
       <c r="V85" s="11"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:22" ht="15.75" customHeight="1">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -3516,7 +3633,7 @@
       <c r="U86" s="11"/>
       <c r="V86" s="11"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:22" ht="15.75" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -3540,7 +3657,7 @@
       <c r="U87" s="11"/>
       <c r="V87" s="11"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:22" ht="15.75" customHeight="1">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -3564,7 +3681,7 @@
       <c r="U88" s="11"/>
       <c r="V88" s="11"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:22" ht="15.75" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -3588,7 +3705,7 @@
       <c r="U89" s="11"/>
       <c r="V89" s="11"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:22" ht="15.75" customHeight="1">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -3612,7 +3729,7 @@
       <c r="U90" s="11"/>
       <c r="V90" s="11"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:22" ht="15.75" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -3636,7 +3753,7 @@
       <c r="U91" s="11"/>
       <c r="V91" s="11"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:22" ht="15.75" customHeight="1">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -3660,7 +3777,7 @@
       <c r="U92" s="11"/>
       <c r="V92" s="11"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:22" ht="15.75" customHeight="1">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -3684,7 +3801,7 @@
       <c r="U93" s="11"/>
       <c r="V93" s="11"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:22" ht="15.75" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -3708,7 +3825,7 @@
       <c r="U94" s="11"/>
       <c r="V94" s="11"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:22" ht="15.75" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -3732,7 +3849,7 @@
       <c r="U95" s="11"/>
       <c r="V95" s="11"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:22" ht="15.75" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -3756,7 +3873,7 @@
       <c r="U96" s="11"/>
       <c r="V96" s="11"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:22" ht="15.75" customHeight="1">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -3780,7 +3897,7 @@
       <c r="U97" s="11"/>
       <c r="V97" s="11"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:22" ht="15.75" customHeight="1">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -3804,7 +3921,7 @@
       <c r="U98" s="11"/>
       <c r="V98" s="11"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:22" ht="15.75" customHeight="1">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -3828,7 +3945,7 @@
       <c r="U99" s="11"/>
       <c r="V99" s="11"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:22" ht="15.75" customHeight="1">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -3852,7 +3969,7 @@
       <c r="U100" s="11"/>
       <c r="V100" s="11"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:22" ht="15.75" customHeight="1">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -3876,7 +3993,7 @@
       <c r="U101" s="11"/>
       <c r="V101" s="11"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:22" ht="15.75" customHeight="1">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -3900,7 +4017,7 @@
       <c r="U102" s="11"/>
       <c r="V102" s="11"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:22" ht="15.75" customHeight="1">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -3924,7 +4041,7 @@
       <c r="U103" s="11"/>
       <c r="V103" s="11"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:22" ht="15.75" customHeight="1">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -3948,7 +4065,7 @@
       <c r="U104" s="11"/>
       <c r="V104" s="11"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:22" ht="15.75" customHeight="1">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -3972,7 +4089,7 @@
       <c r="U105" s="11"/>
       <c r="V105" s="11"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:22" ht="15.75" customHeight="1">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -3996,7 +4113,7 @@
       <c r="U106" s="11"/>
       <c r="V106" s="11"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:22" ht="15.75" customHeight="1">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -4020,7 +4137,7 @@
       <c r="U107" s="11"/>
       <c r="V107" s="11"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:22" ht="15.75" customHeight="1">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -4044,7 +4161,7 @@
       <c r="U108" s="11"/>
       <c r="V108" s="11"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:22" ht="15.75" customHeight="1">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -4068,7 +4185,7 @@
       <c r="U109" s="11"/>
       <c r="V109" s="11"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:22" ht="15.75" customHeight="1">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -4092,7 +4209,7 @@
       <c r="U110" s="11"/>
       <c r="V110" s="11"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:22" ht="15.75" customHeight="1">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -4116,7 +4233,7 @@
       <c r="U111" s="11"/>
       <c r="V111" s="11"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:22" ht="15.75" customHeight="1">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -4140,7 +4257,7 @@
       <c r="U112" s="11"/>
       <c r="V112" s="11"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:22" ht="15.75" customHeight="1">
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
@@ -4164,7 +4281,7 @@
       <c r="U113" s="11"/>
       <c r="V113" s="11"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:22" ht="15.75" customHeight="1">
       <c r="A114" s="8"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
@@ -4188,7 +4305,7 @@
       <c r="U114" s="11"/>
       <c r="V114" s="11"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:22" ht="15.75" customHeight="1">
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
@@ -4212,7 +4329,7 @@
       <c r="U115" s="11"/>
       <c r="V115" s="11"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:22" ht="15.75" customHeight="1">
       <c r="A116" s="8"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
@@ -4236,7 +4353,7 @@
       <c r="U116" s="11"/>
       <c r="V116" s="11"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:22" ht="15.75" customHeight="1">
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
@@ -4260,7 +4377,7 @@
       <c r="U117" s="11"/>
       <c r="V117" s="11"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:22" ht="15.75" customHeight="1">
       <c r="A118" s="8"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
@@ -4284,7 +4401,7 @@
       <c r="U118" s="11"/>
       <c r="V118" s="11"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:22" ht="15.75" customHeight="1">
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
@@ -4308,7 +4425,7 @@
       <c r="U119" s="11"/>
       <c r="V119" s="11"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:22" ht="15.75" customHeight="1">
       <c r="A120" s="8"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
@@ -4332,7 +4449,7 @@
       <c r="U120" s="11"/>
       <c r="V120" s="11"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:22" ht="15.75" customHeight="1">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
@@ -4356,7 +4473,7 @@
       <c r="U121" s="11"/>
       <c r="V121" s="11"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:22" ht="15.75" customHeight="1">
       <c r="A122" s="8"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -4380,7 +4497,7 @@
       <c r="U122" s="11"/>
       <c r="V122" s="11"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:22" ht="15.75" customHeight="1">
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
@@ -4404,7 +4521,7 @@
       <c r="U123" s="11"/>
       <c r="V123" s="11"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:22" ht="15.75" customHeight="1">
       <c r="A124" s="8"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
@@ -4428,7 +4545,7 @@
       <c r="U124" s="11"/>
       <c r="V124" s="11"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:22" ht="15.75" customHeight="1">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
@@ -4452,7 +4569,7 @@
       <c r="U125" s="11"/>
       <c r="V125" s="11"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:22" ht="15.75" customHeight="1">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
@@ -4476,7 +4593,7 @@
       <c r="U126" s="11"/>
       <c r="V126" s="11"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:22" ht="15.75" customHeight="1">
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
@@ -4500,7 +4617,7 @@
       <c r="U127" s="11"/>
       <c r="V127" s="11"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:22" ht="15.75" customHeight="1">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
@@ -4524,7 +4641,7 @@
       <c r="U128" s="11"/>
       <c r="V128" s="11"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:22" ht="15.75" customHeight="1">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
@@ -4548,7 +4665,7 @@
       <c r="U129" s="11"/>
       <c r="V129" s="11"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:22" ht="15.75" customHeight="1">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
@@ -4572,7 +4689,7 @@
       <c r="U130" s="11"/>
       <c r="V130" s="11"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:22" ht="15.75" customHeight="1">
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
@@ -4596,7 +4713,7 @@
       <c r="U131" s="11"/>
       <c r="V131" s="11"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:22" ht="15.75" customHeight="1">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -4620,7 +4737,7 @@
       <c r="U132" s="11"/>
       <c r="V132" s="11"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:22" ht="15.75" customHeight="1">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -4644,7 +4761,7 @@
       <c r="U133" s="11"/>
       <c r="V133" s="11"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:22" ht="15.75" customHeight="1">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -4668,7 +4785,7 @@
       <c r="U134" s="11"/>
       <c r="V134" s="11"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:22" ht="15.75" customHeight="1">
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -4692,7 +4809,7 @@
       <c r="U135" s="11"/>
       <c r="V135" s="11"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:22" ht="15.75" customHeight="1">
       <c r="A136" s="8"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -4716,7 +4833,7 @@
       <c r="U136" s="11"/>
       <c r="V136" s="11"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:22" ht="15.75" customHeight="1">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -4740,7 +4857,7 @@
       <c r="U137" s="11"/>
       <c r="V137" s="11"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:22" ht="15.75" customHeight="1">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -4764,7 +4881,7 @@
       <c r="U138" s="11"/>
       <c r="V138" s="11"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:22" ht="15.75" customHeight="1">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
@@ -4788,7 +4905,7 @@
       <c r="U139" s="11"/>
       <c r="V139" s="11"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:22" ht="15.75" customHeight="1">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
@@ -4812,7 +4929,7 @@
       <c r="U140" s="11"/>
       <c r="V140" s="11"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:22" ht="15.75" customHeight="1">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
@@ -4836,7 +4953,7 @@
       <c r="U141" s="11"/>
       <c r="V141" s="11"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:22" ht="15.75" customHeight="1">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
@@ -4860,7 +4977,7 @@
       <c r="U142" s="11"/>
       <c r="V142" s="11"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:22" ht="15.75" customHeight="1">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
@@ -4884,7 +5001,7 @@
       <c r="U143" s="11"/>
       <c r="V143" s="11"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:22" ht="15.75" customHeight="1">
       <c r="A144" s="8"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
@@ -4908,7 +5025,7 @@
       <c r="U144" s="11"/>
       <c r="V144" s="11"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:22" ht="15.75" customHeight="1">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
@@ -4932,7 +5049,7 @@
       <c r="U145" s="11"/>
       <c r="V145" s="11"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:22" ht="15.75" customHeight="1">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
@@ -4956,7 +5073,7 @@
       <c r="U146" s="11"/>
       <c r="V146" s="11"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:22" ht="15.75" customHeight="1">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -4980,7 +5097,7 @@
       <c r="U147" s="11"/>
       <c r="V147" s="11"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:22" ht="15.75" customHeight="1">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
@@ -5004,7 +5121,7 @@
       <c r="U148" s="11"/>
       <c r="V148" s="11"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:22" ht="15.75" customHeight="1">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -5028,7 +5145,7 @@
       <c r="U149" s="11"/>
       <c r="V149" s="11"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:22" ht="15.75" customHeight="1">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -5052,7 +5169,7 @@
       <c r="U150" s="11"/>
       <c r="V150" s="11"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:22" ht="15.75" customHeight="1">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -5076,7 +5193,7 @@
       <c r="U151" s="11"/>
       <c r="V151" s="11"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:22" ht="15.75" customHeight="1">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -5100,7 +5217,7 @@
       <c r="U152" s="11"/>
       <c r="V152" s="11"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:22" ht="15.75" customHeight="1">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -5124,7 +5241,7 @@
       <c r="U153" s="11"/>
       <c r="V153" s="11"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:22" ht="15.75" customHeight="1">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -5148,7 +5265,7 @@
       <c r="U154" s="11"/>
       <c r="V154" s="11"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:22" ht="15.75" customHeight="1">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -5172,7 +5289,7 @@
       <c r="U155" s="11"/>
       <c r="V155" s="11"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:22" ht="15.75" customHeight="1">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -5196,7 +5313,7 @@
       <c r="U156" s="11"/>
       <c r="V156" s="11"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:22" ht="15.75" customHeight="1">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -5220,7 +5337,7 @@
       <c r="U157" s="11"/>
       <c r="V157" s="11"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:22" ht="15.75" customHeight="1">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -5244,7 +5361,7 @@
       <c r="U158" s="11"/>
       <c r="V158" s="11"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:22" ht="15.75" customHeight="1">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -5268,7 +5385,7 @@
       <c r="U159" s="11"/>
       <c r="V159" s="11"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:22" ht="15.75" customHeight="1">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -5292,7 +5409,7 @@
       <c r="U160" s="11"/>
       <c r="V160" s="11"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:22" ht="15.75" customHeight="1">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -5316,7 +5433,7 @@
       <c r="U161" s="11"/>
       <c r="V161" s="11"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:22" ht="15.75" customHeight="1">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -5340,7 +5457,7 @@
       <c r="U162" s="11"/>
       <c r="V162" s="11"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:22" ht="15.75" customHeight="1">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -5364,7 +5481,7 @@
       <c r="U163" s="11"/>
       <c r="V163" s="11"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:22" ht="15.75" customHeight="1">
       <c r="A164" s="8"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -5388,7 +5505,7 @@
       <c r="U164" s="11"/>
       <c r="V164" s="11"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:22" ht="15.75" customHeight="1">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
@@ -5412,7 +5529,7 @@
       <c r="U165" s="11"/>
       <c r="V165" s="11"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:22" ht="15.75" customHeight="1">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
@@ -5436,7 +5553,7 @@
       <c r="U166" s="11"/>
       <c r="V166" s="11"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:22" ht="15.75" customHeight="1">
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
@@ -5460,7 +5577,7 @@
       <c r="U167" s="11"/>
       <c r="V167" s="11"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:22" ht="15.75" customHeight="1">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
@@ -5484,7 +5601,7 @@
       <c r="U168" s="11"/>
       <c r="V168" s="11"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:22" ht="15.75" customHeight="1">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
@@ -5508,7 +5625,7 @@
       <c r="U169" s="11"/>
       <c r="V169" s="11"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:22" ht="15.75" customHeight="1">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
@@ -5532,7 +5649,7 @@
       <c r="U170" s="11"/>
       <c r="V170" s="11"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:22" ht="15.75" customHeight="1">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
@@ -5556,7 +5673,7 @@
       <c r="U171" s="11"/>
       <c r="V171" s="11"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:22" ht="15.75" customHeight="1">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
@@ -5580,7 +5697,7 @@
       <c r="U172" s="11"/>
       <c r="V172" s="11"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:22" ht="15.75" customHeight="1">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
@@ -5604,7 +5721,7 @@
       <c r="U173" s="11"/>
       <c r="V173" s="11"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:22" ht="15.75" customHeight="1">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
@@ -5628,7 +5745,7 @@
       <c r="U174" s="11"/>
       <c r="V174" s="11"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:22" ht="15.75" customHeight="1">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
@@ -5652,7 +5769,7 @@
       <c r="U175" s="11"/>
       <c r="V175" s="11"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:22" ht="15.75" customHeight="1">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
@@ -5676,7 +5793,7 @@
       <c r="U176" s="11"/>
       <c r="V176" s="11"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:22" ht="15.75" customHeight="1">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
@@ -5700,7 +5817,7 @@
       <c r="U177" s="11"/>
       <c r="V177" s="11"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:22" ht="15.75" customHeight="1">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
@@ -5724,7 +5841,7 @@
       <c r="U178" s="11"/>
       <c r="V178" s="11"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:22" ht="15.75" customHeight="1">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
@@ -5748,7 +5865,7 @@
       <c r="U179" s="11"/>
       <c r="V179" s="11"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:22" ht="15.75" customHeight="1">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
@@ -5772,7 +5889,7 @@
       <c r="U180" s="11"/>
       <c r="V180" s="11"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:22" ht="15.75" customHeight="1">
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
@@ -5796,7 +5913,7 @@
       <c r="U181" s="11"/>
       <c r="V181" s="11"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:22" ht="15.75" customHeight="1">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
@@ -5820,7 +5937,7 @@
       <c r="U182" s="11"/>
       <c r="V182" s="11"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:22" ht="15.75" customHeight="1">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
@@ -5844,7 +5961,7 @@
       <c r="U183" s="11"/>
       <c r="V183" s="11"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:22" ht="15.75" customHeight="1">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
@@ -5868,7 +5985,7 @@
       <c r="U184" s="11"/>
       <c r="V184" s="11"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:22" ht="15.75" customHeight="1">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
@@ -5892,7 +6009,7 @@
       <c r="U185" s="11"/>
       <c r="V185" s="11"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:22" ht="15.75" customHeight="1">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
@@ -5916,7 +6033,7 @@
       <c r="U186" s="11"/>
       <c r="V186" s="11"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:22" ht="15.75" customHeight="1">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
@@ -5940,7 +6057,7 @@
       <c r="U187" s="11"/>
       <c r="V187" s="11"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:22" ht="15.75" customHeight="1">
       <c r="A188" s="8"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -5964,7 +6081,7 @@
       <c r="U188" s="11"/>
       <c r="V188" s="11"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:22" ht="15.75" customHeight="1">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
@@ -5988,7 +6105,7 @@
       <c r="U189" s="11"/>
       <c r="V189" s="11"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:22" ht="15.75" customHeight="1">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -6012,7 +6129,7 @@
       <c r="U190" s="11"/>
       <c r="V190" s="11"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:22" ht="15.75" customHeight="1">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -6036,7 +6153,7 @@
       <c r="U191" s="11"/>
       <c r="V191" s="11"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:22" ht="15.75" customHeight="1">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -6060,7 +6177,7 @@
       <c r="U192" s="11"/>
       <c r="V192" s="11"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:22" ht="15.75" customHeight="1">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
@@ -6084,7 +6201,7 @@
       <c r="U193" s="11"/>
       <c r="V193" s="11"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:22" ht="15.75" customHeight="1">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
@@ -6108,7 +6225,7 @@
       <c r="U194" s="11"/>
       <c r="V194" s="11"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:22" ht="15.75" customHeight="1">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
@@ -6132,7 +6249,7 @@
       <c r="U195" s="11"/>
       <c r="V195" s="11"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:22" ht="15.75" customHeight="1">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
@@ -6156,7 +6273,7 @@
       <c r="U196" s="11"/>
       <c r="V196" s="11"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:22" ht="15.75" customHeight="1">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
@@ -6180,7 +6297,7 @@
       <c r="U197" s="11"/>
       <c r="V197" s="11"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:22" ht="15.75" customHeight="1">
       <c r="A198" s="8"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
@@ -6204,7 +6321,7 @@
       <c r="U198" s="11"/>
       <c r="V198" s="11"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:22" ht="15.75" customHeight="1">
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
@@ -6228,7 +6345,7 @@
       <c r="U199" s="11"/>
       <c r="V199" s="11"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:22" ht="15.75" customHeight="1">
       <c r="A200" s="8"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
@@ -6252,7 +6369,7 @@
       <c r="U200" s="11"/>
       <c r="V200" s="11"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:22" ht="15.75" customHeight="1">
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
@@ -6276,7 +6393,7 @@
       <c r="U201" s="11"/>
       <c r="V201" s="11"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:22" ht="15.75" customHeight="1">
       <c r="A202" s="8"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
@@ -6300,7 +6417,7 @@
       <c r="U202" s="11"/>
       <c r="V202" s="11"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:22" ht="15.75" customHeight="1">
       <c r="A203" s="8"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
@@ -6324,7 +6441,7 @@
       <c r="U203" s="11"/>
       <c r="V203" s="11"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:22" ht="15.75" customHeight="1">
       <c r="A204" s="8"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
@@ -6348,7 +6465,7 @@
       <c r="U204" s="11"/>
       <c r="V204" s="11"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:22" ht="15.75" customHeight="1">
       <c r="A205" s="8"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
@@ -6372,7 +6489,7 @@
       <c r="U205" s="11"/>
       <c r="V205" s="11"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:22" ht="15.75" customHeight="1">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
@@ -6396,7 +6513,7 @@
       <c r="U206" s="11"/>
       <c r="V206" s="11"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:22" ht="15.75" customHeight="1">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
@@ -6420,7 +6537,7 @@
       <c r="U207" s="11"/>
       <c r="V207" s="11"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:22" ht="15.75" customHeight="1">
       <c r="A208" s="8"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
@@ -6444,7 +6561,7 @@
       <c r="U208" s="11"/>
       <c r="V208" s="11"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:22" ht="15.75" customHeight="1">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
@@ -6468,7 +6585,7 @@
       <c r="U209" s="11"/>
       <c r="V209" s="11"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:22" ht="15.75" customHeight="1">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
@@ -6492,7 +6609,7 @@
       <c r="U210" s="11"/>
       <c r="V210" s="11"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:22" ht="15.75" customHeight="1">
       <c r="A211" s="8"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
@@ -6516,7 +6633,7 @@
       <c r="U211" s="11"/>
       <c r="V211" s="11"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:22" ht="15.75" customHeight="1">
       <c r="A212" s="8"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
@@ -6540,7 +6657,7 @@
       <c r="U212" s="11"/>
       <c r="V212" s="11"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:22" ht="15.75" customHeight="1">
       <c r="A213" s="8"/>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
@@ -6564,7 +6681,7 @@
       <c r="U213" s="11"/>
       <c r="V213" s="11"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:22" ht="15.75" customHeight="1">
       <c r="A214" s="8"/>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
@@ -6588,7 +6705,7 @@
       <c r="U214" s="11"/>
       <c r="V214" s="11"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:22" ht="15.75" customHeight="1">
       <c r="A215" s="8"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
@@ -6612,7 +6729,7 @@
       <c r="U215" s="11"/>
       <c r="V215" s="11"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:22" ht="15.75" customHeight="1">
       <c r="A216" s="8"/>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
@@ -6636,7 +6753,7 @@
       <c r="U216" s="11"/>
       <c r="V216" s="11"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:22" ht="15.75" customHeight="1">
       <c r="A217" s="8"/>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
@@ -6660,7 +6777,7 @@
       <c r="U217" s="11"/>
       <c r="V217" s="11"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:22" ht="15.75" customHeight="1">
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
@@ -6684,7 +6801,7 @@
       <c r="U218" s="11"/>
       <c r="V218" s="11"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:22" ht="15.75" customHeight="1">
       <c r="A219" s="8"/>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
@@ -6708,7 +6825,7 @@
       <c r="U219" s="11"/>
       <c r="V219" s="11"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:22" ht="15.75" customHeight="1">
       <c r="A220" s="8"/>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
@@ -6732,7 +6849,7 @@
       <c r="U220" s="11"/>
       <c r="V220" s="11"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="1:22" ht="15.75" customHeight="1">
       <c r="A221" s="27"/>
       <c r="B221" s="27"/>
       <c r="C221" s="27"/>
@@ -6756,7 +6873,7 @@
       <c r="U221" s="11"/>
       <c r="V221" s="11"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="1:22" ht="15.75" customHeight="1">
       <c r="A222" s="27"/>
       <c r="B222" s="27"/>
       <c r="C222" s="27"/>
@@ -6780,7 +6897,7 @@
       <c r="U222" s="11"/>
       <c r="V222" s="11"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="1:22" ht="15.75" customHeight="1">
       <c r="A223" s="27"/>
       <c r="B223" s="27"/>
       <c r="C223" s="27"/>
@@ -6804,7 +6921,7 @@
       <c r="U223" s="11"/>
       <c r="V223" s="11"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="1:22" ht="15.75" customHeight="1">
       <c r="A224" s="27"/>
       <c r="B224" s="27"/>
       <c r="C224" s="27"/>
@@ -6828,3900 +6945,3899 @@
       <c r="U224" s="11"/>
       <c r="V224" s="11"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="20:22" ht="15.75" customHeight="1">
       <c r="T225" s="11"/>
       <c r="U225" s="11"/>
       <c r="V225" s="11"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="20:22" ht="15.75" customHeight="1">
       <c r="T226" s="11"/>
       <c r="U226" s="11"/>
       <c r="V226" s="11"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="20:22" ht="15.75" customHeight="1">
       <c r="T227" s="11"/>
       <c r="U227" s="11"/>
       <c r="V227" s="11"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="20:22" ht="15.75" customHeight="1">
       <c r="T228" s="11"/>
       <c r="U228" s="11"/>
       <c r="V228" s="11"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="20:22" ht="15.75" customHeight="1">
       <c r="T229" s="11"/>
       <c r="U229" s="11"/>
       <c r="V229" s="11"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="20:22" ht="15.75" customHeight="1">
       <c r="T230" s="11"/>
       <c r="U230" s="11"/>
       <c r="V230" s="11"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="20:22" ht="15.75" customHeight="1">
       <c r="T231" s="11"/>
       <c r="U231" s="11"/>
       <c r="V231" s="11"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="20:22" ht="15.75" customHeight="1">
       <c r="T232" s="11"/>
       <c r="U232" s="11"/>
       <c r="V232" s="11"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="20:22" ht="15.75" customHeight="1">
       <c r="T233" s="11"/>
       <c r="U233" s="11"/>
       <c r="V233" s="11"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="20:22" ht="15.75" customHeight="1">
       <c r="T234" s="11"/>
       <c r="U234" s="11"/>
       <c r="V234" s="11"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="20:22" ht="15.75" customHeight="1">
       <c r="T235" s="11"/>
       <c r="U235" s="11"/>
       <c r="V235" s="11"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="20:22" ht="15.75" customHeight="1">
       <c r="T236" s="11"/>
       <c r="U236" s="11"/>
       <c r="V236" s="11"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="20:22" ht="15.75" customHeight="1">
       <c r="T237" s="11"/>
       <c r="U237" s="11"/>
       <c r="V237" s="11"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="20:22" ht="15.75" customHeight="1">
       <c r="T238" s="11"/>
       <c r="U238" s="11"/>
       <c r="V238" s="11"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="20:22" ht="15.75" customHeight="1">
       <c r="T239" s="11"/>
       <c r="U239" s="11"/>
       <c r="V239" s="11"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="20:22" ht="15.75" customHeight="1">
       <c r="T240" s="11"/>
       <c r="U240" s="11"/>
       <c r="V240" s="11"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="20:22" ht="15.75" customHeight="1">
       <c r="T241" s="11"/>
       <c r="U241" s="11"/>
       <c r="V241" s="11"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="20:22" ht="15.75" customHeight="1">
       <c r="T242" s="11"/>
       <c r="U242" s="11"/>
       <c r="V242" s="11"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="20:22" ht="15.75" customHeight="1">
       <c r="T243" s="11"/>
       <c r="U243" s="11"/>
       <c r="V243" s="11"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="20:22" ht="15.75" customHeight="1">
       <c r="T244" s="11"/>
       <c r="U244" s="11"/>
       <c r="V244" s="11"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="20:22" ht="15.75" customHeight="1">
       <c r="T245" s="11"/>
       <c r="U245" s="11"/>
       <c r="V245" s="11"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="20:22" ht="15.75" customHeight="1">
       <c r="T246" s="11"/>
       <c r="U246" s="11"/>
       <c r="V246" s="11"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="20:22" ht="15.75" customHeight="1">
       <c r="T247" s="11"/>
       <c r="U247" s="11"/>
       <c r="V247" s="11"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="20:22" ht="15.75" customHeight="1">
       <c r="T248" s="11"/>
       <c r="U248" s="11"/>
       <c r="V248" s="11"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="20:22" ht="15.75" customHeight="1">
       <c r="T249" s="11"/>
       <c r="U249" s="11"/>
       <c r="V249" s="11"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="20:22" ht="15.75" customHeight="1">
       <c r="T250" s="11"/>
       <c r="U250" s="11"/>
       <c r="V250" s="11"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" spans="20:22" ht="15.75" customHeight="1">
       <c r="T251" s="11"/>
       <c r="U251" s="11"/>
       <c r="V251" s="11"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" spans="20:22" ht="15.75" customHeight="1">
       <c r="T252" s="11"/>
       <c r="U252" s="11"/>
       <c r="V252" s="11"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" spans="20:22" ht="15.75" customHeight="1">
       <c r="T253" s="11"/>
       <c r="U253" s="11"/>
       <c r="V253" s="11"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" spans="20:22" ht="15.75" customHeight="1">
       <c r="T254" s="11"/>
       <c r="U254" s="11"/>
       <c r="V254" s="11"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" spans="20:22" ht="15.75" customHeight="1">
       <c r="T255" s="11"/>
       <c r="U255" s="11"/>
       <c r="V255" s="11"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" spans="20:22" ht="15.75" customHeight="1">
       <c r="T256" s="11"/>
       <c r="U256" s="11"/>
       <c r="V256" s="11"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" spans="20:22" ht="15.75" customHeight="1">
       <c r="T257" s="11"/>
       <c r="U257" s="11"/>
       <c r="V257" s="11"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" spans="20:22" ht="15.75" customHeight="1">
       <c r="T258" s="11"/>
       <c r="U258" s="11"/>
       <c r="V258" s="11"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" spans="20:22" ht="15.75" customHeight="1">
       <c r="T259" s="11"/>
       <c r="U259" s="11"/>
       <c r="V259" s="11"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" spans="20:22" ht="15.75" customHeight="1">
       <c r="T260" s="11"/>
       <c r="U260" s="11"/>
       <c r="V260" s="11"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" spans="20:22" ht="15.75" customHeight="1">
       <c r="T261" s="11"/>
       <c r="U261" s="11"/>
       <c r="V261" s="11"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" spans="20:22" ht="15.75" customHeight="1">
       <c r="T262" s="11"/>
       <c r="U262" s="11"/>
       <c r="V262" s="11"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" spans="20:22" ht="15.75" customHeight="1">
       <c r="T263" s="11"/>
       <c r="U263" s="11"/>
       <c r="V263" s="11"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" spans="20:22" ht="15.75" customHeight="1">
       <c r="T264" s="11"/>
       <c r="U264" s="11"/>
       <c r="V264" s="11"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" spans="20:22" ht="15.75" customHeight="1">
       <c r="T265" s="11"/>
       <c r="U265" s="11"/>
       <c r="V265" s="11"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" spans="20:22" ht="15.75" customHeight="1">
       <c r="T266" s="11"/>
       <c r="U266" s="11"/>
       <c r="V266" s="11"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" spans="20:22" ht="15.75" customHeight="1">
       <c r="T267" s="11"/>
       <c r="U267" s="11"/>
       <c r="V267" s="11"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" spans="20:22" ht="15.75" customHeight="1">
       <c r="T268" s="11"/>
       <c r="U268" s="11"/>
       <c r="V268" s="11"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" spans="20:22" ht="15.75" customHeight="1">
       <c r="T269" s="11"/>
       <c r="U269" s="11"/>
       <c r="V269" s="11"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" spans="20:22" ht="15.75" customHeight="1">
       <c r="T270" s="11"/>
       <c r="U270" s="11"/>
       <c r="V270" s="11"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" spans="20:22" ht="15.75" customHeight="1">
       <c r="T271" s="11"/>
       <c r="U271" s="11"/>
       <c r="V271" s="11"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" spans="20:22" ht="15.75" customHeight="1">
       <c r="T272" s="11"/>
       <c r="U272" s="11"/>
       <c r="V272" s="11"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" spans="20:22" ht="15.75" customHeight="1">
       <c r="T273" s="11"/>
       <c r="U273" s="11"/>
       <c r="V273" s="11"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" spans="20:22" ht="15.75" customHeight="1">
       <c r="T274" s="11"/>
       <c r="U274" s="11"/>
       <c r="V274" s="11"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" spans="20:22" ht="15.75" customHeight="1">
       <c r="T275" s="11"/>
       <c r="U275" s="11"/>
       <c r="V275" s="11"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" spans="20:22" ht="15.75" customHeight="1">
       <c r="T276" s="11"/>
       <c r="U276" s="11"/>
       <c r="V276" s="11"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" spans="20:22" ht="15.75" customHeight="1">
       <c r="T277" s="11"/>
       <c r="U277" s="11"/>
       <c r="V277" s="11"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" spans="20:22" ht="15.75" customHeight="1">
       <c r="T278" s="11"/>
       <c r="U278" s="11"/>
       <c r="V278" s="11"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" spans="20:22" ht="15.75" customHeight="1">
       <c r="T279" s="11"/>
       <c r="U279" s="11"/>
       <c r="V279" s="11"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" spans="20:22" ht="15.75" customHeight="1">
       <c r="T280" s="11"/>
       <c r="U280" s="11"/>
       <c r="V280" s="11"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" spans="20:22" ht="15.75" customHeight="1">
       <c r="T281" s="11"/>
       <c r="U281" s="11"/>
       <c r="V281" s="11"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" spans="20:22" ht="15.75" customHeight="1">
       <c r="T282" s="11"/>
       <c r="U282" s="11"/>
       <c r="V282" s="11"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" spans="20:22" ht="15.75" customHeight="1">
       <c r="T283" s="11"/>
       <c r="U283" s="11"/>
       <c r="V283" s="11"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" spans="20:22" ht="15.75" customHeight="1">
       <c r="T284" s="11"/>
       <c r="U284" s="11"/>
       <c r="V284" s="11"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" spans="20:22" ht="15.75" customHeight="1">
       <c r="T285" s="11"/>
       <c r="U285" s="11"/>
       <c r="V285" s="11"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" spans="20:22" ht="15.75" customHeight="1">
       <c r="T286" s="11"/>
       <c r="U286" s="11"/>
       <c r="V286" s="11"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" spans="20:22" ht="15.75" customHeight="1">
       <c r="T287" s="11"/>
       <c r="U287" s="11"/>
       <c r="V287" s="11"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" spans="20:22" ht="15.75" customHeight="1">
       <c r="T288" s="11"/>
       <c r="U288" s="11"/>
       <c r="V288" s="11"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" spans="20:22" ht="15.75" customHeight="1">
       <c r="T289" s="11"/>
       <c r="U289" s="11"/>
       <c r="V289" s="11"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" spans="20:22" ht="15.75" customHeight="1">
       <c r="T290" s="11"/>
       <c r="U290" s="11"/>
       <c r="V290" s="11"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" spans="20:22" ht="15.75" customHeight="1">
       <c r="T291" s="11"/>
       <c r="U291" s="11"/>
       <c r="V291" s="11"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" spans="20:22" ht="15.75" customHeight="1">
       <c r="T292" s="11"/>
       <c r="U292" s="11"/>
       <c r="V292" s="11"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" spans="20:22" ht="15.75" customHeight="1">
       <c r="T293" s="11"/>
       <c r="U293" s="11"/>
       <c r="V293" s="11"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" spans="20:22" ht="15.75" customHeight="1">
       <c r="T294" s="11"/>
       <c r="U294" s="11"/>
       <c r="V294" s="11"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" spans="20:22" ht="15.75" customHeight="1">
       <c r="T295" s="11"/>
       <c r="U295" s="11"/>
       <c r="V295" s="11"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" spans="20:22" ht="15.75" customHeight="1">
       <c r="T296" s="11"/>
       <c r="U296" s="11"/>
       <c r="V296" s="11"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" spans="20:22" ht="15.75" customHeight="1">
       <c r="T297" s="11"/>
       <c r="U297" s="11"/>
       <c r="V297" s="11"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" spans="20:22" ht="15.75" customHeight="1">
       <c r="T298" s="11"/>
       <c r="U298" s="11"/>
       <c r="V298" s="11"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" spans="20:22" ht="15.75" customHeight="1">
       <c r="T299" s="11"/>
       <c r="U299" s="11"/>
       <c r="V299" s="11"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" spans="20:22" ht="15.75" customHeight="1">
       <c r="T300" s="11"/>
       <c r="U300" s="11"/>
       <c r="V300" s="11"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" spans="20:22" ht="15.75" customHeight="1">
       <c r="T301" s="11"/>
       <c r="U301" s="11"/>
       <c r="V301" s="11"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" spans="20:22" ht="15.75" customHeight="1">
       <c r="T302" s="11"/>
       <c r="U302" s="11"/>
       <c r="V302" s="11"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" spans="20:22" ht="15.75" customHeight="1">
       <c r="T303" s="11"/>
       <c r="U303" s="11"/>
       <c r="V303" s="11"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" spans="20:22" ht="15.75" customHeight="1">
       <c r="T304" s="11"/>
       <c r="U304" s="11"/>
       <c r="V304" s="11"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" spans="20:22" ht="15.75" customHeight="1">
       <c r="T305" s="11"/>
       <c r="U305" s="11"/>
       <c r="V305" s="11"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" spans="20:22" ht="15.75" customHeight="1">
       <c r="T306" s="11"/>
       <c r="U306" s="11"/>
       <c r="V306" s="11"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" spans="20:22" ht="15.75" customHeight="1">
       <c r="T307" s="11"/>
       <c r="U307" s="11"/>
       <c r="V307" s="11"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" spans="20:22" ht="15.75" customHeight="1">
       <c r="T308" s="11"/>
       <c r="U308" s="11"/>
       <c r="V308" s="11"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" spans="20:22" ht="15.75" customHeight="1">
       <c r="T309" s="11"/>
       <c r="U309" s="11"/>
       <c r="V309" s="11"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" spans="20:22" ht="15.75" customHeight="1">
       <c r="T310" s="11"/>
       <c r="U310" s="11"/>
       <c r="V310" s="11"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" spans="20:22" ht="15.75" customHeight="1">
       <c r="T311" s="11"/>
       <c r="U311" s="11"/>
       <c r="V311" s="11"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" spans="20:22" ht="15.75" customHeight="1">
       <c r="T312" s="11"/>
       <c r="U312" s="11"/>
       <c r="V312" s="11"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" spans="20:22" ht="15.75" customHeight="1">
       <c r="T313" s="11"/>
       <c r="U313" s="11"/>
       <c r="V313" s="11"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" spans="20:22" ht="15.75" customHeight="1">
       <c r="T314" s="11"/>
       <c r="U314" s="11"/>
       <c r="V314" s="11"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" spans="20:22" ht="15.75" customHeight="1">
       <c r="T315" s="11"/>
       <c r="U315" s="11"/>
       <c r="V315" s="11"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" spans="20:22" ht="15.75" customHeight="1">
       <c r="T316" s="11"/>
       <c r="U316" s="11"/>
       <c r="V316" s="11"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" spans="20:22" ht="15.75" customHeight="1">
       <c r="T317" s="11"/>
       <c r="U317" s="11"/>
       <c r="V317" s="11"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" spans="20:22" ht="15.75" customHeight="1">
       <c r="T318" s="11"/>
       <c r="U318" s="11"/>
       <c r="V318" s="11"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" spans="20:22" ht="15.75" customHeight="1">
       <c r="T319" s="11"/>
       <c r="U319" s="11"/>
       <c r="V319" s="11"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" spans="20:22" ht="15.75" customHeight="1">
       <c r="T320" s="11"/>
       <c r="U320" s="11"/>
       <c r="V320" s="11"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" spans="20:22" ht="15.75" customHeight="1">
       <c r="T321" s="11"/>
       <c r="U321" s="11"/>
       <c r="V321" s="11"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" spans="20:22" ht="15.75" customHeight="1">
       <c r="T322" s="11"/>
       <c r="U322" s="11"/>
       <c r="V322" s="11"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" spans="20:22" ht="15.75" customHeight="1">
       <c r="T323" s="11"/>
       <c r="U323" s="11"/>
       <c r="V323" s="11"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" spans="20:22" ht="15.75" customHeight="1">
       <c r="T324" s="11"/>
       <c r="U324" s="11"/>
       <c r="V324" s="11"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" spans="20:22" ht="15.75" customHeight="1">
       <c r="T325" s="11"/>
       <c r="U325" s="11"/>
       <c r="V325" s="11"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" spans="20:22" ht="15.75" customHeight="1">
       <c r="T326" s="11"/>
       <c r="U326" s="11"/>
       <c r="V326" s="11"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" spans="20:22" ht="15.75" customHeight="1">
       <c r="T327" s="11"/>
       <c r="U327" s="11"/>
       <c r="V327" s="11"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" spans="20:22" ht="15.75" customHeight="1">
       <c r="T328" s="11"/>
       <c r="U328" s="11"/>
       <c r="V328" s="11"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" spans="20:22" ht="15.75" customHeight="1">
       <c r="T329" s="11"/>
       <c r="U329" s="11"/>
       <c r="V329" s="11"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" spans="20:22" ht="15.75" customHeight="1">
       <c r="T330" s="11"/>
       <c r="U330" s="11"/>
       <c r="V330" s="11"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" spans="20:22" ht="15.75" customHeight="1">
       <c r="T331" s="11"/>
       <c r="U331" s="11"/>
       <c r="V331" s="11"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" spans="20:22" ht="15.75" customHeight="1">
       <c r="T332" s="11"/>
       <c r="U332" s="11"/>
       <c r="V332" s="11"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" spans="20:22" ht="15.75" customHeight="1">
       <c r="T333" s="11"/>
       <c r="U333" s="11"/>
       <c r="V333" s="11"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" spans="20:22" ht="15.75" customHeight="1">
       <c r="T334" s="11"/>
       <c r="U334" s="11"/>
       <c r="V334" s="11"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" spans="20:22" ht="15.75" customHeight="1">
       <c r="T335" s="11"/>
       <c r="U335" s="11"/>
       <c r="V335" s="11"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" spans="20:22" ht="15.75" customHeight="1">
       <c r="T336" s="11"/>
       <c r="U336" s="11"/>
       <c r="V336" s="11"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" spans="20:22" ht="15.75" customHeight="1">
       <c r="T337" s="11"/>
       <c r="U337" s="11"/>
       <c r="V337" s="11"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" spans="20:22" ht="15.75" customHeight="1">
       <c r="T338" s="11"/>
       <c r="U338" s="11"/>
       <c r="V338" s="11"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" spans="20:22" ht="15.75" customHeight="1">
       <c r="T339" s="11"/>
       <c r="U339" s="11"/>
       <c r="V339" s="11"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" spans="20:22" ht="15.75" customHeight="1">
       <c r="T340" s="11"/>
       <c r="U340" s="11"/>
       <c r="V340" s="11"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" spans="20:22" ht="15.75" customHeight="1">
       <c r="T341" s="11"/>
       <c r="U341" s="11"/>
       <c r="V341" s="11"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" spans="20:22" ht="15.75" customHeight="1">
       <c r="T342" s="11"/>
       <c r="U342" s="11"/>
       <c r="V342" s="11"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" spans="20:22" ht="15.75" customHeight="1">
       <c r="T343" s="11"/>
       <c r="U343" s="11"/>
       <c r="V343" s="11"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" spans="20:22" ht="15.75" customHeight="1">
       <c r="T344" s="11"/>
       <c r="U344" s="11"/>
       <c r="V344" s="11"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" spans="20:22" ht="15.75" customHeight="1">
       <c r="T345" s="11"/>
       <c r="U345" s="11"/>
       <c r="V345" s="11"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" spans="20:22" ht="15.75" customHeight="1">
       <c r="T346" s="11"/>
       <c r="U346" s="11"/>
       <c r="V346" s="11"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" spans="20:22" ht="15.75" customHeight="1">
       <c r="T347" s="11"/>
       <c r="U347" s="11"/>
       <c r="V347" s="11"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" spans="20:22" ht="15.75" customHeight="1">
       <c r="T348" s="11"/>
       <c r="U348" s="11"/>
       <c r="V348" s="11"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" spans="20:22" ht="15.75" customHeight="1">
       <c r="T349" s="11"/>
       <c r="U349" s="11"/>
       <c r="V349" s="11"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" spans="20:22" ht="15.75" customHeight="1">
       <c r="T350" s="11"/>
       <c r="U350" s="11"/>
       <c r="V350" s="11"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" spans="20:22" ht="15.75" customHeight="1">
       <c r="T351" s="11"/>
       <c r="U351" s="11"/>
       <c r="V351" s="11"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" spans="20:22" ht="15.75" customHeight="1">
       <c r="T352" s="11"/>
       <c r="U352" s="11"/>
       <c r="V352" s="11"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" spans="20:22" ht="15.75" customHeight="1">
       <c r="T353" s="11"/>
       <c r="U353" s="11"/>
       <c r="V353" s="11"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" spans="20:22" ht="15.75" customHeight="1">
       <c r="T354" s="11"/>
       <c r="U354" s="11"/>
       <c r="V354" s="11"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" spans="20:22" ht="15.75" customHeight="1">
       <c r="T355" s="11"/>
       <c r="U355" s="11"/>
       <c r="V355" s="11"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" spans="20:22" ht="15.75" customHeight="1">
       <c r="T356" s="11"/>
       <c r="U356" s="11"/>
       <c r="V356" s="11"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" spans="20:22" ht="15.75" customHeight="1">
       <c r="T357" s="11"/>
       <c r="U357" s="11"/>
       <c r="V357" s="11"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" spans="20:22" ht="15.75" customHeight="1">
       <c r="T358" s="11"/>
       <c r="U358" s="11"/>
       <c r="V358" s="11"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" spans="20:22" ht="15.75" customHeight="1">
       <c r="T359" s="11"/>
       <c r="U359" s="11"/>
       <c r="V359" s="11"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" spans="20:22" ht="15.75" customHeight="1">
       <c r="T360" s="11"/>
       <c r="U360" s="11"/>
       <c r="V360" s="11"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" spans="20:22" ht="15.75" customHeight="1">
       <c r="T361" s="11"/>
       <c r="U361" s="11"/>
       <c r="V361" s="11"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" spans="20:22" ht="15.75" customHeight="1">
       <c r="T362" s="11"/>
       <c r="U362" s="11"/>
       <c r="V362" s="11"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" spans="20:22" ht="15.75" customHeight="1">
       <c r="T363" s="11"/>
       <c r="U363" s="11"/>
       <c r="V363" s="11"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" spans="20:22" ht="15.75" customHeight="1">
       <c r="T364" s="11"/>
       <c r="U364" s="11"/>
       <c r="V364" s="11"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" spans="20:22" ht="15.75" customHeight="1">
       <c r="T365" s="11"/>
       <c r="U365" s="11"/>
       <c r="V365" s="11"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" spans="20:22" ht="15.75" customHeight="1">
       <c r="T366" s="11"/>
       <c r="U366" s="11"/>
       <c r="V366" s="11"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" spans="20:22" ht="15.75" customHeight="1">
       <c r="T367" s="11"/>
       <c r="U367" s="11"/>
       <c r="V367" s="11"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" spans="20:22" ht="15.75" customHeight="1">
       <c r="T368" s="11"/>
       <c r="U368" s="11"/>
       <c r="V368" s="11"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" spans="20:22" ht="15.75" customHeight="1">
       <c r="T369" s="11"/>
       <c r="U369" s="11"/>
       <c r="V369" s="11"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" spans="20:22" ht="15.75" customHeight="1">
       <c r="T370" s="11"/>
       <c r="U370" s="11"/>
       <c r="V370" s="11"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" spans="20:22" ht="15.75" customHeight="1">
       <c r="T371" s="11"/>
       <c r="U371" s="11"/>
       <c r="V371" s="11"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" spans="20:22" ht="15.75" customHeight="1">
       <c r="T372" s="11"/>
       <c r="U372" s="11"/>
       <c r="V372" s="11"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" spans="20:22" ht="15.75" customHeight="1">
       <c r="T373" s="11"/>
       <c r="U373" s="11"/>
       <c r="V373" s="11"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" spans="20:22" ht="15.75" customHeight="1">
       <c r="T374" s="11"/>
       <c r="U374" s="11"/>
       <c r="V374" s="11"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" spans="20:22" ht="15.75" customHeight="1">
       <c r="T375" s="11"/>
       <c r="U375" s="11"/>
       <c r="V375" s="11"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" spans="20:22" ht="15.75" customHeight="1">
       <c r="T376" s="11"/>
       <c r="U376" s="11"/>
       <c r="V376" s="11"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" spans="20:22" ht="15.75" customHeight="1">
       <c r="T377" s="11"/>
       <c r="U377" s="11"/>
       <c r="V377" s="11"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" spans="20:22" ht="15.75" customHeight="1">
       <c r="T378" s="11"/>
       <c r="U378" s="11"/>
       <c r="V378" s="11"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" spans="20:22" ht="15.75" customHeight="1">
       <c r="T379" s="11"/>
       <c r="U379" s="11"/>
       <c r="V379" s="11"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" spans="20:22" ht="15.75" customHeight="1">
       <c r="T380" s="11"/>
       <c r="U380" s="11"/>
       <c r="V380" s="11"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" spans="20:22" ht="15.75" customHeight="1">
       <c r="T381" s="11"/>
       <c r="U381" s="11"/>
       <c r="V381" s="11"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" spans="20:22" ht="15.75" customHeight="1">
       <c r="T382" s="11"/>
       <c r="U382" s="11"/>
       <c r="V382" s="11"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" spans="20:22" ht="15.75" customHeight="1">
       <c r="T383" s="11"/>
       <c r="U383" s="11"/>
       <c r="V383" s="11"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" spans="20:22" ht="15.75" customHeight="1">
       <c r="T384" s="11"/>
       <c r="U384" s="11"/>
       <c r="V384" s="11"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" spans="20:22" ht="15.75" customHeight="1">
       <c r="T385" s="11"/>
       <c r="U385" s="11"/>
       <c r="V385" s="11"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" spans="20:22" ht="15.75" customHeight="1">
       <c r="T386" s="11"/>
       <c r="U386" s="11"/>
       <c r="V386" s="11"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" spans="20:22" ht="15.75" customHeight="1">
       <c r="T387" s="11"/>
       <c r="U387" s="11"/>
       <c r="V387" s="11"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" spans="20:22" ht="15.75" customHeight="1">
       <c r="T388" s="11"/>
       <c r="U388" s="11"/>
       <c r="V388" s="11"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" spans="20:22" ht="15.75" customHeight="1">
       <c r="T389" s="11"/>
       <c r="U389" s="11"/>
       <c r="V389" s="11"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" spans="20:22" ht="15.75" customHeight="1">
       <c r="T390" s="11"/>
       <c r="U390" s="11"/>
       <c r="V390" s="11"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" spans="20:22" ht="15.75" customHeight="1">
       <c r="T391" s="11"/>
       <c r="U391" s="11"/>
       <c r="V391" s="11"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" spans="20:22" ht="15.75" customHeight="1">
       <c r="T392" s="11"/>
       <c r="U392" s="11"/>
       <c r="V392" s="11"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" spans="20:22" ht="15.75" customHeight="1">
       <c r="T393" s="11"/>
       <c r="U393" s="11"/>
       <c r="V393" s="11"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" spans="20:22" ht="15.75" customHeight="1">
       <c r="T394" s="11"/>
       <c r="U394" s="11"/>
       <c r="V394" s="11"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" spans="20:22" ht="15.75" customHeight="1">
       <c r="T395" s="11"/>
       <c r="U395" s="11"/>
       <c r="V395" s="11"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" spans="20:22" ht="15.75" customHeight="1">
       <c r="T396" s="11"/>
       <c r="U396" s="11"/>
       <c r="V396" s="11"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" spans="20:22" ht="15.75" customHeight="1">
       <c r="T397" s="11"/>
       <c r="U397" s="11"/>
       <c r="V397" s="11"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" spans="20:22" ht="15.75" customHeight="1">
       <c r="T398" s="11"/>
       <c r="U398" s="11"/>
       <c r="V398" s="11"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" spans="20:22" ht="15.75" customHeight="1">
       <c r="T399" s="11"/>
       <c r="U399" s="11"/>
       <c r="V399" s="11"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" spans="20:22" ht="15.75" customHeight="1">
       <c r="T400" s="11"/>
       <c r="U400" s="11"/>
       <c r="V400" s="11"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" spans="20:22" ht="15.75" customHeight="1">
       <c r="T401" s="11"/>
       <c r="U401" s="11"/>
       <c r="V401" s="11"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" spans="20:22" ht="15.75" customHeight="1">
       <c r="T402" s="11"/>
       <c r="U402" s="11"/>
       <c r="V402" s="11"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" spans="20:22" ht="15.75" customHeight="1">
       <c r="T403" s="11"/>
       <c r="U403" s="11"/>
       <c r="V403" s="11"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" spans="20:22" ht="15.75" customHeight="1">
       <c r="T404" s="11"/>
       <c r="U404" s="11"/>
       <c r="V404" s="11"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" spans="20:22" ht="15.75" customHeight="1">
       <c r="T405" s="11"/>
       <c r="U405" s="11"/>
       <c r="V405" s="11"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" spans="20:22" ht="15.75" customHeight="1">
       <c r="T406" s="11"/>
       <c r="U406" s="11"/>
       <c r="V406" s="11"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" spans="20:22" ht="15.75" customHeight="1">
       <c r="T407" s="11"/>
       <c r="U407" s="11"/>
       <c r="V407" s="11"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" spans="20:22" ht="15.75" customHeight="1">
       <c r="T408" s="11"/>
       <c r="U408" s="11"/>
       <c r="V408" s="11"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" spans="20:22" ht="15.75" customHeight="1">
       <c r="T409" s="11"/>
       <c r="U409" s="11"/>
       <c r="V409" s="11"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" spans="20:22" ht="15.75" customHeight="1">
       <c r="T410" s="11"/>
       <c r="U410" s="11"/>
       <c r="V410" s="11"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" spans="20:22" ht="15.75" customHeight="1">
       <c r="T411" s="11"/>
       <c r="U411" s="11"/>
       <c r="V411" s="11"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" spans="20:22" ht="15.75" customHeight="1">
       <c r="T412" s="11"/>
       <c r="U412" s="11"/>
       <c r="V412" s="11"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" spans="20:22" ht="15.75" customHeight="1">
       <c r="T413" s="11"/>
       <c r="U413" s="11"/>
       <c r="V413" s="11"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" spans="20:22" ht="15.75" customHeight="1">
       <c r="T414" s="11"/>
       <c r="U414" s="11"/>
       <c r="V414" s="11"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" spans="20:22" ht="15.75" customHeight="1">
       <c r="T415" s="11"/>
       <c r="U415" s="11"/>
       <c r="V415" s="11"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" spans="20:22" ht="15.75" customHeight="1">
       <c r="T416" s="11"/>
       <c r="U416" s="11"/>
       <c r="V416" s="11"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" spans="20:22" ht="15.75" customHeight="1">
       <c r="T417" s="11"/>
       <c r="U417" s="11"/>
       <c r="V417" s="11"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" spans="20:22" ht="15.75" customHeight="1">
       <c r="T418" s="11"/>
       <c r="U418" s="11"/>
       <c r="V418" s="11"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" spans="20:22" ht="15.75" customHeight="1">
       <c r="T419" s="11"/>
       <c r="U419" s="11"/>
       <c r="V419" s="11"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" spans="20:22" ht="15.75" customHeight="1">
       <c r="T420" s="11"/>
       <c r="U420" s="11"/>
       <c r="V420" s="11"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" spans="20:22" ht="15.75" customHeight="1">
       <c r="T421" s="11"/>
       <c r="U421" s="11"/>
       <c r="V421" s="11"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" spans="20:22" ht="15.75" customHeight="1">
       <c r="T422" s="11"/>
       <c r="U422" s="11"/>
       <c r="V422" s="11"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" spans="20:22" ht="15.75" customHeight="1">
       <c r="T423" s="11"/>
       <c r="U423" s="11"/>
       <c r="V423" s="11"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" spans="20:22" ht="15.75" customHeight="1">
       <c r="T424" s="11"/>
       <c r="U424" s="11"/>
       <c r="V424" s="11"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" spans="20:22" ht="15.75" customHeight="1">
       <c r="T425" s="11"/>
       <c r="U425" s="11"/>
       <c r="V425" s="11"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" spans="20:22" ht="15.75" customHeight="1">
       <c r="T426" s="11"/>
       <c r="U426" s="11"/>
       <c r="V426" s="11"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" spans="20:22" ht="15.75" customHeight="1">
       <c r="T427" s="11"/>
       <c r="U427" s="11"/>
       <c r="V427" s="11"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" spans="20:22" ht="15.75" customHeight="1">
       <c r="T428" s="11"/>
       <c r="U428" s="11"/>
       <c r="V428" s="11"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" spans="20:22" ht="15.75" customHeight="1">
       <c r="T429" s="11"/>
       <c r="U429" s="11"/>
       <c r="V429" s="11"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" spans="20:22" ht="15.75" customHeight="1">
       <c r="T430" s="11"/>
       <c r="U430" s="11"/>
       <c r="V430" s="11"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" spans="20:22" ht="15.75" customHeight="1">
       <c r="T431" s="11"/>
       <c r="U431" s="11"/>
       <c r="V431" s="11"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" spans="20:22" ht="15.75" customHeight="1">
       <c r="T432" s="11"/>
       <c r="U432" s="11"/>
       <c r="V432" s="11"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" spans="20:22" ht="15.75" customHeight="1">
       <c r="T433" s="11"/>
       <c r="U433" s="11"/>
       <c r="V433" s="11"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" spans="20:22" ht="15.75" customHeight="1">
       <c r="T434" s="11"/>
       <c r="U434" s="11"/>
       <c r="V434" s="11"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" spans="20:22" ht="15.75" customHeight="1">
       <c r="T435" s="11"/>
       <c r="U435" s="11"/>
       <c r="V435" s="11"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" spans="20:22" ht="15.75" customHeight="1">
       <c r="T436" s="11"/>
       <c r="U436" s="11"/>
       <c r="V436" s="11"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" spans="20:22" ht="15.75" customHeight="1">
       <c r="T437" s="11"/>
       <c r="U437" s="11"/>
       <c r="V437" s="11"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" spans="20:22" ht="15.75" customHeight="1">
       <c r="T438" s="11"/>
       <c r="U438" s="11"/>
       <c r="V438" s="11"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" spans="20:22" ht="15.75" customHeight="1">
       <c r="T439" s="11"/>
       <c r="U439" s="11"/>
       <c r="V439" s="11"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" spans="20:22" ht="15.75" customHeight="1">
       <c r="T440" s="11"/>
       <c r="U440" s="11"/>
       <c r="V440" s="11"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" spans="20:22" ht="15.75" customHeight="1">
       <c r="T441" s="11"/>
       <c r="U441" s="11"/>
       <c r="V441" s="11"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" spans="20:22" ht="15.75" customHeight="1">
       <c r="T442" s="11"/>
       <c r="U442" s="11"/>
       <c r="V442" s="11"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" spans="20:22" ht="15.75" customHeight="1">
       <c r="T443" s="11"/>
       <c r="U443" s="11"/>
       <c r="V443" s="11"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" spans="20:22" ht="15.75" customHeight="1">
       <c r="T444" s="11"/>
       <c r="U444" s="11"/>
       <c r="V444" s="11"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" spans="20:22" ht="15.75" customHeight="1">
       <c r="T445" s="11"/>
       <c r="U445" s="11"/>
       <c r="V445" s="11"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" spans="20:22" ht="15.75" customHeight="1">
       <c r="T446" s="11"/>
       <c r="U446" s="11"/>
       <c r="V446" s="11"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" spans="20:22" ht="15.75" customHeight="1">
       <c r="T447" s="11"/>
       <c r="U447" s="11"/>
       <c r="V447" s="11"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" spans="20:22" ht="15.75" customHeight="1">
       <c r="T448" s="11"/>
       <c r="U448" s="11"/>
       <c r="V448" s="11"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" spans="20:22" ht="15.75" customHeight="1">
       <c r="T449" s="11"/>
       <c r="U449" s="11"/>
       <c r="V449" s="11"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" spans="20:22" ht="15.75" customHeight="1">
       <c r="T450" s="11"/>
       <c r="U450" s="11"/>
       <c r="V450" s="11"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" spans="20:22" ht="15.75" customHeight="1">
       <c r="T451" s="11"/>
       <c r="U451" s="11"/>
       <c r="V451" s="11"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" spans="20:22" ht="15.75" customHeight="1">
       <c r="T452" s="11"/>
       <c r="U452" s="11"/>
       <c r="V452" s="11"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" spans="20:22" ht="15.75" customHeight="1">
       <c r="T453" s="11"/>
       <c r="U453" s="11"/>
       <c r="V453" s="11"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" spans="20:22" ht="15.75" customHeight="1">
       <c r="T454" s="11"/>
       <c r="U454" s="11"/>
       <c r="V454" s="11"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" spans="20:22" ht="15.75" customHeight="1">
       <c r="T455" s="11"/>
       <c r="U455" s="11"/>
       <c r="V455" s="11"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" spans="20:22" ht="15.75" customHeight="1">
       <c r="T456" s="11"/>
       <c r="U456" s="11"/>
       <c r="V456" s="11"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" spans="20:22" ht="15.75" customHeight="1">
       <c r="T457" s="11"/>
       <c r="U457" s="11"/>
       <c r="V457" s="11"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" spans="20:22" ht="15.75" customHeight="1">
       <c r="T458" s="11"/>
       <c r="U458" s="11"/>
       <c r="V458" s="11"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" spans="20:22" ht="15.75" customHeight="1">
       <c r="T459" s="11"/>
       <c r="U459" s="11"/>
       <c r="V459" s="11"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" spans="20:22" ht="15.75" customHeight="1">
       <c r="T460" s="11"/>
       <c r="U460" s="11"/>
       <c r="V460" s="11"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" spans="20:22" ht="15.75" customHeight="1">
       <c r="T461" s="11"/>
       <c r="U461" s="11"/>
       <c r="V461" s="11"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" spans="20:22" ht="15.75" customHeight="1">
       <c r="T462" s="11"/>
       <c r="U462" s="11"/>
       <c r="V462" s="11"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" spans="20:22" ht="15.75" customHeight="1">
       <c r="T463" s="11"/>
       <c r="U463" s="11"/>
       <c r="V463" s="11"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" spans="20:22" ht="15.75" customHeight="1">
       <c r="T464" s="11"/>
       <c r="U464" s="11"/>
       <c r="V464" s="11"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" spans="20:22" ht="15.75" customHeight="1">
       <c r="T465" s="11"/>
       <c r="U465" s="11"/>
       <c r="V465" s="11"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" spans="20:22" ht="15.75" customHeight="1">
       <c r="T466" s="11"/>
       <c r="U466" s="11"/>
       <c r="V466" s="11"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" spans="20:22" ht="15.75" customHeight="1">
       <c r="T467" s="11"/>
       <c r="U467" s="11"/>
       <c r="V467" s="11"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" spans="20:22" ht="15.75" customHeight="1">
       <c r="T468" s="11"/>
       <c r="U468" s="11"/>
       <c r="V468" s="11"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" spans="20:22" ht="15.75" customHeight="1">
       <c r="T469" s="11"/>
       <c r="U469" s="11"/>
       <c r="V469" s="11"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" spans="20:22" ht="15.75" customHeight="1">
       <c r="T470" s="11"/>
       <c r="U470" s="11"/>
       <c r="V470" s="11"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" spans="20:22" ht="15.75" customHeight="1">
       <c r="T471" s="11"/>
       <c r="U471" s="11"/>
       <c r="V471" s="11"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" spans="20:22" ht="15.75" customHeight="1">
       <c r="T472" s="11"/>
       <c r="U472" s="11"/>
       <c r="V472" s="11"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" spans="20:22" ht="15.75" customHeight="1">
       <c r="T473" s="11"/>
       <c r="U473" s="11"/>
       <c r="V473" s="11"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" spans="20:22" ht="15.75" customHeight="1">
       <c r="T474" s="11"/>
       <c r="U474" s="11"/>
       <c r="V474" s="11"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" spans="20:22" ht="15.75" customHeight="1">
       <c r="T475" s="11"/>
       <c r="U475" s="11"/>
       <c r="V475" s="11"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" spans="20:22" ht="15.75" customHeight="1">
       <c r="T476" s="11"/>
       <c r="U476" s="11"/>
       <c r="V476" s="11"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" spans="20:22" ht="15.75" customHeight="1">
       <c r="T477" s="11"/>
       <c r="U477" s="11"/>
       <c r="V477" s="11"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" spans="20:22" ht="15.75" customHeight="1">
       <c r="T478" s="11"/>
       <c r="U478" s="11"/>
       <c r="V478" s="11"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" spans="20:22" ht="15.75" customHeight="1">
       <c r="T479" s="11"/>
       <c r="U479" s="11"/>
       <c r="V479" s="11"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" spans="20:22" ht="15.75" customHeight="1">
       <c r="T480" s="11"/>
       <c r="U480" s="11"/>
       <c r="V480" s="11"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" spans="20:22" ht="15.75" customHeight="1">
       <c r="T481" s="11"/>
       <c r="U481" s="11"/>
       <c r="V481" s="11"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" spans="20:22" ht="15.75" customHeight="1">
       <c r="T482" s="11"/>
       <c r="U482" s="11"/>
       <c r="V482" s="11"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" spans="20:22" ht="15.75" customHeight="1">
       <c r="T483" s="11"/>
       <c r="U483" s="11"/>
       <c r="V483" s="11"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" spans="20:22" ht="15.75" customHeight="1">
       <c r="T484" s="11"/>
       <c r="U484" s="11"/>
       <c r="V484" s="11"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" spans="20:22" ht="15.75" customHeight="1">
       <c r="T485" s="11"/>
       <c r="U485" s="11"/>
       <c r="V485" s="11"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" spans="20:22" ht="15.75" customHeight="1">
       <c r="T486" s="11"/>
       <c r="U486" s="11"/>
       <c r="V486" s="11"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" spans="20:22" ht="15.75" customHeight="1">
       <c r="T487" s="11"/>
       <c r="U487" s="11"/>
       <c r="V487" s="11"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" spans="20:22" ht="15.75" customHeight="1">
       <c r="T488" s="11"/>
       <c r="U488" s="11"/>
       <c r="V488" s="11"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" spans="20:22" ht="15.75" customHeight="1">
       <c r="T489" s="11"/>
       <c r="U489" s="11"/>
       <c r="V489" s="11"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" spans="20:22" ht="15.75" customHeight="1">
       <c r="T490" s="11"/>
       <c r="U490" s="11"/>
       <c r="V490" s="11"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" spans="20:22" ht="15.75" customHeight="1">
       <c r="T491" s="11"/>
       <c r="U491" s="11"/>
       <c r="V491" s="11"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" spans="20:22" ht="15.75" customHeight="1">
       <c r="T492" s="11"/>
       <c r="U492" s="11"/>
       <c r="V492" s="11"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" spans="20:22" ht="15.75" customHeight="1">
       <c r="T493" s="11"/>
       <c r="U493" s="11"/>
       <c r="V493" s="11"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" spans="20:22" ht="15.75" customHeight="1">
       <c r="T494" s="11"/>
       <c r="U494" s="11"/>
       <c r="V494" s="11"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" spans="20:22" ht="15.75" customHeight="1">
       <c r="T495" s="11"/>
       <c r="U495" s="11"/>
       <c r="V495" s="11"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" spans="20:22" ht="15.75" customHeight="1">
       <c r="T496" s="11"/>
       <c r="U496" s="11"/>
       <c r="V496" s="11"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" spans="20:22" ht="15.75" customHeight="1">
       <c r="T497" s="11"/>
       <c r="U497" s="11"/>
       <c r="V497" s="11"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" spans="20:22" ht="15.75" customHeight="1">
       <c r="T498" s="11"/>
       <c r="U498" s="11"/>
       <c r="V498" s="11"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" spans="20:22" ht="15.75" customHeight="1">
       <c r="T499" s="11"/>
       <c r="U499" s="11"/>
       <c r="V499" s="11"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" spans="20:22" ht="15.75" customHeight="1">
       <c r="T500" s="11"/>
       <c r="U500" s="11"/>
       <c r="V500" s="11"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" spans="20:22" ht="15.75" customHeight="1">
       <c r="T501" s="11"/>
       <c r="U501" s="11"/>
       <c r="V501" s="11"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" spans="20:22" ht="15.75" customHeight="1">
       <c r="T502" s="11"/>
       <c r="U502" s="11"/>
       <c r="V502" s="11"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" spans="20:22" ht="15.75" customHeight="1">
       <c r="T503" s="11"/>
       <c r="U503" s="11"/>
       <c r="V503" s="11"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" spans="20:22" ht="15.75" customHeight="1">
       <c r="T504" s="11"/>
       <c r="U504" s="11"/>
       <c r="V504" s="11"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" spans="20:22" ht="15.75" customHeight="1">
       <c r="T505" s="11"/>
       <c r="U505" s="11"/>
       <c r="V505" s="11"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" spans="20:22" ht="15.75" customHeight="1">
       <c r="T506" s="11"/>
       <c r="U506" s="11"/>
       <c r="V506" s="11"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" spans="20:22" ht="15.75" customHeight="1">
       <c r="T507" s="11"/>
       <c r="U507" s="11"/>
       <c r="V507" s="11"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" spans="20:22" ht="15.75" customHeight="1">
       <c r="T508" s="11"/>
       <c r="U508" s="11"/>
       <c r="V508" s="11"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" spans="20:22" ht="15.75" customHeight="1">
       <c r="T509" s="11"/>
       <c r="U509" s="11"/>
       <c r="V509" s="11"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" spans="20:22" ht="15.75" customHeight="1">
       <c r="T510" s="11"/>
       <c r="U510" s="11"/>
       <c r="V510" s="11"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" spans="20:22" ht="15.75" customHeight="1">
       <c r="T511" s="11"/>
       <c r="U511" s="11"/>
       <c r="V511" s="11"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" spans="20:22" ht="15.75" customHeight="1">
       <c r="T512" s="11"/>
       <c r="U512" s="11"/>
       <c r="V512" s="11"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" spans="20:22" ht="15.75" customHeight="1">
       <c r="T513" s="11"/>
       <c r="U513" s="11"/>
       <c r="V513" s="11"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" spans="20:22" ht="15.75" customHeight="1">
       <c r="T514" s="11"/>
       <c r="U514" s="11"/>
       <c r="V514" s="11"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" spans="20:22" ht="15.75" customHeight="1">
       <c r="T515" s="11"/>
       <c r="U515" s="11"/>
       <c r="V515" s="11"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" spans="20:22" ht="15.75" customHeight="1">
       <c r="T516" s="11"/>
       <c r="U516" s="11"/>
       <c r="V516" s="11"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" spans="20:22" ht="15.75" customHeight="1">
       <c r="T517" s="11"/>
       <c r="U517" s="11"/>
       <c r="V517" s="11"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" spans="20:22" ht="15.75" customHeight="1">
       <c r="T518" s="11"/>
       <c r="U518" s="11"/>
       <c r="V518" s="11"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" spans="20:22" ht="15.75" customHeight="1">
       <c r="T519" s="11"/>
       <c r="U519" s="11"/>
       <c r="V519" s="11"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" spans="20:22" ht="15.75" customHeight="1">
       <c r="T520" s="11"/>
       <c r="U520" s="11"/>
       <c r="V520" s="11"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" spans="20:22" ht="15.75" customHeight="1">
       <c r="T521" s="11"/>
       <c r="U521" s="11"/>
       <c r="V521" s="11"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" spans="20:22" ht="15.75" customHeight="1">
       <c r="T522" s="11"/>
       <c r="U522" s="11"/>
       <c r="V522" s="11"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" spans="20:22" ht="15.75" customHeight="1">
       <c r="T523" s="11"/>
       <c r="U523" s="11"/>
       <c r="V523" s="11"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" spans="20:22" ht="15.75" customHeight="1">
       <c r="T524" s="11"/>
       <c r="U524" s="11"/>
       <c r="V524" s="11"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" spans="20:22" ht="15.75" customHeight="1">
       <c r="T525" s="11"/>
       <c r="U525" s="11"/>
       <c r="V525" s="11"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" spans="20:22" ht="15.75" customHeight="1">
       <c r="T526" s="11"/>
       <c r="U526" s="11"/>
       <c r="V526" s="11"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" spans="20:22" ht="15.75" customHeight="1">
       <c r="T527" s="11"/>
       <c r="U527" s="11"/>
       <c r="V527" s="11"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" spans="20:22" ht="15.75" customHeight="1">
       <c r="T528" s="11"/>
       <c r="U528" s="11"/>
       <c r="V528" s="11"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" spans="20:22" ht="15.75" customHeight="1">
       <c r="T529" s="11"/>
       <c r="U529" s="11"/>
       <c r="V529" s="11"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" spans="20:22" ht="15.75" customHeight="1">
       <c r="T530" s="11"/>
       <c r="U530" s="11"/>
       <c r="V530" s="11"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" spans="20:22" ht="15.75" customHeight="1">
       <c r="T531" s="11"/>
       <c r="U531" s="11"/>
       <c r="V531" s="11"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" spans="20:22" ht="15.75" customHeight="1">
       <c r="T532" s="11"/>
       <c r="U532" s="11"/>
       <c r="V532" s="11"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" spans="20:22" ht="15.75" customHeight="1">
       <c r="T533" s="11"/>
       <c r="U533" s="11"/>
       <c r="V533" s="11"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" spans="20:22" ht="15.75" customHeight="1">
       <c r="T534" s="11"/>
       <c r="U534" s="11"/>
       <c r="V534" s="11"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" spans="20:22" ht="15.75" customHeight="1">
       <c r="T535" s="11"/>
       <c r="U535" s="11"/>
       <c r="V535" s="11"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" spans="20:22" ht="15.75" customHeight="1">
       <c r="T536" s="11"/>
       <c r="U536" s="11"/>
       <c r="V536" s="11"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" spans="20:22" ht="15.75" customHeight="1">
       <c r="T537" s="11"/>
       <c r="U537" s="11"/>
       <c r="V537" s="11"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" spans="20:22" ht="15.75" customHeight="1">
       <c r="T538" s="11"/>
       <c r="U538" s="11"/>
       <c r="V538" s="11"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" spans="20:22" ht="15.75" customHeight="1">
       <c r="T539" s="11"/>
       <c r="U539" s="11"/>
       <c r="V539" s="11"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" spans="20:22" ht="15.75" customHeight="1">
       <c r="T540" s="11"/>
       <c r="U540" s="11"/>
       <c r="V540" s="11"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" spans="20:22" ht="15.75" customHeight="1">
       <c r="T541" s="11"/>
       <c r="U541" s="11"/>
       <c r="V541" s="11"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" spans="20:22" ht="15.75" customHeight="1">
       <c r="T542" s="11"/>
       <c r="U542" s="11"/>
       <c r="V542" s="11"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" spans="20:22" ht="15.75" customHeight="1">
       <c r="T543" s="11"/>
       <c r="U543" s="11"/>
       <c r="V543" s="11"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" spans="20:22" ht="15.75" customHeight="1">
       <c r="T544" s="11"/>
       <c r="U544" s="11"/>
       <c r="V544" s="11"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" spans="20:22" ht="15.75" customHeight="1">
       <c r="T545" s="11"/>
       <c r="U545" s="11"/>
       <c r="V545" s="11"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" spans="20:22" ht="15.75" customHeight="1">
       <c r="T546" s="11"/>
       <c r="U546" s="11"/>
       <c r="V546" s="11"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" spans="20:22" ht="15.75" customHeight="1">
       <c r="T547" s="11"/>
       <c r="U547" s="11"/>
       <c r="V547" s="11"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" spans="20:22" ht="15.75" customHeight="1">
       <c r="T548" s="11"/>
       <c r="U548" s="11"/>
       <c r="V548" s="11"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" spans="20:22" ht="15.75" customHeight="1">
       <c r="T549" s="11"/>
       <c r="U549" s="11"/>
       <c r="V549" s="11"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" spans="20:22" ht="15.75" customHeight="1">
       <c r="T550" s="11"/>
       <c r="U550" s="11"/>
       <c r="V550" s="11"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" spans="20:22" ht="15.75" customHeight="1">
       <c r="T551" s="11"/>
       <c r="U551" s="11"/>
       <c r="V551" s="11"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" spans="20:22" ht="15.75" customHeight="1">
       <c r="T552" s="11"/>
       <c r="U552" s="11"/>
       <c r="V552" s="11"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" spans="20:22" ht="15.75" customHeight="1">
       <c r="T553" s="11"/>
       <c r="U553" s="11"/>
       <c r="V553" s="11"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" spans="20:22" ht="15.75" customHeight="1">
       <c r="T554" s="11"/>
       <c r="U554" s="11"/>
       <c r="V554" s="11"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" spans="20:22" ht="15.75" customHeight="1">
       <c r="T555" s="11"/>
       <c r="U555" s="11"/>
       <c r="V555" s="11"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" spans="20:22" ht="15.75" customHeight="1">
       <c r="T556" s="11"/>
       <c r="U556" s="11"/>
       <c r="V556" s="11"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" spans="20:22" ht="15.75" customHeight="1">
       <c r="T557" s="11"/>
       <c r="U557" s="11"/>
       <c r="V557" s="11"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" spans="20:22" ht="15.75" customHeight="1">
       <c r="T558" s="11"/>
       <c r="U558" s="11"/>
       <c r="V558" s="11"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" spans="20:22" ht="15.75" customHeight="1">
       <c r="T559" s="11"/>
       <c r="U559" s="11"/>
       <c r="V559" s="11"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" spans="20:22" ht="15.75" customHeight="1">
       <c r="T560" s="11"/>
       <c r="U560" s="11"/>
       <c r="V560" s="11"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" spans="20:22" ht="15.75" customHeight="1">
       <c r="T561" s="11"/>
       <c r="U561" s="11"/>
       <c r="V561" s="11"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" spans="20:22" ht="15.75" customHeight="1">
       <c r="T562" s="11"/>
       <c r="U562" s="11"/>
       <c r="V562" s="11"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" spans="20:22" ht="15.75" customHeight="1">
       <c r="T563" s="11"/>
       <c r="U563" s="11"/>
       <c r="V563" s="11"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" spans="20:22" ht="15.75" customHeight="1">
       <c r="T564" s="11"/>
       <c r="U564" s="11"/>
       <c r="V564" s="11"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" spans="20:22" ht="15.75" customHeight="1">
       <c r="T565" s="11"/>
       <c r="U565" s="11"/>
       <c r="V565" s="11"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" spans="20:22" ht="15.75" customHeight="1">
       <c r="T566" s="11"/>
       <c r="U566" s="11"/>
       <c r="V566" s="11"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" spans="20:22" ht="15.75" customHeight="1">
       <c r="T567" s="11"/>
       <c r="U567" s="11"/>
       <c r="V567" s="11"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" spans="20:22" ht="15.75" customHeight="1">
       <c r="T568" s="11"/>
       <c r="U568" s="11"/>
       <c r="V568" s="11"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" spans="20:22" ht="15.75" customHeight="1">
       <c r="T569" s="11"/>
       <c r="U569" s="11"/>
       <c r="V569" s="11"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" spans="20:22" ht="15.75" customHeight="1">
       <c r="T570" s="11"/>
       <c r="U570" s="11"/>
       <c r="V570" s="11"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" spans="20:22" ht="15.75" customHeight="1">
       <c r="T571" s="11"/>
       <c r="U571" s="11"/>
       <c r="V571" s="11"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" spans="20:22" ht="15.75" customHeight="1">
       <c r="T572" s="11"/>
       <c r="U572" s="11"/>
       <c r="V572" s="11"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" spans="20:22" ht="15.75" customHeight="1">
       <c r="T573" s="11"/>
       <c r="U573" s="11"/>
       <c r="V573" s="11"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" spans="20:22" ht="15.75" customHeight="1">
       <c r="T574" s="11"/>
       <c r="U574" s="11"/>
       <c r="V574" s="11"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" spans="20:22" ht="15.75" customHeight="1">
       <c r="T575" s="11"/>
       <c r="U575" s="11"/>
       <c r="V575" s="11"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" spans="20:22" ht="15.75" customHeight="1">
       <c r="T576" s="11"/>
       <c r="U576" s="11"/>
       <c r="V576" s="11"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" spans="20:22" ht="15.75" customHeight="1">
       <c r="T577" s="11"/>
       <c r="U577" s="11"/>
       <c r="V577" s="11"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" spans="20:22" ht="15.75" customHeight="1">
       <c r="T578" s="11"/>
       <c r="U578" s="11"/>
       <c r="V578" s="11"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" spans="20:22" ht="15.75" customHeight="1">
       <c r="T579" s="11"/>
       <c r="U579" s="11"/>
       <c r="V579" s="11"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" spans="20:22" ht="15.75" customHeight="1">
       <c r="T580" s="11"/>
       <c r="U580" s="11"/>
       <c r="V580" s="11"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" spans="20:22" ht="15.75" customHeight="1">
       <c r="T581" s="11"/>
       <c r="U581" s="11"/>
       <c r="V581" s="11"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" spans="20:22" ht="15.75" customHeight="1">
       <c r="T582" s="11"/>
       <c r="U582" s="11"/>
       <c r="V582" s="11"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" spans="20:22" ht="15.75" customHeight="1">
       <c r="T583" s="11"/>
       <c r="U583" s="11"/>
       <c r="V583" s="11"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" spans="20:22" ht="15.75" customHeight="1">
       <c r="T584" s="11"/>
       <c r="U584" s="11"/>
       <c r="V584" s="11"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" spans="20:22" ht="15.75" customHeight="1">
       <c r="T585" s="11"/>
       <c r="U585" s="11"/>
       <c r="V585" s="11"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" spans="20:22" ht="15.75" customHeight="1">
       <c r="T586" s="11"/>
       <c r="U586" s="11"/>
       <c r="V586" s="11"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" spans="20:22" ht="15.75" customHeight="1">
       <c r="T587" s="11"/>
       <c r="U587" s="11"/>
       <c r="V587" s="11"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" spans="20:22" ht="15.75" customHeight="1">
       <c r="T588" s="11"/>
       <c r="U588" s="11"/>
       <c r="V588" s="11"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" spans="20:22" ht="15.75" customHeight="1">
       <c r="T589" s="11"/>
       <c r="U589" s="11"/>
       <c r="V589" s="11"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" spans="20:22" ht="15.75" customHeight="1">
       <c r="T590" s="11"/>
       <c r="U590" s="11"/>
       <c r="V590" s="11"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" spans="20:22" ht="15.75" customHeight="1">
       <c r="T591" s="11"/>
       <c r="U591" s="11"/>
       <c r="V591" s="11"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" spans="20:22" ht="15.75" customHeight="1">
       <c r="T592" s="11"/>
       <c r="U592" s="11"/>
       <c r="V592" s="11"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" spans="20:22" ht="15.75" customHeight="1">
       <c r="T593" s="11"/>
       <c r="U593" s="11"/>
       <c r="V593" s="11"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" spans="20:22" ht="15.75" customHeight="1">
       <c r="T594" s="11"/>
       <c r="U594" s="11"/>
       <c r="V594" s="11"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" spans="20:22" ht="15.75" customHeight="1">
       <c r="T595" s="11"/>
       <c r="U595" s="11"/>
       <c r="V595" s="11"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" spans="20:22" ht="15.75" customHeight="1">
       <c r="T596" s="11"/>
       <c r="U596" s="11"/>
       <c r="V596" s="11"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" spans="20:22" ht="15.75" customHeight="1">
       <c r="T597" s="11"/>
       <c r="U597" s="11"/>
       <c r="V597" s="11"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" spans="20:22" ht="15.75" customHeight="1">
       <c r="T598" s="11"/>
       <c r="U598" s="11"/>
       <c r="V598" s="11"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" spans="20:22" ht="15.75" customHeight="1">
       <c r="T599" s="11"/>
       <c r="U599" s="11"/>
       <c r="V599" s="11"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" spans="20:22" ht="15.75" customHeight="1">
       <c r="T600" s="11"/>
       <c r="U600" s="11"/>
       <c r="V600" s="11"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" spans="20:22" ht="15.75" customHeight="1">
       <c r="T601" s="11"/>
       <c r="U601" s="11"/>
       <c r="V601" s="11"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" spans="20:22" ht="15.75" customHeight="1">
       <c r="T602" s="11"/>
       <c r="U602" s="11"/>
       <c r="V602" s="11"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" spans="20:22" ht="15.75" customHeight="1">
       <c r="T603" s="11"/>
       <c r="U603" s="11"/>
       <c r="V603" s="11"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" spans="20:22" ht="15.75" customHeight="1">
       <c r="T604" s="11"/>
       <c r="U604" s="11"/>
       <c r="V604" s="11"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" spans="20:22" ht="15.75" customHeight="1">
       <c r="T605" s="11"/>
       <c r="U605" s="11"/>
       <c r="V605" s="11"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" spans="20:22" ht="15.75" customHeight="1">
       <c r="T606" s="11"/>
       <c r="U606" s="11"/>
       <c r="V606" s="11"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" spans="20:22" ht="15.75" customHeight="1">
       <c r="T607" s="11"/>
       <c r="U607" s="11"/>
       <c r="V607" s="11"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" spans="20:22" ht="15.75" customHeight="1">
       <c r="T608" s="11"/>
       <c r="U608" s="11"/>
       <c r="V608" s="11"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" spans="20:22" ht="15.75" customHeight="1">
       <c r="T609" s="11"/>
       <c r="U609" s="11"/>
       <c r="V609" s="11"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" spans="20:22" ht="15.75" customHeight="1">
       <c r="T610" s="11"/>
       <c r="U610" s="11"/>
       <c r="V610" s="11"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" spans="20:22" ht="15.75" customHeight="1">
       <c r="T611" s="11"/>
       <c r="U611" s="11"/>
       <c r="V611" s="11"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" spans="20:22" ht="15.75" customHeight="1">
       <c r="T612" s="11"/>
       <c r="U612" s="11"/>
       <c r="V612" s="11"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" spans="20:22" ht="15.75" customHeight="1">
       <c r="T613" s="11"/>
       <c r="U613" s="11"/>
       <c r="V613" s="11"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" spans="20:22" ht="15.75" customHeight="1">
       <c r="T614" s="11"/>
       <c r="U614" s="11"/>
       <c r="V614" s="11"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" spans="20:22" ht="15.75" customHeight="1">
       <c r="T615" s="11"/>
       <c r="U615" s="11"/>
       <c r="V615" s="11"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" spans="20:22" ht="15.75" customHeight="1">
       <c r="T616" s="11"/>
       <c r="U616" s="11"/>
       <c r="V616" s="11"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" spans="20:22" ht="15.75" customHeight="1">
       <c r="T617" s="11"/>
       <c r="U617" s="11"/>
       <c r="V617" s="11"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" spans="20:22" ht="15.75" customHeight="1">
       <c r="T618" s="11"/>
       <c r="U618" s="11"/>
       <c r="V618" s="11"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" spans="20:22" ht="15.75" customHeight="1">
       <c r="T619" s="11"/>
       <c r="U619" s="11"/>
       <c r="V619" s="11"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" spans="20:22" ht="15.75" customHeight="1">
       <c r="T620" s="11"/>
       <c r="U620" s="11"/>
       <c r="V620" s="11"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" spans="20:22" ht="15.75" customHeight="1">
       <c r="T621" s="11"/>
       <c r="U621" s="11"/>
       <c r="V621" s="11"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" spans="20:22" ht="15.75" customHeight="1">
       <c r="T622" s="11"/>
       <c r="U622" s="11"/>
       <c r="V622" s="11"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" spans="20:22" ht="15.75" customHeight="1">
       <c r="T623" s="11"/>
       <c r="U623" s="11"/>
       <c r="V623" s="11"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" spans="20:22" ht="15.75" customHeight="1">
       <c r="T624" s="11"/>
       <c r="U624" s="11"/>
       <c r="V624" s="11"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" spans="20:22" ht="15.75" customHeight="1">
       <c r="T625" s="11"/>
       <c r="U625" s="11"/>
       <c r="V625" s="11"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" spans="20:22" ht="15.75" customHeight="1">
       <c r="T626" s="11"/>
       <c r="U626" s="11"/>
       <c r="V626" s="11"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" spans="20:22" ht="15.75" customHeight="1">
       <c r="T627" s="11"/>
       <c r="U627" s="11"/>
       <c r="V627" s="11"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" spans="20:22" ht="15.75" customHeight="1">
       <c r="T628" s="11"/>
       <c r="U628" s="11"/>
       <c r="V628" s="11"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" spans="20:22" ht="15.75" customHeight="1">
       <c r="T629" s="11"/>
       <c r="U629" s="11"/>
       <c r="V629" s="11"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" spans="20:22" ht="15.75" customHeight="1">
       <c r="T630" s="11"/>
       <c r="U630" s="11"/>
       <c r="V630" s="11"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" spans="20:22" ht="15.75" customHeight="1">
       <c r="T631" s="11"/>
       <c r="U631" s="11"/>
       <c r="V631" s="11"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" spans="20:22" ht="15.75" customHeight="1">
       <c r="T632" s="11"/>
       <c r="U632" s="11"/>
       <c r="V632" s="11"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" spans="20:22" ht="15.75" customHeight="1">
       <c r="T633" s="11"/>
       <c r="U633" s="11"/>
       <c r="V633" s="11"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" spans="20:22" ht="15.75" customHeight="1">
       <c r="T634" s="11"/>
       <c r="U634" s="11"/>
       <c r="V634" s="11"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" spans="20:22" ht="15.75" customHeight="1">
       <c r="T635" s="11"/>
       <c r="U635" s="11"/>
       <c r="V635" s="11"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" spans="20:22" ht="15.75" customHeight="1">
       <c r="T636" s="11"/>
       <c r="U636" s="11"/>
       <c r="V636" s="11"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" spans="20:22" ht="15.75" customHeight="1">
       <c r="T637" s="11"/>
       <c r="U637" s="11"/>
       <c r="V637" s="11"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" spans="20:22" ht="15.75" customHeight="1">
       <c r="T638" s="11"/>
       <c r="U638" s="11"/>
       <c r="V638" s="11"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" spans="20:22" ht="15.75" customHeight="1">
       <c r="T639" s="11"/>
       <c r="U639" s="11"/>
       <c r="V639" s="11"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" spans="20:22" ht="15.75" customHeight="1">
       <c r="T640" s="11"/>
       <c r="U640" s="11"/>
       <c r="V640" s="11"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" spans="20:22" ht="15.75" customHeight="1">
       <c r="T641" s="11"/>
       <c r="U641" s="11"/>
       <c r="V641" s="11"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" spans="20:22" ht="15.75" customHeight="1">
       <c r="T642" s="11"/>
       <c r="U642" s="11"/>
       <c r="V642" s="11"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" spans="20:22" ht="15.75" customHeight="1">
       <c r="T643" s="11"/>
       <c r="U643" s="11"/>
       <c r="V643" s="11"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" spans="20:22" ht="15.75" customHeight="1">
       <c r="T644" s="11"/>
       <c r="U644" s="11"/>
       <c r="V644" s="11"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" spans="20:22" ht="15.75" customHeight="1">
       <c r="T645" s="11"/>
       <c r="U645" s="11"/>
       <c r="V645" s="11"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" spans="20:22" ht="15.75" customHeight="1">
       <c r="T646" s="11"/>
       <c r="U646" s="11"/>
       <c r="V646" s="11"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" spans="20:22" ht="15.75" customHeight="1">
       <c r="T647" s="11"/>
       <c r="U647" s="11"/>
       <c r="V647" s="11"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" spans="20:22" ht="15.75" customHeight="1">
       <c r="T648" s="11"/>
       <c r="U648" s="11"/>
       <c r="V648" s="11"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" spans="20:22" ht="15.75" customHeight="1">
       <c r="T649" s="11"/>
       <c r="U649" s="11"/>
       <c r="V649" s="11"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" spans="20:22" ht="15.75" customHeight="1">
       <c r="T650" s="11"/>
       <c r="U650" s="11"/>
       <c r="V650" s="11"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" spans="20:22" ht="15.75" customHeight="1">
       <c r="T651" s="11"/>
       <c r="U651" s="11"/>
       <c r="V651" s="11"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" spans="20:22" ht="15.75" customHeight="1">
       <c r="T652" s="11"/>
       <c r="U652" s="11"/>
       <c r="V652" s="11"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" spans="20:22" ht="15.75" customHeight="1">
       <c r="T653" s="11"/>
       <c r="U653" s="11"/>
       <c r="V653" s="11"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" spans="20:22" ht="15.75" customHeight="1">
       <c r="T654" s="11"/>
       <c r="U654" s="11"/>
       <c r="V654" s="11"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" spans="20:22" ht="15.75" customHeight="1">
       <c r="T655" s="11"/>
       <c r="U655" s="11"/>
       <c r="V655" s="11"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" spans="20:22" ht="15.75" customHeight="1">
       <c r="T656" s="11"/>
       <c r="U656" s="11"/>
       <c r="V656" s="11"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" spans="20:22" ht="15.75" customHeight="1">
       <c r="T657" s="11"/>
       <c r="U657" s="11"/>
       <c r="V657" s="11"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" spans="20:22" ht="15.75" customHeight="1">
       <c r="T658" s="11"/>
       <c r="U658" s="11"/>
       <c r="V658" s="11"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" spans="20:22" ht="15.75" customHeight="1">
       <c r="T659" s="11"/>
       <c r="U659" s="11"/>
       <c r="V659" s="11"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" spans="20:22" ht="15.75" customHeight="1">
       <c r="T660" s="11"/>
       <c r="U660" s="11"/>
       <c r="V660" s="11"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" spans="20:22" ht="15.75" customHeight="1">
       <c r="T661" s="11"/>
       <c r="U661" s="11"/>
       <c r="V661" s="11"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" spans="20:22" ht="15.75" customHeight="1">
       <c r="T662" s="11"/>
       <c r="U662" s="11"/>
       <c r="V662" s="11"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" spans="20:22" ht="15.75" customHeight="1">
       <c r="T663" s="11"/>
       <c r="U663" s="11"/>
       <c r="V663" s="11"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" spans="20:22" ht="15.75" customHeight="1">
       <c r="T664" s="11"/>
       <c r="U664" s="11"/>
       <c r="V664" s="11"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" spans="20:22" ht="15.75" customHeight="1">
       <c r="T665" s="11"/>
       <c r="U665" s="11"/>
       <c r="V665" s="11"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" spans="20:22" ht="15.75" customHeight="1">
       <c r="T666" s="11"/>
       <c r="U666" s="11"/>
       <c r="V666" s="11"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" spans="20:22" ht="15.75" customHeight="1">
       <c r="T667" s="11"/>
       <c r="U667" s="11"/>
       <c r="V667" s="11"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" spans="20:22" ht="15.75" customHeight="1">
       <c r="T668" s="11"/>
       <c r="U668" s="11"/>
       <c r="V668" s="11"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" spans="20:22" ht="15.75" customHeight="1">
       <c r="T669" s="11"/>
       <c r="U669" s="11"/>
       <c r="V669" s="11"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" spans="20:22" ht="15.75" customHeight="1">
       <c r="T670" s="11"/>
       <c r="U670" s="11"/>
       <c r="V670" s="11"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" spans="20:22" ht="15.75" customHeight="1">
       <c r="T671" s="11"/>
       <c r="U671" s="11"/>
       <c r="V671" s="11"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" spans="20:22" ht="15.75" customHeight="1">
       <c r="T672" s="11"/>
       <c r="U672" s="11"/>
       <c r="V672" s="11"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" spans="20:22" ht="15.75" customHeight="1">
       <c r="T673" s="11"/>
       <c r="U673" s="11"/>
       <c r="V673" s="11"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" spans="20:22" ht="15.75" customHeight="1">
       <c r="T674" s="11"/>
       <c r="U674" s="11"/>
       <c r="V674" s="11"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" spans="20:22" ht="15.75" customHeight="1">
       <c r="T675" s="11"/>
       <c r="U675" s="11"/>
       <c r="V675" s="11"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" spans="20:22" ht="15.75" customHeight="1">
       <c r="T676" s="11"/>
       <c r="U676" s="11"/>
       <c r="V676" s="11"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" spans="20:22" ht="15.75" customHeight="1">
       <c r="T677" s="11"/>
       <c r="U677" s="11"/>
       <c r="V677" s="11"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" spans="20:22" ht="15.75" customHeight="1">
       <c r="T678" s="11"/>
       <c r="U678" s="11"/>
       <c r="V678" s="11"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" spans="20:22" ht="15.75" customHeight="1">
       <c r="T679" s="11"/>
       <c r="U679" s="11"/>
       <c r="V679" s="11"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" spans="20:22" ht="15.75" customHeight="1">
       <c r="T680" s="11"/>
       <c r="U680" s="11"/>
       <c r="V680" s="11"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" spans="20:22" ht="15.75" customHeight="1">
       <c r="T681" s="11"/>
       <c r="U681" s="11"/>
       <c r="V681" s="11"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" spans="20:22" ht="15.75" customHeight="1">
       <c r="T682" s="11"/>
       <c r="U682" s="11"/>
       <c r="V682" s="11"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" spans="20:22" ht="15.75" customHeight="1">
       <c r="T683" s="11"/>
       <c r="U683" s="11"/>
       <c r="V683" s="11"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" spans="20:22" ht="15.75" customHeight="1">
       <c r="T684" s="11"/>
       <c r="U684" s="11"/>
       <c r="V684" s="11"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" spans="20:22" ht="15.75" customHeight="1">
       <c r="T685" s="11"/>
       <c r="U685" s="11"/>
       <c r="V685" s="11"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" spans="20:22" ht="15.75" customHeight="1">
       <c r="T686" s="11"/>
       <c r="U686" s="11"/>
       <c r="V686" s="11"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" spans="20:22" ht="15.75" customHeight="1">
       <c r="T687" s="11"/>
       <c r="U687" s="11"/>
       <c r="V687" s="11"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" spans="20:22" ht="15.75" customHeight="1">
       <c r="T688" s="11"/>
       <c r="U688" s="11"/>
       <c r="V688" s="11"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" spans="20:22" ht="15.75" customHeight="1">
       <c r="T689" s="11"/>
       <c r="U689" s="11"/>
       <c r="V689" s="11"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" spans="20:22" ht="15.75" customHeight="1">
       <c r="T690" s="11"/>
       <c r="U690" s="11"/>
       <c r="V690" s="11"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" spans="20:22" ht="15.75" customHeight="1">
       <c r="T691" s="11"/>
       <c r="U691" s="11"/>
       <c r="V691" s="11"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" spans="20:22" ht="15.75" customHeight="1">
       <c r="T692" s="11"/>
       <c r="U692" s="11"/>
       <c r="V692" s="11"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" spans="20:22" ht="15.75" customHeight="1">
       <c r="T693" s="11"/>
       <c r="U693" s="11"/>
       <c r="V693" s="11"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" spans="20:22" ht="15.75" customHeight="1">
       <c r="T694" s="11"/>
       <c r="U694" s="11"/>
       <c r="V694" s="11"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" spans="20:22" ht="15.75" customHeight="1">
       <c r="T695" s="11"/>
       <c r="U695" s="11"/>
       <c r="V695" s="11"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" spans="20:22" ht="15.75" customHeight="1">
       <c r="T696" s="11"/>
       <c r="U696" s="11"/>
       <c r="V696" s="11"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" spans="20:22" ht="15.75" customHeight="1">
       <c r="T697" s="11"/>
       <c r="U697" s="11"/>
       <c r="V697" s="11"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" spans="20:22" ht="15.75" customHeight="1">
       <c r="T698" s="11"/>
       <c r="U698" s="11"/>
       <c r="V698" s="11"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" spans="20:22" ht="15.75" customHeight="1">
       <c r="T699" s="11"/>
       <c r="U699" s="11"/>
       <c r="V699" s="11"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" spans="20:22" ht="15.75" customHeight="1">
       <c r="T700" s="11"/>
       <c r="U700" s="11"/>
       <c r="V700" s="11"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" spans="20:22" ht="15.75" customHeight="1">
       <c r="T701" s="11"/>
       <c r="U701" s="11"/>
       <c r="V701" s="11"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" spans="20:22" ht="15.75" customHeight="1">
       <c r="T702" s="11"/>
       <c r="U702" s="11"/>
       <c r="V702" s="11"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" spans="20:22" ht="15.75" customHeight="1">
       <c r="T703" s="11"/>
       <c r="U703" s="11"/>
       <c r="V703" s="11"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" spans="20:22" ht="15.75" customHeight="1">
       <c r="T704" s="11"/>
       <c r="U704" s="11"/>
       <c r="V704" s="11"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" spans="20:22" ht="15.75" customHeight="1">
       <c r="T705" s="11"/>
       <c r="U705" s="11"/>
       <c r="V705" s="11"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" spans="20:22" ht="15.75" customHeight="1">
       <c r="T706" s="11"/>
       <c r="U706" s="11"/>
       <c r="V706" s="11"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" spans="20:22" ht="15.75" customHeight="1">
       <c r="T707" s="11"/>
       <c r="U707" s="11"/>
       <c r="V707" s="11"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" spans="20:22" ht="15.75" customHeight="1">
       <c r="T708" s="11"/>
       <c r="U708" s="11"/>
       <c r="V708" s="11"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" spans="20:22" ht="15.75" customHeight="1">
       <c r="T709" s="11"/>
       <c r="U709" s="11"/>
       <c r="V709" s="11"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" spans="20:22" ht="15.75" customHeight="1">
       <c r="T710" s="11"/>
       <c r="U710" s="11"/>
       <c r="V710" s="11"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" spans="20:22" ht="15.75" customHeight="1">
       <c r="T711" s="11"/>
       <c r="U711" s="11"/>
       <c r="V711" s="11"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" spans="20:22" ht="15.75" customHeight="1">
       <c r="T712" s="11"/>
       <c r="U712" s="11"/>
       <c r="V712" s="11"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" spans="20:22" ht="15.75" customHeight="1">
       <c r="T713" s="11"/>
       <c r="U713" s="11"/>
       <c r="V713" s="11"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" spans="20:22" ht="15.75" customHeight="1">
       <c r="T714" s="11"/>
       <c r="U714" s="11"/>
       <c r="V714" s="11"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" spans="20:22" ht="15.75" customHeight="1">
       <c r="T715" s="11"/>
       <c r="U715" s="11"/>
       <c r="V715" s="11"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" spans="20:22" ht="15.75" customHeight="1">
       <c r="T716" s="11"/>
       <c r="U716" s="11"/>
       <c r="V716" s="11"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" spans="20:22" ht="15.75" customHeight="1">
       <c r="T717" s="11"/>
       <c r="U717" s="11"/>
       <c r="V717" s="11"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" spans="20:22" ht="15.75" customHeight="1">
       <c r="T718" s="11"/>
       <c r="U718" s="11"/>
       <c r="V718" s="11"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" spans="20:22" ht="15.75" customHeight="1">
       <c r="T719" s="11"/>
       <c r="U719" s="11"/>
       <c r="V719" s="11"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" spans="20:22" ht="15.75" customHeight="1">
       <c r="T720" s="11"/>
       <c r="U720" s="11"/>
       <c r="V720" s="11"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" spans="20:22" ht="15.75" customHeight="1">
       <c r="T721" s="11"/>
       <c r="U721" s="11"/>
       <c r="V721" s="11"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" spans="20:22" ht="15.75" customHeight="1">
       <c r="T722" s="11"/>
       <c r="U722" s="11"/>
       <c r="V722" s="11"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" spans="20:22" ht="15.75" customHeight="1">
       <c r="T723" s="11"/>
       <c r="U723" s="11"/>
       <c r="V723" s="11"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" spans="20:22" ht="15.75" customHeight="1">
       <c r="T724" s="11"/>
       <c r="U724" s="11"/>
       <c r="V724" s="11"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" spans="20:22" ht="15.75" customHeight="1">
       <c r="T725" s="11"/>
       <c r="U725" s="11"/>
       <c r="V725" s="11"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" spans="20:22" ht="15.75" customHeight="1">
       <c r="T726" s="11"/>
       <c r="U726" s="11"/>
       <c r="V726" s="11"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" spans="20:22" ht="15.75" customHeight="1">
       <c r="T727" s="11"/>
       <c r="U727" s="11"/>
       <c r="V727" s="11"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" spans="20:22" ht="15.75" customHeight="1">
       <c r="T728" s="11"/>
       <c r="U728" s="11"/>
       <c r="V728" s="11"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" spans="20:22" ht="15.75" customHeight="1">
       <c r="T729" s="11"/>
       <c r="U729" s="11"/>
       <c r="V729" s="11"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" spans="20:22" ht="15.75" customHeight="1">
       <c r="T730" s="11"/>
       <c r="U730" s="11"/>
       <c r="V730" s="11"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" spans="20:22" ht="15.75" customHeight="1">
       <c r="T731" s="11"/>
       <c r="U731" s="11"/>
       <c r="V731" s="11"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" spans="20:22" ht="15.75" customHeight="1">
       <c r="T732" s="11"/>
       <c r="U732" s="11"/>
       <c r="V732" s="11"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" spans="20:22" ht="15.75" customHeight="1">
       <c r="T733" s="11"/>
       <c r="U733" s="11"/>
       <c r="V733" s="11"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" spans="20:22" ht="15.75" customHeight="1">
       <c r="T734" s="11"/>
       <c r="U734" s="11"/>
       <c r="V734" s="11"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" spans="20:22" ht="15.75" customHeight="1">
       <c r="T735" s="11"/>
       <c r="U735" s="11"/>
       <c r="V735" s="11"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" spans="20:22" ht="15.75" customHeight="1">
       <c r="T736" s="11"/>
       <c r="U736" s="11"/>
       <c r="V736" s="11"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" spans="20:22" ht="15.75" customHeight="1">
       <c r="T737" s="11"/>
       <c r="U737" s="11"/>
       <c r="V737" s="11"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" spans="20:22" ht="15.75" customHeight="1">
       <c r="T738" s="11"/>
       <c r="U738" s="11"/>
       <c r="V738" s="11"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" spans="20:22" ht="15.75" customHeight="1">
       <c r="T739" s="11"/>
       <c r="U739" s="11"/>
       <c r="V739" s="11"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" spans="20:22" ht="15.75" customHeight="1">
       <c r="T740" s="11"/>
       <c r="U740" s="11"/>
       <c r="V740" s="11"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" spans="20:22" ht="15.75" customHeight="1">
       <c r="T741" s="11"/>
       <c r="U741" s="11"/>
       <c r="V741" s="11"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" spans="20:22" ht="15.75" customHeight="1">
       <c r="T742" s="11"/>
       <c r="U742" s="11"/>
       <c r="V742" s="11"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" spans="20:22" ht="15.75" customHeight="1">
       <c r="T743" s="11"/>
       <c r="U743" s="11"/>
       <c r="V743" s="11"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" spans="20:22" ht="15.75" customHeight="1">
       <c r="T744" s="11"/>
       <c r="U744" s="11"/>
       <c r="V744" s="11"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" spans="20:22" ht="15.75" customHeight="1">
       <c r="T745" s="11"/>
       <c r="U745" s="11"/>
       <c r="V745" s="11"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" spans="20:22" ht="15.75" customHeight="1">
       <c r="T746" s="11"/>
       <c r="U746" s="11"/>
       <c r="V746" s="11"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" spans="20:22" ht="15.75" customHeight="1">
       <c r="T747" s="11"/>
       <c r="U747" s="11"/>
       <c r="V747" s="11"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" spans="20:22" ht="15.75" customHeight="1">
       <c r="T748" s="11"/>
       <c r="U748" s="11"/>
       <c r="V748" s="11"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" spans="20:22" ht="15.75" customHeight="1">
       <c r="T749" s="11"/>
       <c r="U749" s="11"/>
       <c r="V749" s="11"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" spans="20:22" ht="15.75" customHeight="1">
       <c r="T750" s="11"/>
       <c r="U750" s="11"/>
       <c r="V750" s="11"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" spans="20:22" ht="15.75" customHeight="1">
       <c r="T751" s="11"/>
       <c r="U751" s="11"/>
       <c r="V751" s="11"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" spans="20:22" ht="15.75" customHeight="1">
       <c r="T752" s="11"/>
       <c r="U752" s="11"/>
       <c r="V752" s="11"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" spans="20:22" ht="15.75" customHeight="1">
       <c r="T753" s="11"/>
       <c r="U753" s="11"/>
       <c r="V753" s="11"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" spans="20:22" ht="15.75" customHeight="1">
       <c r="T754" s="11"/>
       <c r="U754" s="11"/>
       <c r="V754" s="11"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" spans="20:22" ht="15.75" customHeight="1">
       <c r="T755" s="11"/>
       <c r="U755" s="11"/>
       <c r="V755" s="11"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" spans="20:22" ht="15.75" customHeight="1">
       <c r="T756" s="11"/>
       <c r="U756" s="11"/>
       <c r="V756" s="11"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" spans="20:22" ht="15.75" customHeight="1">
       <c r="T757" s="11"/>
       <c r="U757" s="11"/>
       <c r="V757" s="11"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" spans="20:22" ht="15.75" customHeight="1">
       <c r="T758" s="11"/>
       <c r="U758" s="11"/>
       <c r="V758" s="11"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" spans="20:22" ht="15.75" customHeight="1">
       <c r="T759" s="11"/>
       <c r="U759" s="11"/>
       <c r="V759" s="11"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" spans="20:22" ht="15.75" customHeight="1">
       <c r="T760" s="11"/>
       <c r="U760" s="11"/>
       <c r="V760" s="11"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" spans="20:22" ht="15.75" customHeight="1">
       <c r="T761" s="11"/>
       <c r="U761" s="11"/>
       <c r="V761" s="11"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" spans="20:22" ht="15.75" customHeight="1">
       <c r="T762" s="11"/>
       <c r="U762" s="11"/>
       <c r="V762" s="11"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" spans="20:22" ht="15.75" customHeight="1">
       <c r="T763" s="11"/>
       <c r="U763" s="11"/>
       <c r="V763" s="11"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" spans="20:22" ht="15.75" customHeight="1">
       <c r="T764" s="11"/>
       <c r="U764" s="11"/>
       <c r="V764" s="11"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" spans="20:22" ht="15.75" customHeight="1">
       <c r="T765" s="11"/>
       <c r="U765" s="11"/>
       <c r="V765" s="11"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" spans="20:22" ht="15.75" customHeight="1">
       <c r="T766" s="11"/>
       <c r="U766" s="11"/>
       <c r="V766" s="11"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" spans="20:22" ht="15.75" customHeight="1">
       <c r="T767" s="11"/>
       <c r="U767" s="11"/>
       <c r="V767" s="11"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" spans="20:22" ht="15.75" customHeight="1">
       <c r="T768" s="11"/>
       <c r="U768" s="11"/>
       <c r="V768" s="11"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" spans="20:22" ht="15.75" customHeight="1">
       <c r="T769" s="11"/>
       <c r="U769" s="11"/>
       <c r="V769" s="11"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" spans="20:22" ht="15.75" customHeight="1">
       <c r="T770" s="11"/>
       <c r="U770" s="11"/>
       <c r="V770" s="11"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" spans="20:22" ht="15.75" customHeight="1">
       <c r="T771" s="11"/>
       <c r="U771" s="11"/>
       <c r="V771" s="11"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" spans="20:22" ht="15.75" customHeight="1">
       <c r="T772" s="11"/>
       <c r="U772" s="11"/>
       <c r="V772" s="11"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" spans="20:22" ht="15.75" customHeight="1">
       <c r="T773" s="11"/>
       <c r="U773" s="11"/>
       <c r="V773" s="11"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" spans="20:22" ht="15.75" customHeight="1">
       <c r="T774" s="11"/>
       <c r="U774" s="11"/>
       <c r="V774" s="11"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" spans="20:22" ht="15.75" customHeight="1">
       <c r="T775" s="11"/>
       <c r="U775" s="11"/>
       <c r="V775" s="11"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" spans="20:22" ht="15.75" customHeight="1">
       <c r="T776" s="11"/>
       <c r="U776" s="11"/>
       <c r="V776" s="11"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" spans="20:22" ht="15.75" customHeight="1">
       <c r="T777" s="11"/>
       <c r="U777" s="11"/>
       <c r="V777" s="11"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" spans="20:22" ht="15.75" customHeight="1">
       <c r="T778" s="11"/>
       <c r="U778" s="11"/>
       <c r="V778" s="11"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" spans="20:22" ht="15.75" customHeight="1">
       <c r="T779" s="11"/>
       <c r="U779" s="11"/>
       <c r="V779" s="11"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" spans="20:22" ht="15.75" customHeight="1">
       <c r="T780" s="11"/>
       <c r="U780" s="11"/>
       <c r="V780" s="11"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" spans="20:22" ht="15.75" customHeight="1">
       <c r="T781" s="11"/>
       <c r="U781" s="11"/>
       <c r="V781" s="11"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" spans="20:22" ht="15.75" customHeight="1">
       <c r="T782" s="11"/>
       <c r="U782" s="11"/>
       <c r="V782" s="11"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" spans="20:22" ht="15.75" customHeight="1">
       <c r="T783" s="11"/>
       <c r="U783" s="11"/>
       <c r="V783" s="11"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" spans="20:22" ht="15.75" customHeight="1">
       <c r="T784" s="11"/>
       <c r="U784" s="11"/>
       <c r="V784" s="11"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" spans="20:22" ht="15.75" customHeight="1">
       <c r="T785" s="11"/>
       <c r="U785" s="11"/>
       <c r="V785" s="11"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" spans="20:22" ht="15.75" customHeight="1">
       <c r="T786" s="11"/>
       <c r="U786" s="11"/>
       <c r="V786" s="11"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" spans="20:22" ht="15.75" customHeight="1">
       <c r="T787" s="11"/>
       <c r="U787" s="11"/>
       <c r="V787" s="11"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" spans="20:22" ht="15.75" customHeight="1">
       <c r="T788" s="11"/>
       <c r="U788" s="11"/>
       <c r="V788" s="11"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" spans="20:22" ht="15.75" customHeight="1">
       <c r="T789" s="11"/>
       <c r="U789" s="11"/>
       <c r="V789" s="11"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" spans="20:22" ht="15.75" customHeight="1">
       <c r="T790" s="11"/>
       <c r="U790" s="11"/>
       <c r="V790" s="11"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" spans="20:22" ht="15.75" customHeight="1">
       <c r="T791" s="11"/>
       <c r="U791" s="11"/>
       <c r="V791" s="11"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" spans="20:22" ht="15.75" customHeight="1">
       <c r="T792" s="11"/>
       <c r="U792" s="11"/>
       <c r="V792" s="11"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" spans="20:22" ht="15.75" customHeight="1">
       <c r="T793" s="11"/>
       <c r="U793" s="11"/>
       <c r="V793" s="11"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" spans="20:22" ht="15.75" customHeight="1">
       <c r="T794" s="11"/>
       <c r="U794" s="11"/>
       <c r="V794" s="11"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" spans="20:22" ht="15.75" customHeight="1">
       <c r="T795" s="11"/>
       <c r="U795" s="11"/>
       <c r="V795" s="11"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" spans="20:22" ht="15.75" customHeight="1">
       <c r="T796" s="11"/>
       <c r="U796" s="11"/>
       <c r="V796" s="11"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" spans="20:22" ht="15.75" customHeight="1">
       <c r="T797" s="11"/>
       <c r="U797" s="11"/>
       <c r="V797" s="11"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" spans="20:22" ht="15.75" customHeight="1">
       <c r="T798" s="11"/>
       <c r="U798" s="11"/>
       <c r="V798" s="11"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" spans="20:22" ht="15.75" customHeight="1">
       <c r="T799" s="11"/>
       <c r="U799" s="11"/>
       <c r="V799" s="11"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" spans="20:22" ht="15.75" customHeight="1">
       <c r="T800" s="11"/>
       <c r="U800" s="11"/>
       <c r="V800" s="11"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" spans="20:22" ht="15.75" customHeight="1">
       <c r="T801" s="11"/>
       <c r="U801" s="11"/>
       <c r="V801" s="11"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" spans="20:22" ht="15.75" customHeight="1">
       <c r="T802" s="11"/>
       <c r="U802" s="11"/>
       <c r="V802" s="11"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" spans="20:22" ht="15.75" customHeight="1">
       <c r="T803" s="11"/>
       <c r="U803" s="11"/>
       <c r="V803" s="11"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" spans="20:22" ht="15.75" customHeight="1">
       <c r="T804" s="11"/>
       <c r="U804" s="11"/>
       <c r="V804" s="11"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" spans="20:22" ht="15.75" customHeight="1">
       <c r="T805" s="11"/>
       <c r="U805" s="11"/>
       <c r="V805" s="11"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" spans="20:22" ht="15.75" customHeight="1">
       <c r="T806" s="11"/>
       <c r="U806" s="11"/>
       <c r="V806" s="11"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" spans="20:22" ht="15.75" customHeight="1">
       <c r="T807" s="11"/>
       <c r="U807" s="11"/>
       <c r="V807" s="11"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" spans="20:22" ht="15.75" customHeight="1">
       <c r="T808" s="11"/>
       <c r="U808" s="11"/>
       <c r="V808" s="11"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" spans="20:22" ht="15.75" customHeight="1">
       <c r="T809" s="11"/>
       <c r="U809" s="11"/>
       <c r="V809" s="11"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" spans="20:22" ht="15.75" customHeight="1">
       <c r="T810" s="11"/>
       <c r="U810" s="11"/>
       <c r="V810" s="11"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" spans="20:22" ht="15.75" customHeight="1">
       <c r="T811" s="11"/>
       <c r="U811" s="11"/>
       <c r="V811" s="11"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" spans="20:22" ht="15.75" customHeight="1">
       <c r="T812" s="11"/>
       <c r="U812" s="11"/>
       <c r="V812" s="11"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" spans="20:22" ht="15.75" customHeight="1">
       <c r="T813" s="11"/>
       <c r="U813" s="11"/>
       <c r="V813" s="11"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" spans="20:22" ht="15.75" customHeight="1">
       <c r="T814" s="11"/>
       <c r="U814" s="11"/>
       <c r="V814" s="11"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" spans="20:22" ht="15.75" customHeight="1">
       <c r="T815" s="11"/>
       <c r="U815" s="11"/>
       <c r="V815" s="11"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" spans="20:22" ht="15.75" customHeight="1">
       <c r="T816" s="11"/>
       <c r="U816" s="11"/>
       <c r="V816" s="11"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" spans="20:22" ht="15.75" customHeight="1">
       <c r="T817" s="11"/>
       <c r="U817" s="11"/>
       <c r="V817" s="11"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" spans="20:22" ht="15.75" customHeight="1">
       <c r="T818" s="11"/>
       <c r="U818" s="11"/>
       <c r="V818" s="11"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" spans="20:22" ht="15.75" customHeight="1">
       <c r="T819" s="11"/>
       <c r="U819" s="11"/>
       <c r="V819" s="11"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" spans="20:22" ht="15.75" customHeight="1">
       <c r="T820" s="11"/>
       <c r="U820" s="11"/>
       <c r="V820" s="11"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" spans="20:22" ht="15.75" customHeight="1">
       <c r="T821" s="11"/>
       <c r="U821" s="11"/>
       <c r="V821" s="11"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" spans="20:22" ht="15.75" customHeight="1">
       <c r="T822" s="11"/>
       <c r="U822" s="11"/>
       <c r="V822" s="11"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" spans="20:22" ht="15.75" customHeight="1">
       <c r="T823" s="11"/>
       <c r="U823" s="11"/>
       <c r="V823" s="11"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" spans="20:22" ht="15.75" customHeight="1">
       <c r="T824" s="11"/>
       <c r="U824" s="11"/>
       <c r="V824" s="11"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" spans="20:22" ht="15.75" customHeight="1">
       <c r="T825" s="11"/>
       <c r="U825" s="11"/>
       <c r="V825" s="11"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" spans="20:22" ht="15.75" customHeight="1">
       <c r="T826" s="11"/>
       <c r="U826" s="11"/>
       <c r="V826" s="11"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" spans="20:22" ht="15.75" customHeight="1">
       <c r="T827" s="11"/>
       <c r="U827" s="11"/>
       <c r="V827" s="11"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" spans="20:22" ht="15.75" customHeight="1">
       <c r="T828" s="11"/>
       <c r="U828" s="11"/>
       <c r="V828" s="11"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" spans="20:22" ht="15.75" customHeight="1">
       <c r="T829" s="11"/>
       <c r="U829" s="11"/>
       <c r="V829" s="11"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" spans="20:22" ht="15.75" customHeight="1">
       <c r="T830" s="11"/>
       <c r="U830" s="11"/>
       <c r="V830" s="11"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" spans="20:22" ht="15.75" customHeight="1">
       <c r="T831" s="11"/>
       <c r="U831" s="11"/>
       <c r="V831" s="11"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" spans="20:22" ht="15.75" customHeight="1">
       <c r="T832" s="11"/>
       <c r="U832" s="11"/>
       <c r="V832" s="11"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" spans="20:22" ht="15.75" customHeight="1">
       <c r="T833" s="11"/>
       <c r="U833" s="11"/>
       <c r="V833" s="11"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" spans="20:22" ht="15.75" customHeight="1">
       <c r="T834" s="11"/>
       <c r="U834" s="11"/>
       <c r="V834" s="11"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" spans="20:22" ht="15.75" customHeight="1">
       <c r="T835" s="11"/>
       <c r="U835" s="11"/>
       <c r="V835" s="11"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" spans="20:22" ht="15.75" customHeight="1">
       <c r="T836" s="11"/>
       <c r="U836" s="11"/>
       <c r="V836" s="11"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" spans="20:22" ht="15.75" customHeight="1">
       <c r="T837" s="11"/>
       <c r="U837" s="11"/>
       <c r="V837" s="11"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" spans="20:22" ht="15.75" customHeight="1">
       <c r="T838" s="11"/>
       <c r="U838" s="11"/>
       <c r="V838" s="11"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" spans="20:22" ht="15.75" customHeight="1">
       <c r="T839" s="11"/>
       <c r="U839" s="11"/>
       <c r="V839" s="11"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" spans="20:22" ht="15.75" customHeight="1">
       <c r="T840" s="11"/>
       <c r="U840" s="11"/>
       <c r="V840" s="11"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" spans="20:22" ht="15.75" customHeight="1">
       <c r="T841" s="11"/>
       <c r="U841" s="11"/>
       <c r="V841" s="11"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" spans="20:22" ht="15.75" customHeight="1">
       <c r="T842" s="11"/>
       <c r="U842" s="11"/>
       <c r="V842" s="11"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" spans="20:22" ht="15.75" customHeight="1">
       <c r="T843" s="11"/>
       <c r="U843" s="11"/>
       <c r="V843" s="11"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" spans="20:22" ht="15.75" customHeight="1">
       <c r="T844" s="11"/>
       <c r="U844" s="11"/>
       <c r="V844" s="11"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" spans="20:22" ht="15.75" customHeight="1">
       <c r="T845" s="11"/>
       <c r="U845" s="11"/>
       <c r="V845" s="11"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" spans="20:22" ht="15.75" customHeight="1">
       <c r="T846" s="11"/>
       <c r="U846" s="11"/>
       <c r="V846" s="11"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" spans="20:22" ht="15.75" customHeight="1">
       <c r="T847" s="11"/>
       <c r="U847" s="11"/>
       <c r="V847" s="11"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" spans="20:22" ht="15.75" customHeight="1">
       <c r="T848" s="11"/>
       <c r="U848" s="11"/>
       <c r="V848" s="11"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" spans="20:22" ht="15.75" customHeight="1">
       <c r="T849" s="11"/>
       <c r="U849" s="11"/>
       <c r="V849" s="11"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" spans="20:22" ht="15.75" customHeight="1">
       <c r="T850" s="11"/>
       <c r="U850" s="11"/>
       <c r="V850" s="11"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" spans="20:22" ht="15.75" customHeight="1">
       <c r="T851" s="11"/>
       <c r="U851" s="11"/>
       <c r="V851" s="11"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" spans="20:22" ht="15.75" customHeight="1">
       <c r="T852" s="11"/>
       <c r="U852" s="11"/>
       <c r="V852" s="11"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" spans="20:22" ht="15.75" customHeight="1">
       <c r="T853" s="11"/>
       <c r="U853" s="11"/>
       <c r="V853" s="11"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" spans="20:22" ht="15.75" customHeight="1">
       <c r="T854" s="11"/>
       <c r="U854" s="11"/>
       <c r="V854" s="11"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" spans="20:22" ht="15.75" customHeight="1">
       <c r="T855" s="11"/>
       <c r="U855" s="11"/>
       <c r="V855" s="11"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" spans="20:22" ht="15.75" customHeight="1">
       <c r="T856" s="11"/>
       <c r="U856" s="11"/>
       <c r="V856" s="11"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" spans="20:22" ht="15.75" customHeight="1">
       <c r="T857" s="11"/>
       <c r="U857" s="11"/>
       <c r="V857" s="11"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" spans="20:22" ht="15.75" customHeight="1">
       <c r="T858" s="11"/>
       <c r="U858" s="11"/>
       <c r="V858" s="11"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" spans="20:22" ht="15.75" customHeight="1">
       <c r="T859" s="11"/>
       <c r="U859" s="11"/>
       <c r="V859" s="11"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" spans="20:22" ht="15.75" customHeight="1">
       <c r="T860" s="11"/>
       <c r="U860" s="11"/>
       <c r="V860" s="11"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" spans="20:22" ht="15.75" customHeight="1">
       <c r="T861" s="11"/>
       <c r="U861" s="11"/>
       <c r="V861" s="11"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" spans="20:22" ht="15.75" customHeight="1">
       <c r="T862" s="11"/>
       <c r="U862" s="11"/>
       <c r="V862" s="11"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" spans="20:22" ht="15.75" customHeight="1">
       <c r="T863" s="11"/>
       <c r="U863" s="11"/>
       <c r="V863" s="11"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" spans="20:22" ht="15.75" customHeight="1">
       <c r="T864" s="11"/>
       <c r="U864" s="11"/>
       <c r="V864" s="11"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" spans="20:22" ht="15.75" customHeight="1">
       <c r="T865" s="11"/>
       <c r="U865" s="11"/>
       <c r="V865" s="11"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" spans="20:22" ht="15.75" customHeight="1">
       <c r="T866" s="11"/>
       <c r="U866" s="11"/>
       <c r="V866" s="11"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" spans="20:22" ht="15.75" customHeight="1">
       <c r="T867" s="11"/>
       <c r="U867" s="11"/>
       <c r="V867" s="11"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" spans="20:22" ht="15.75" customHeight="1">
       <c r="T868" s="11"/>
       <c r="U868" s="11"/>
       <c r="V868" s="11"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" spans="20:22" ht="15.75" customHeight="1">
       <c r="T869" s="11"/>
       <c r="U869" s="11"/>
       <c r="V869" s="11"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" spans="20:22" ht="15.75" customHeight="1">
       <c r="T870" s="11"/>
       <c r="U870" s="11"/>
       <c r="V870" s="11"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" spans="20:22" ht="15.75" customHeight="1">
       <c r="T871" s="11"/>
       <c r="U871" s="11"/>
       <c r="V871" s="11"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" spans="20:22" ht="15.75" customHeight="1">
       <c r="T872" s="11"/>
       <c r="U872" s="11"/>
       <c r="V872" s="11"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" spans="20:22" ht="15.75" customHeight="1">
       <c r="T873" s="11"/>
       <c r="U873" s="11"/>
       <c r="V873" s="11"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" spans="20:22" ht="15.75" customHeight="1">
       <c r="T874" s="11"/>
       <c r="U874" s="11"/>
       <c r="V874" s="11"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" spans="20:22" ht="15.75" customHeight="1">
       <c r="T875" s="11"/>
       <c r="U875" s="11"/>
       <c r="V875" s="11"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" spans="20:22" ht="15.75" customHeight="1">
       <c r="T876" s="11"/>
       <c r="U876" s="11"/>
       <c r="V876" s="11"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" spans="20:22" ht="15.75" customHeight="1">
       <c r="T877" s="11"/>
       <c r="U877" s="11"/>
       <c r="V877" s="11"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" spans="20:22" ht="15.75" customHeight="1">
       <c r="T878" s="11"/>
       <c r="U878" s="11"/>
       <c r="V878" s="11"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" spans="20:22" ht="15.75" customHeight="1">
       <c r="T879" s="11"/>
       <c r="U879" s="11"/>
       <c r="V879" s="11"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" spans="20:22" ht="15.75" customHeight="1">
       <c r="T880" s="11"/>
       <c r="U880" s="11"/>
       <c r="V880" s="11"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" spans="20:22" ht="15.75" customHeight="1">
       <c r="T881" s="11"/>
       <c r="U881" s="11"/>
       <c r="V881" s="11"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" spans="20:22" ht="15.75" customHeight="1">
       <c r="T882" s="11"/>
       <c r="U882" s="11"/>
       <c r="V882" s="11"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" spans="20:22" ht="15.75" customHeight="1">
       <c r="T883" s="11"/>
       <c r="U883" s="11"/>
       <c r="V883" s="11"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" spans="20:22" ht="15.75" customHeight="1">
       <c r="T884" s="11"/>
       <c r="U884" s="11"/>
       <c r="V884" s="11"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" spans="20:22" ht="15.75" customHeight="1">
       <c r="T885" s="11"/>
       <c r="U885" s="11"/>
       <c r="V885" s="11"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" spans="20:22" ht="15.75" customHeight="1">
       <c r="T886" s="11"/>
       <c r="U886" s="11"/>
       <c r="V886" s="11"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" spans="20:22" ht="15.75" customHeight="1">
       <c r="T887" s="11"/>
       <c r="U887" s="11"/>
       <c r="V887" s="11"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" spans="20:22" ht="15.75" customHeight="1">
       <c r="T888" s="11"/>
       <c r="U888" s="11"/>
       <c r="V888" s="11"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" spans="20:22" ht="15.75" customHeight="1">
       <c r="T889" s="11"/>
       <c r="U889" s="11"/>
       <c r="V889" s="11"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" spans="20:22" ht="15.75" customHeight="1">
       <c r="T890" s="11"/>
       <c r="U890" s="11"/>
       <c r="V890" s="11"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" spans="20:22" ht="15.75" customHeight="1">
       <c r="T891" s="11"/>
       <c r="U891" s="11"/>
       <c r="V891" s="11"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" spans="20:22" ht="15.75" customHeight="1">
       <c r="T892" s="11"/>
       <c r="U892" s="11"/>
       <c r="V892" s="11"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" spans="20:22" ht="15.75" customHeight="1">
       <c r="T893" s="11"/>
       <c r="U893" s="11"/>
       <c r="V893" s="11"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" spans="20:22" ht="15.75" customHeight="1">
       <c r="T894" s="11"/>
       <c r="U894" s="11"/>
       <c r="V894" s="11"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" spans="20:22" ht="15.75" customHeight="1">
       <c r="T895" s="11"/>
       <c r="U895" s="11"/>
       <c r="V895" s="11"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" spans="20:22" ht="15.75" customHeight="1">
       <c r="T896" s="11"/>
       <c r="U896" s="11"/>
       <c r="V896" s="11"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" spans="20:22" ht="15.75" customHeight="1">
       <c r="T897" s="11"/>
       <c r="U897" s="11"/>
       <c r="V897" s="11"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" spans="20:22" ht="15.75" customHeight="1">
       <c r="T898" s="11"/>
       <c r="U898" s="11"/>
       <c r="V898" s="11"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" spans="20:22" ht="15.75" customHeight="1">
       <c r="T899" s="11"/>
       <c r="U899" s="11"/>
       <c r="V899" s="11"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" spans="20:22" ht="15.75" customHeight="1">
       <c r="T900" s="11"/>
       <c r="U900" s="11"/>
       <c r="V900" s="11"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" spans="20:22" ht="15.75" customHeight="1">
       <c r="T901" s="11"/>
       <c r="U901" s="11"/>
       <c r="V901" s="11"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" spans="20:22" ht="15.75" customHeight="1">
       <c r="T902" s="11"/>
       <c r="U902" s="11"/>
       <c r="V902" s="11"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" spans="20:22" ht="15.75" customHeight="1">
       <c r="T903" s="11"/>
       <c r="U903" s="11"/>
       <c r="V903" s="11"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" spans="20:22" ht="15.75" customHeight="1">
       <c r="T904" s="11"/>
       <c r="U904" s="11"/>
       <c r="V904" s="11"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" spans="20:22" ht="15.75" customHeight="1">
       <c r="T905" s="11"/>
       <c r="U905" s="11"/>
       <c r="V905" s="11"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" spans="20:22" ht="15.75" customHeight="1">
       <c r="T906" s="11"/>
       <c r="U906" s="11"/>
       <c r="V906" s="11"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" spans="20:22" ht="15.75" customHeight="1">
       <c r="T907" s="11"/>
       <c r="U907" s="11"/>
       <c r="V907" s="11"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" spans="20:22" ht="15.75" customHeight="1">
       <c r="T908" s="11"/>
       <c r="U908" s="11"/>
       <c r="V908" s="11"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" spans="20:22" ht="15.75" customHeight="1">
       <c r="T909" s="11"/>
       <c r="U909" s="11"/>
       <c r="V909" s="11"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" spans="20:22" ht="15.75" customHeight="1">
       <c r="T910" s="11"/>
       <c r="U910" s="11"/>
       <c r="V910" s="11"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" spans="20:22" ht="15.75" customHeight="1">
       <c r="T911" s="11"/>
       <c r="U911" s="11"/>
       <c r="V911" s="11"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" spans="20:22" ht="15.75" customHeight="1">
       <c r="T912" s="11"/>
       <c r="U912" s="11"/>
       <c r="V912" s="11"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" spans="20:22" ht="15.75" customHeight="1">
       <c r="T913" s="11"/>
       <c r="U913" s="11"/>
       <c r="V913" s="11"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" spans="20:22" ht="15.75" customHeight="1">
       <c r="T914" s="11"/>
       <c r="U914" s="11"/>
       <c r="V914" s="11"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" spans="20:22" ht="15.75" customHeight="1">
       <c r="T915" s="11"/>
       <c r="U915" s="11"/>
       <c r="V915" s="11"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" spans="20:22" ht="15.75" customHeight="1">
       <c r="T916" s="11"/>
       <c r="U916" s="11"/>
       <c r="V916" s="11"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" spans="20:22" ht="15.75" customHeight="1">
       <c r="T917" s="11"/>
       <c r="U917" s="11"/>
       <c r="V917" s="11"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" spans="20:22" ht="15.75" customHeight="1">
       <c r="T918" s="11"/>
       <c r="U918" s="11"/>
       <c r="V918" s="11"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" spans="20:22" ht="15.75" customHeight="1">
       <c r="T919" s="11"/>
       <c r="U919" s="11"/>
       <c r="V919" s="11"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" spans="20:22" ht="15.75" customHeight="1">
       <c r="T920" s="11"/>
       <c r="U920" s="11"/>
       <c r="V920" s="11"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" spans="20:22" ht="15.75" customHeight="1">
       <c r="T921" s="11"/>
       <c r="U921" s="11"/>
       <c r="V921" s="11"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" spans="20:22" ht="15.75" customHeight="1">
       <c r="T922" s="11"/>
       <c r="U922" s="11"/>
       <c r="V922" s="11"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" spans="20:22" ht="15.75" customHeight="1">
       <c r="T923" s="11"/>
       <c r="U923" s="11"/>
       <c r="V923" s="11"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" spans="20:22" ht="15.75" customHeight="1">
       <c r="T924" s="11"/>
       <c r="U924" s="11"/>
       <c r="V924" s="11"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" spans="20:22" ht="15.75" customHeight="1">
       <c r="T925" s="11"/>
       <c r="U925" s="11"/>
       <c r="V925" s="11"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" spans="20:22" ht="15.75" customHeight="1">
       <c r="T926" s="11"/>
       <c r="U926" s="11"/>
       <c r="V926" s="11"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" spans="20:22" ht="15.75" customHeight="1">
       <c r="T927" s="11"/>
       <c r="U927" s="11"/>
       <c r="V927" s="11"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" spans="20:22" ht="15.75" customHeight="1">
       <c r="T928" s="11"/>
       <c r="U928" s="11"/>
       <c r="V928" s="11"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" spans="20:22" ht="15.75" customHeight="1">
       <c r="T929" s="11"/>
       <c r="U929" s="11"/>
       <c r="V929" s="11"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" spans="20:22" ht="15.75" customHeight="1">
       <c r="T930" s="11"/>
       <c r="U930" s="11"/>
       <c r="V930" s="11"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" spans="20:22" ht="15.75" customHeight="1">
       <c r="T931" s="11"/>
       <c r="U931" s="11"/>
       <c r="V931" s="11"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" spans="20:22" ht="15.75" customHeight="1">
       <c r="T932" s="11"/>
       <c r="U932" s="11"/>
       <c r="V932" s="11"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" spans="20:22" ht="15.75" customHeight="1">
       <c r="T933" s="11"/>
       <c r="U933" s="11"/>
       <c r="V933" s="11"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" spans="20:22" ht="15.75" customHeight="1">
       <c r="T934" s="11"/>
       <c r="U934" s="11"/>
       <c r="V934" s="11"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" spans="20:22" ht="15.75" customHeight="1">
       <c r="T935" s="11"/>
       <c r="U935" s="11"/>
       <c r="V935" s="11"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" spans="20:22" ht="15.75" customHeight="1">
       <c r="T936" s="11"/>
       <c r="U936" s="11"/>
       <c r="V936" s="11"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" spans="20:22" ht="15.75" customHeight="1">
       <c r="T937" s="11"/>
       <c r="U937" s="11"/>
       <c r="V937" s="11"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" spans="20:22" ht="15.75" customHeight="1">
       <c r="T938" s="11"/>
       <c r="U938" s="11"/>
       <c r="V938" s="11"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" spans="20:22" ht="15.75" customHeight="1">
       <c r="T939" s="11"/>
       <c r="U939" s="11"/>
       <c r="V939" s="11"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" spans="20:22" ht="15.75" customHeight="1">
       <c r="T940" s="11"/>
       <c r="U940" s="11"/>
       <c r="V940" s="11"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" spans="20:22" ht="15.75" customHeight="1">
       <c r="T941" s="11"/>
       <c r="U941" s="11"/>
       <c r="V941" s="11"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" spans="20:22" ht="15.75" customHeight="1">
       <c r="T942" s="11"/>
       <c r="U942" s="11"/>
       <c r="V942" s="11"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" spans="20:22" ht="15.75" customHeight="1">
       <c r="T943" s="11"/>
       <c r="U943" s="11"/>
       <c r="V943" s="11"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" spans="20:22" ht="15.75" customHeight="1">
       <c r="T944" s="11"/>
       <c r="U944" s="11"/>
       <c r="V944" s="11"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" spans="20:22" ht="15.75" customHeight="1">
       <c r="T945" s="11"/>
       <c r="U945" s="11"/>
       <c r="V945" s="11"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" spans="20:22" ht="15.75" customHeight="1">
       <c r="T946" s="11"/>
       <c r="U946" s="11"/>
       <c r="V946" s="11"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" spans="20:22" ht="15.75" customHeight="1">
       <c r="T947" s="11"/>
       <c r="U947" s="11"/>
       <c r="V947" s="11"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" spans="20:22" ht="15.75" customHeight="1">
       <c r="T948" s="11"/>
       <c r="U948" s="11"/>
       <c r="V948" s="11"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" spans="20:22" ht="15.75" customHeight="1">
       <c r="T949" s="11"/>
       <c r="U949" s="11"/>
       <c r="V949" s="11"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" spans="20:22" ht="15.75" customHeight="1">
       <c r="T950" s="11"/>
       <c r="U950" s="11"/>
       <c r="V950" s="11"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" spans="20:22" ht="15.75" customHeight="1">
       <c r="T951" s="11"/>
       <c r="U951" s="11"/>
       <c r="V951" s="11"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" spans="20:22" ht="15.75" customHeight="1">
       <c r="T952" s="11"/>
       <c r="U952" s="11"/>
       <c r="V952" s="11"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" spans="20:22" ht="15.75" customHeight="1">
       <c r="T953" s="11"/>
       <c r="U953" s="11"/>
       <c r="V953" s="11"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" spans="20:22" ht="15.75" customHeight="1">
       <c r="T954" s="11"/>
       <c r="U954" s="11"/>
       <c r="V954" s="11"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" spans="20:22" ht="15.75" customHeight="1">
       <c r="T955" s="11"/>
       <c r="U955" s="11"/>
       <c r="V955" s="11"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" spans="20:22" ht="15.75" customHeight="1">
       <c r="T956" s="11"/>
       <c r="U956" s="11"/>
       <c r="V956" s="11"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" spans="20:22" ht="15.75" customHeight="1">
       <c r="T957" s="11"/>
       <c r="U957" s="11"/>
       <c r="V957" s="11"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" spans="20:22" ht="15.75" customHeight="1">
       <c r="T958" s="11"/>
       <c r="U958" s="11"/>
       <c r="V958" s="11"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" spans="20:22" ht="15.75" customHeight="1">
       <c r="T959" s="11"/>
       <c r="U959" s="11"/>
       <c r="V959" s="11"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" spans="20:22" ht="15.75" customHeight="1">
       <c r="T960" s="11"/>
       <c r="U960" s="11"/>
       <c r="V960" s="11"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" spans="20:22" ht="15.75" customHeight="1">
       <c r="T961" s="11"/>
       <c r="U961" s="11"/>
       <c r="V961" s="11"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" spans="20:22" ht="15.75" customHeight="1">
       <c r="T962" s="11"/>
       <c r="U962" s="11"/>
       <c r="V962" s="11"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" spans="20:22" ht="15.75" customHeight="1">
       <c r="T963" s="11"/>
       <c r="U963" s="11"/>
       <c r="V963" s="11"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" spans="20:22" ht="15.75" customHeight="1">
       <c r="T964" s="11"/>
       <c r="U964" s="11"/>
       <c r="V964" s="11"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" spans="20:22" ht="15.75" customHeight="1">
       <c r="T965" s="11"/>
       <c r="U965" s="11"/>
       <c r="V965" s="11"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" spans="20:22" ht="15.75" customHeight="1">
       <c r="T966" s="11"/>
       <c r="U966" s="11"/>
       <c r="V966" s="11"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" spans="20:22" ht="15.75" customHeight="1">
       <c r="T967" s="11"/>
       <c r="U967" s="11"/>
       <c r="V967" s="11"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" spans="20:22" ht="15.75" customHeight="1">
       <c r="T968" s="11"/>
       <c r="U968" s="11"/>
       <c r="V968" s="11"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" spans="20:22" ht="15.75" customHeight="1">
       <c r="T969" s="11"/>
       <c r="U969" s="11"/>
       <c r="V969" s="11"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" spans="20:22" ht="15.75" customHeight="1">
       <c r="T970" s="11"/>
       <c r="U970" s="11"/>
       <c r="V970" s="11"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" spans="20:22" ht="15.75" customHeight="1">
       <c r="T971" s="11"/>
       <c r="U971" s="11"/>
       <c r="V971" s="11"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" spans="20:22" ht="15.75" customHeight="1">
       <c r="T972" s="11"/>
       <c r="U972" s="11"/>
       <c r="V972" s="11"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" spans="20:22" ht="15.75" customHeight="1">
       <c r="T973" s="11"/>
       <c r="U973" s="11"/>
       <c r="V973" s="11"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" spans="20:22" ht="15.75" customHeight="1">
       <c r="T974" s="11"/>
       <c r="U974" s="11"/>
       <c r="V974" s="11"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" spans="20:22" ht="15.75" customHeight="1">
       <c r="T975" s="11"/>
       <c r="U975" s="11"/>
       <c r="V975" s="11"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" spans="20:22" ht="15.75" customHeight="1">
       <c r="T976" s="11"/>
       <c r="U976" s="11"/>
       <c r="V976" s="11"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" spans="20:22" ht="15.75" customHeight="1">
       <c r="T977" s="11"/>
       <c r="U977" s="11"/>
       <c r="V977" s="11"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" spans="20:22" ht="15.75" customHeight="1">
       <c r="T978" s="11"/>
       <c r="U978" s="11"/>
       <c r="V978" s="11"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" spans="20:22" ht="15.75" customHeight="1">
       <c r="T979" s="11"/>
       <c r="U979" s="11"/>
       <c r="V979" s="11"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" spans="20:22" ht="15.75" customHeight="1">
       <c r="T980" s="11"/>
       <c r="U980" s="11"/>
       <c r="V980" s="11"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" spans="20:22" ht="15.75" customHeight="1">
       <c r="T981" s="11"/>
       <c r="U981" s="11"/>
       <c r="V981" s="11"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" spans="20:22" ht="15.75" customHeight="1">
       <c r="T982" s="11"/>
       <c r="U982" s="11"/>
       <c r="V982" s="11"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" spans="20:22" ht="15.75" customHeight="1">
       <c r="T983" s="11"/>
       <c r="U983" s="11"/>
       <c r="V983" s="11"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" spans="20:22" ht="15.75" customHeight="1">
       <c r="T984" s="11"/>
       <c r="U984" s="11"/>
       <c r="V984" s="11"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" spans="20:22" ht="15.75" customHeight="1">
       <c r="T985" s="11"/>
       <c r="U985" s="11"/>
       <c r="V985" s="11"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" spans="20:22" ht="15.75" customHeight="1">
       <c r="T986" s="11"/>
       <c r="U986" s="11"/>
       <c r="V986" s="11"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" spans="20:22" ht="15.75" customHeight="1">
       <c r="T987" s="11"/>
       <c r="U987" s="11"/>
       <c r="V987" s="11"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" spans="20:22" ht="15.75" customHeight="1">
       <c r="T988" s="11"/>
       <c r="U988" s="11"/>
       <c r="V988" s="11"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" spans="20:22" ht="15.75" customHeight="1">
       <c r="T989" s="11"/>
       <c r="U989" s="11"/>
       <c r="V989" s="11"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" spans="20:22" ht="15.75" customHeight="1">
       <c r="T990" s="11"/>
       <c r="U990" s="11"/>
       <c r="V990" s="11"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" spans="20:22" ht="15.75" customHeight="1">
       <c r="T991" s="11"/>
       <c r="U991" s="11"/>
       <c r="V991" s="11"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" spans="20:22" ht="15.75" customHeight="1">
       <c r="T992" s="11"/>
       <c r="U992" s="11"/>
       <c r="V992" s="11"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" spans="20:22" ht="15.75" customHeight="1">
       <c r="T993" s="11"/>
       <c r="U993" s="11"/>
       <c r="V993" s="11"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" spans="20:22" ht="15.75" customHeight="1">
       <c r="T994" s="11"/>
       <c r="U994" s="11"/>
       <c r="V994" s="11"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" spans="20:22" ht="15.75" customHeight="1">
       <c r="T995" s="11"/>
       <c r="U995" s="11"/>
       <c r="V995" s="11"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" spans="20:22" ht="15.75" customHeight="1">
       <c r="T996" s="11"/>
       <c r="U996" s="11"/>
       <c r="V996" s="11"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" spans="20:22" ht="15.75" customHeight="1">
       <c r="T997" s="11"/>
       <c r="U997" s="11"/>
       <c r="V997" s="11"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" spans="20:22" ht="15.75" customHeight="1">
       <c r="T998" s="11"/>
       <c r="U998" s="11"/>
       <c r="V998" s="11"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" spans="20:22" ht="15.75" customHeight="1">
       <c r="T999" s="11"/>
       <c r="U999" s="11"/>
       <c r="V999" s="11"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" spans="20:22" ht="15.75" customHeight="1">
       <c r="T1000" s="11"/>
       <c r="U1000" s="11"/>
       <c r="V1000" s="11"/>
     </row>
-    <row r="1001" ht="15.75" customHeight="1">
+    <row r="1001" spans="20:22" ht="15.75" customHeight="1">
       <c r="T1001" s="11"/>
       <c r="U1001" s="11"/>
       <c r="V1001" s="11"/>
     </row>
-    <row r="1002" ht="15.75" customHeight="1">
+    <row r="1002" spans="20:22" ht="15.75" customHeight="1">
       <c r="T1002" s="11"/>
       <c r="U1002" s="11"/>
       <c r="V1002" s="11"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="153">
   <si>
     <t>아이디</t>
   </si>
@@ -79,6 +79,9 @@
     <t>추가 데미지</t>
   </si>
   <si>
+    <t>이펙트 반지름</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t>ExtraDamage</t>
+  </si>
+  <si>
+    <t>VFXRadius</t>
   </si>
   <si>
     <t>skill_scholar_basic_fire</t>
@@ -564,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -611,7 +617,8 @@
     <xf borderId="1" fillId="0" fontId="5" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -929,152 +936,161 @@
       <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="O2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="P2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="W2" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="V3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" s="7">
         <v>15.0</v>
@@ -1105,36 +1121,37 @@
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R4" s="9"/>
       <c r="S4" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T4" s="12"/>
       <c r="U4" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V4" s="14">
         <v>10.0</v>
       </c>
+      <c r="W4" s="12"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D5" s="8">
         <v>15.0</v>
@@ -1163,34 +1180,35 @@
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T5" s="12"/>
       <c r="U5" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="8">
         <v>28.0</v>
@@ -1219,34 +1237,35 @@
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="T6" s="12"/>
       <c r="U6" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="8">
         <v>10.0</v>
@@ -1275,34 +1294,35 @@
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="T7" s="12"/>
       <c r="U7" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D8" s="7">
         <v>18.0</v>
@@ -1331,34 +1351,35 @@
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R8" s="9"/>
       <c r="S8" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T8" s="12"/>
       <c r="U8" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" s="7">
         <v>40.0</v>
@@ -1387,720 +1408,737 @@
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P9" s="15"/>
       <c r="Q9" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="12"/>
       <c r="U9" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V9" s="12"/>
       <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="18">
+      <c r="B10" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="19">
         <v>45.0</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <v>8.0</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <v>30.0</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18">
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19">
         <v>4.0</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="19">
         <v>10.0</v>
       </c>
-      <c r="M10" s="18"/>
+      <c r="M10" s="19"/>
       <c r="N10" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="P10" s="18"/>
+        <v>54</v>
+      </c>
+      <c r="P10" s="19"/>
       <c r="Q10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="R10" s="18"/>
-      <c r="S10" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R10" s="19"/>
+      <c r="S10" s="18" t="s">
+        <v>90</v>
       </c>
       <c r="T10" s="12"/>
       <c r="U10" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="18">
+      <c r="A11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="19">
         <v>45.0</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <v>8.0</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <v>30.0</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18">
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19">
         <v>4.0</v>
       </c>
-      <c r="L11" s="18">
+      <c r="L11" s="19">
         <v>10.0</v>
       </c>
-      <c r="M11" s="18"/>
+      <c r="M11" s="19"/>
       <c r="N11" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P11" s="18"/>
+        <v>61</v>
+      </c>
+      <c r="P11" s="19"/>
       <c r="Q11" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="18"/>
-      <c r="S11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R11" s="19"/>
+      <c r="S11" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="T11" s="12"/>
       <c r="U11" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="A12" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="19">
         <v>45.0</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <v>8.0</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <v>30.0</v>
       </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18">
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19">
         <v>4.0</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="19">
         <v>10.0</v>
       </c>
-      <c r="M12" s="18"/>
+      <c r="M12" s="19"/>
       <c r="N12" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P12" s="18"/>
+        <v>67</v>
+      </c>
+      <c r="P12" s="19"/>
       <c r="Q12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="R12" s="18"/>
-      <c r="S12" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R12" s="19"/>
+      <c r="S12" s="18" t="s">
+        <v>99</v>
       </c>
       <c r="T12" s="12"/>
       <c r="U12" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V12" s="12"/>
+      <c r="W12" s="12"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="18">
+      <c r="A13" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="19">
         <v>45.0</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <v>8.0</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <v>30.0</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19">
         <v>4.0</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="19">
         <v>10.0</v>
       </c>
-      <c r="M13" s="18"/>
+      <c r="M13" s="19"/>
       <c r="N13" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="P13" s="18"/>
+        <v>73</v>
+      </c>
+      <c r="P13" s="19"/>
       <c r="Q13" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="R13" s="18"/>
-      <c r="S13" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R13" s="19"/>
+      <c r="S13" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="T13" s="12"/>
       <c r="U13" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="18">
+      <c r="A14" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="19">
         <v>45.0</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <v>8.0</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <v>30.0</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18">
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19">
         <v>4.0</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="19">
         <v>10.0</v>
       </c>
-      <c r="M14" s="18"/>
+      <c r="M14" s="19"/>
       <c r="N14" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="P14" s="18"/>
+        <v>79</v>
+      </c>
+      <c r="P14" s="19"/>
       <c r="Q14" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="R14" s="18"/>
-      <c r="S14" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R14" s="19"/>
+      <c r="S14" s="18" t="s">
+        <v>107</v>
       </c>
       <c r="T14" s="12"/>
       <c r="U14" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V14" s="12"/>
+      <c r="W14" s="13">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18">
+      <c r="B15" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19">
         <v>45.0</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <v>60.0</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="18">
         <v>8.0</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18">
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19">
         <v>5.0</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="19">
         <v>8.0</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="19">
         <v>120.0</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O15" s="9"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="R15" s="18"/>
-      <c r="S15" s="17" t="s">
-        <v>111</v>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="R15" s="19"/>
+      <c r="S15" s="18" t="s">
+        <v>113</v>
       </c>
       <c r="T15" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="18" t="s">
+      <c r="A16" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19">
+        <v>60.0</v>
+      </c>
+      <c r="F16" s="19">
+        <v>50.0</v>
+      </c>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q16" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="U16" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18">
-        <v>60.0</v>
-      </c>
-      <c r="F16" s="18">
-        <v>50.0</v>
-      </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q16" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="R16" s="18"/>
-      <c r="S16" s="18"/>
-      <c r="T16" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="U16" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
+      <c r="B17" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
       <c r="N17" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O17" s="9"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="18"/>
-      <c r="S17" s="17" t="s">
-        <v>125</v>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="19"/>
+      <c r="S17" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="T17" s="12"/>
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="D18" s="18">
+      <c r="B18" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="19">
         <v>20.0</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="19">
         <v>0.65</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="19">
         <v>0.0</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="19">
         <v>3.0</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="19">
         <v>15.0</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="19">
         <v>1.0</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="19">
         <v>1.0</v>
       </c>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18">
+      <c r="K18" s="19"/>
+      <c r="L18" s="19">
         <v>12.0</v>
       </c>
-      <c r="M18" s="18"/>
+      <c r="M18" s="19"/>
       <c r="N18" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="17" t="s">
-        <v>129</v>
+        <v>79</v>
+      </c>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="18" t="s">
+        <v>131</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="V18" s="13"/>
+      <c r="W18" s="12"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
+        <v>133</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="17" t="s">
-        <v>133</v>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="18" t="s">
+        <v>135</v>
       </c>
       <c r="T19" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U19" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V19" s="13"/>
+      <c r="W19" s="12"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
+      <c r="B20" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
       <c r="N20" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O20" s="9"/>
-      <c r="P20" s="18"/>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="19"/>
+      <c r="S20" s="19"/>
       <c r="T20" s="12"/>
       <c r="U20" s="12"/>
       <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="18">
+      <c r="B21" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="19">
         <v>18.0</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <v>0.55</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <v>0.0</v>
       </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18">
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19">
         <v>2.0</v>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="19">
         <v>2.5</v>
       </c>
-      <c r="M21" s="18"/>
+      <c r="M21" s="19"/>
       <c r="N21" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P21" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
+        <v>67</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="19"/>
+      <c r="S21" s="19"/>
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
       <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="A22" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="18">
+      <c r="B22" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="19">
         <v>32.0</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="19">
         <v>7.0</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="19">
         <v>25.0</v>
       </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18">
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19">
         <v>3.5</v>
       </c>
-      <c r="L22" s="18">
+      <c r="L22" s="19">
         <v>4.5</v>
       </c>
-      <c r="M22" s="18"/>
+      <c r="M22" s="19"/>
       <c r="N22" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
+        <v>67</v>
+      </c>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
       <c r="T22" s="13"/>
       <c r="U22" s="12"/>
       <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" s="18" t="s">
+      <c r="A23" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="18">
+      <c r="B23" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="19">
         <v>90.0</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="19">
         <v>45.0</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="19">
         <v>50.0</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="19">
         <v>2.0</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="19">
         <v>10.0</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="19">
         <v>0.0</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="19">
         <v>1.0</v>
       </c>
-      <c r="K23" s="18">
+      <c r="K23" s="19">
         <v>3.0</v>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="19">
         <v>10.0</v>
       </c>
-      <c r="M23" s="18"/>
+      <c r="M23" s="19"/>
       <c r="N23" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
+        <v>67</v>
+      </c>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
       <c r="T23" s="12"/>
       <c r="U23" s="12"/>
       <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C24" s="18" t="s">
+      <c r="A24" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="18">
+      <c r="B24" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="19">
         <v>18.0</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="19">
         <v>60.0</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="19">
         <v>55.0</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="19">
         <v>5.0</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="19">
         <v>4.0</v>
       </c>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19">
         <v>1.0</v>
       </c>
-      <c r="K24" s="18">
+      <c r="K24" s="19">
         <v>5.0</v>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="19">
         <v>10.0</v>
       </c>
-      <c r="M24" s="18"/>
+      <c r="M24" s="19"/>
       <c r="N24" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="18"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
+        <v>67</v>
+      </c>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
       <c r="T24" s="12"/>
       <c r="U24" s="12"/>
       <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
@@ -6807,97 +6845,97 @@
       <c r="V220" s="12"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="21"/>
-      <c r="B221" s="21"/>
-      <c r="C221" s="21"/>
-      <c r="D221" s="21"/>
-      <c r="E221" s="21"/>
-      <c r="F221" s="21"/>
-      <c r="G221" s="21"/>
-      <c r="H221" s="21"/>
-      <c r="I221" s="21"/>
-      <c r="J221" s="21"/>
-      <c r="K221" s="21"/>
-      <c r="L221" s="21"/>
-      <c r="M221" s="21"/>
-      <c r="N221" s="21"/>
-      <c r="O221" s="21"/>
-      <c r="P221" s="21"/>
-      <c r="Q221" s="21"/>
-      <c r="R221" s="21"/>
-      <c r="S221" s="21"/>
+      <c r="A221" s="22"/>
+      <c r="B221" s="22"/>
+      <c r="C221" s="22"/>
+      <c r="D221" s="22"/>
+      <c r="E221" s="22"/>
+      <c r="F221" s="22"/>
+      <c r="G221" s="22"/>
+      <c r="H221" s="22"/>
+      <c r="I221" s="22"/>
+      <c r="J221" s="22"/>
+      <c r="K221" s="22"/>
+      <c r="L221" s="22"/>
+      <c r="M221" s="22"/>
+      <c r="N221" s="22"/>
+      <c r="O221" s="22"/>
+      <c r="P221" s="22"/>
+      <c r="Q221" s="22"/>
+      <c r="R221" s="22"/>
+      <c r="S221" s="22"/>
       <c r="T221" s="12"/>
       <c r="U221" s="12"/>
       <c r="V221" s="12"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="21"/>
-      <c r="B222" s="21"/>
-      <c r="C222" s="21"/>
-      <c r="D222" s="21"/>
-      <c r="E222" s="21"/>
-      <c r="F222" s="21"/>
-      <c r="G222" s="21"/>
-      <c r="H222" s="21"/>
-      <c r="I222" s="21"/>
-      <c r="J222" s="21"/>
-      <c r="K222" s="21"/>
-      <c r="L222" s="21"/>
-      <c r="M222" s="21"/>
-      <c r="N222" s="21"/>
-      <c r="O222" s="21"/>
-      <c r="P222" s="21"/>
-      <c r="Q222" s="21"/>
-      <c r="R222" s="21"/>
-      <c r="S222" s="21"/>
+      <c r="A222" s="22"/>
+      <c r="B222" s="22"/>
+      <c r="C222" s="22"/>
+      <c r="D222" s="22"/>
+      <c r="E222" s="22"/>
+      <c r="F222" s="22"/>
+      <c r="G222" s="22"/>
+      <c r="H222" s="22"/>
+      <c r="I222" s="22"/>
+      <c r="J222" s="22"/>
+      <c r="K222" s="22"/>
+      <c r="L222" s="22"/>
+      <c r="M222" s="22"/>
+      <c r="N222" s="22"/>
+      <c r="O222" s="22"/>
+      <c r="P222" s="22"/>
+      <c r="Q222" s="22"/>
+      <c r="R222" s="22"/>
+      <c r="S222" s="22"/>
       <c r="T222" s="12"/>
       <c r="U222" s="12"/>
       <c r="V222" s="12"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="21"/>
-      <c r="B223" s="21"/>
-      <c r="C223" s="21"/>
-      <c r="D223" s="21"/>
-      <c r="E223" s="21"/>
-      <c r="F223" s="21"/>
-      <c r="G223" s="21"/>
-      <c r="H223" s="21"/>
-      <c r="I223" s="21"/>
-      <c r="J223" s="21"/>
-      <c r="K223" s="21"/>
-      <c r="L223" s="21"/>
-      <c r="M223" s="21"/>
-      <c r="N223" s="21"/>
-      <c r="O223" s="21"/>
-      <c r="P223" s="21"/>
-      <c r="Q223" s="21"/>
-      <c r="R223" s="21"/>
-      <c r="S223" s="21"/>
+      <c r="A223" s="22"/>
+      <c r="B223" s="22"/>
+      <c r="C223" s="22"/>
+      <c r="D223" s="22"/>
+      <c r="E223" s="22"/>
+      <c r="F223" s="22"/>
+      <c r="G223" s="22"/>
+      <c r="H223" s="22"/>
+      <c r="I223" s="22"/>
+      <c r="J223" s="22"/>
+      <c r="K223" s="22"/>
+      <c r="L223" s="22"/>
+      <c r="M223" s="22"/>
+      <c r="N223" s="22"/>
+      <c r="O223" s="22"/>
+      <c r="P223" s="22"/>
+      <c r="Q223" s="22"/>
+      <c r="R223" s="22"/>
+      <c r="S223" s="22"/>
       <c r="T223" s="12"/>
       <c r="U223" s="12"/>
       <c r="V223" s="12"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="21"/>
-      <c r="B224" s="21"/>
-      <c r="C224" s="21"/>
-      <c r="D224" s="21"/>
-      <c r="E224" s="21"/>
-      <c r="F224" s="21"/>
-      <c r="G224" s="21"/>
-      <c r="H224" s="21"/>
-      <c r="I224" s="21"/>
-      <c r="J224" s="21"/>
-      <c r="K224" s="21"/>
-      <c r="L224" s="21"/>
-      <c r="M224" s="21"/>
-      <c r="N224" s="21"/>
-      <c r="O224" s="21"/>
-      <c r="P224" s="21"/>
-      <c r="Q224" s="21"/>
-      <c r="R224" s="21"/>
-      <c r="S224" s="21"/>
+      <c r="A224" s="22"/>
+      <c r="B224" s="22"/>
+      <c r="C224" s="22"/>
+      <c r="D224" s="22"/>
+      <c r="E224" s="22"/>
+      <c r="F224" s="22"/>
+      <c r="G224" s="22"/>
+      <c r="H224" s="22"/>
+      <c r="I224" s="22"/>
+      <c r="J224" s="22"/>
+      <c r="K224" s="22"/>
+      <c r="L224" s="22"/>
+      <c r="M224" s="22"/>
+      <c r="N224" s="22"/>
+      <c r="O224" s="22"/>
+      <c r="P224" s="22"/>
+      <c r="Q224" s="22"/>
+      <c r="R224" s="22"/>
+      <c r="S224" s="22"/>
       <c r="T224" s="12"/>
       <c r="U224" s="12"/>
       <c r="V224" s="12"/>

--- a/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerSkillData.xlsx
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="153">
-  <si>
-    <t>아이디</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="152">
   <si>
     <t>이름</t>
   </si>
@@ -373,7 +370,7 @@
     <t>Pet</t>
   </si>
   <si>
-    <t>buff_berserksoul_petattackspeed, buff_berserksoul_petmaxhealth, buff_berserksoul_petmovespeed</t>
+    <t>buff_berserksoul_petattackspeed,buff_berserksoul_petmaxhealth,buff_berserksoul_petmovespeed</t>
   </si>
   <si>
     <t>Scholar/BererkSoulEffect</t>
@@ -629,7 +626,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -870,227 +867,225 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" ht="24.0" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="W2" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="W2" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" ht="27.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="W3" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="D4" s="7">
         <v>15.0</v>
@@ -1121,22 +1116,22 @@
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R4" s="9"/>
       <c r="S4" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T4" s="12"/>
       <c r="U4" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V4" s="14">
         <v>10.0</v>
@@ -1145,13 +1140,13 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="D5" s="8">
         <v>15.0</v>
@@ -1180,35 +1175,35 @@
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T5" s="12"/>
       <c r="U5" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V5" s="12"/>
       <c r="W5" s="12"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="D6" s="8">
         <v>28.0</v>
@@ -1237,35 +1232,35 @@
       </c>
       <c r="M6" s="8"/>
       <c r="N6" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T6" s="12"/>
       <c r="U6" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="D7" s="8">
         <v>10.0</v>
@@ -1294,35 +1289,35 @@
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P7" s="8"/>
       <c r="Q7" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T7" s="12"/>
       <c r="U7" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="D8" s="7">
         <v>18.0</v>
@@ -1351,35 +1346,35 @@
       </c>
       <c r="M8" s="8"/>
       <c r="N8" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R8" s="9"/>
       <c r="S8" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T8" s="12"/>
       <c r="U8" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="D9" s="7">
         <v>40.0</v>
@@ -1408,20 +1403,20 @@
       </c>
       <c r="M9" s="8"/>
       <c r="N9" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P9" s="15"/>
       <c r="Q9" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="12"/>
       <c r="U9" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V9" s="12"/>
       <c r="W9" s="16"/>
@@ -1431,13 +1426,13 @@
     </row>
     <row r="10">
       <c r="A10" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="19" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>88</v>
       </c>
       <c r="D10" s="19">
         <v>45.0</v>
@@ -1460,35 +1455,35 @@
       </c>
       <c r="M10" s="19"/>
       <c r="N10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="P10" s="19"/>
       <c r="Q10" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R10" s="19"/>
       <c r="S10" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T10" s="12"/>
       <c r="U10" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
     </row>
     <row r="11">
       <c r="A11" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>93</v>
-      </c>
       <c r="C11" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="19">
         <v>45.0</v>
@@ -1511,35 +1506,35 @@
       </c>
       <c r="M11" s="19"/>
       <c r="N11" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P11" s="19"/>
       <c r="Q11" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R11" s="19"/>
       <c r="S11" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T11" s="12"/>
       <c r="U11" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>97</v>
-      </c>
       <c r="C12" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="19">
         <v>45.0</v>
@@ -1562,35 +1557,35 @@
       </c>
       <c r="M12" s="19"/>
       <c r="N12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P12" s="19"/>
       <c r="Q12" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R12" s="19"/>
       <c r="S12" s="18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T12" s="12"/>
       <c r="U12" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
     </row>
     <row r="13">
       <c r="A13" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>101</v>
-      </c>
       <c r="C13" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" s="19">
         <v>45.0</v>
@@ -1613,35 +1608,35 @@
       </c>
       <c r="M13" s="19"/>
       <c r="N13" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P13" s="19"/>
       <c r="Q13" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R13" s="19"/>
       <c r="S13" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T13" s="12"/>
       <c r="U13" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>105</v>
-      </c>
       <c r="C14" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" s="19">
         <v>45.0</v>
@@ -1664,22 +1659,22 @@
       </c>
       <c r="M14" s="19"/>
       <c r="N14" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P14" s="19"/>
       <c r="Q14" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R14" s="19"/>
       <c r="S14" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T14" s="12"/>
       <c r="U14" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V14" s="12"/>
       <c r="W14" s="13">
@@ -1688,13 +1683,13 @@
     </row>
     <row r="15">
       <c r="A15" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="C15" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>110</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19">
@@ -1719,35 +1714,35 @@
         <v>120.0</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="19"/>
       <c r="Q15" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R15" s="19"/>
       <c r="S15" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="T15" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="T15" s="13" t="s">
+      <c r="U15" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="U15" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="V15" s="12"/>
       <c r="W15" s="12"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="C16" s="19" t="s">
         <v>117</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>118</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19">
@@ -1764,35 +1759,35 @@
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O16" s="9"/>
       <c r="P16" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q16" s="18" t="s">
         <v>120</v>
-      </c>
-      <c r="Q16" s="18" t="s">
-        <v>121</v>
       </c>
       <c r="R16" s="19"/>
       <c r="S16" s="19"/>
       <c r="T16" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U16" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V16" s="12"/>
       <c r="W16" s="12"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="C17" s="19" t="s">
         <v>124</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>125</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -1805,14 +1800,14 @@
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O17" s="9"/>
       <c r="P17" s="19"/>
       <c r="Q17" s="19"/>
       <c r="R17" s="19"/>
       <c r="S17" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="T17" s="12"/>
       <c r="U17" s="12"/>
@@ -1821,13 +1816,13 @@
     </row>
     <row r="18">
       <c r="A18" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="C18" s="19" t="s">
         <v>129</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>130</v>
       </c>
       <c r="D18" s="19">
         <v>20.0</v>
@@ -1856,37 +1851,45 @@
       </c>
       <c r="M18" s="19"/>
       <c r="N18" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P18" s="19"/>
       <c r="Q18" s="19"/>
       <c r="R18" s="19"/>
       <c r="S18" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="T18" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="T18" s="13" t="s">
-        <v>132</v>
-      </c>
       <c r="U18" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V18" s="13"/>
       <c r="W18" s="12"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="19">
+        <v>45.0</v>
+      </c>
+      <c r="E19" s="19">
+        <v>8.0</v>
+      </c>
+      <c r="F19" s="19">
+        <v>30.0</v>
+      </c>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
@@ -1900,26 +1903,26 @@
       <c r="Q19" s="19"/>
       <c r="R19" s="19"/>
       <c r="S19" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="T19" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="T19" s="13" t="s">
-        <v>136</v>
-      </c>
       <c r="U19" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V19" s="13"/>
       <c r="W19" s="12"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="C20" s="19" t="s">
         <v>138</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>139</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
@@ -1932,7 +1935,7 @@
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O20" s="9"/>
       <c r="P20" s="19"/>
@@ -1946,13 +1949,13 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="19" t="s">
         <v>141</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>142</v>
       </c>
       <c r="D21" s="19">
         <v>18.0</v>
@@ -1975,13 +1978,13 @@
       </c>
       <c r="M21" s="19"/>
       <c r="N21" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P21" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q21" s="19"/>
       <c r="R21" s="19"/>
@@ -1993,13 +1996,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="19" t="s">
         <v>145</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>146</v>
       </c>
       <c r="D22" s="19">
         <v>32.0</v>
@@ -2022,10 +2025,10 @@
       </c>
       <c r="M22" s="19"/>
       <c r="N22" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P22" s="19"/>
       <c r="Q22" s="19"/>
@@ -2038,13 +2041,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="C23" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>149</v>
       </c>
       <c r="D23" s="19">
         <v>90.0</v>
@@ -2075,10 +2078,10 @@
       </c>
       <c r="M23" s="19"/>
       <c r="N23" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P23" s="19"/>
       <c r="Q23" s="19"/>
@@ -2091,13 +2094,13 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="C24" s="19" t="s">
         <v>151</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>152</v>
       </c>
       <c r="D24" s="19">
         <v>18.0</v>
@@ -2126,10 +2129,10 @@
       </c>
       <c r="M24" s="19"/>
       <c r="N24" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P24" s="19"/>
       <c r="Q24" s="19"/>
